--- a/基本設計/10_API共通と認証_基本設計書.xlsx
+++ b/基本設計/10_API共通と認証_基本設計書.xlsx
@@ -2,16 +2,16 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00_表紙" sheetId="1" r:id="R69b80f91edf8410e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_改訂履歴" sheetId="2" r:id="R46b75ab88d4546fe"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="18_API一覧" sheetId="19" r:id="Rf882653721404656"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="19_API共通I-O" sheetId="20" r:id="R8a458c4ed70d4b02"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="20_API主要項目処理" sheetId="21" r:id="Ree88a1af7628464c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="21_エラーコード" sheetId="22" r:id="R3605ce5c20bb4d52"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="22_API処理・権限" sheetId="23" r:id="R22a75eb7c64945af"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="23_API項目定義" sheetId="24" r:id="R538ced10f2d04ac1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="24_APIサンプル" sheetId="25" r:id="R8aa0f1749a424011"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="25_API権限対応" sheetId="26" r:id="R344774821a934ddb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00_表紙" sheetId="1" r:id="R446effeec1d74afc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_改訂履歴" sheetId="2" r:id="R8f07e1d5e77e4559"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="18_API一覧" sheetId="19" r:id="Rf3e0cf9789994f3a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="19_API共通I-O" sheetId="20" r:id="R936264e325324bcf"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="20_API主要項目処理" sheetId="21" r:id="R17c4f27076de4fa9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="21_エラーコード" sheetId="22" r:id="R59197ae24c944140"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="22_API処理・権限" sheetId="23" r:id="Rf1fa536a330845b6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="23_API項目定義" sheetId="24" r:id="Red899e757b90439c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="24_APIサンプル" sheetId="25" r:id="R1ff5d8fcdee64c92"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="25_API権限対応" sheetId="26" r:id="Rfbed900a7d6d4928"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1298,10 +1298,7 @@
       <x:c r="F16" s="196"/>
     </x:row>
     <x:row r="17">
-      <x:c r="A17" t="str">
-        <x:v>本書は Company WorkHub の基本設計内容を定義する。
-Ver.1.8 は状態変更入口、API/DB制約、取込Transaction、日報一意制約、通知・Token保持を整合した再Review対応版である。</x:v>
-      </x:c>
+      <x:c r="A17"/>
       <x:c r="C17"/>
       <x:c r="D17"/>
       <x:c r="E17"/>
@@ -1317,25 +1314,22 @@
     </x:row>
     <x:row r="19">
       <x:c r="A19"/>
-      <x:c r="B19" s="240" t="str">
-        <x:v>本書は Company WorkHub の基本設計内容を定義する。
-Ver.1.7 は状態変更入口、API/DB制約、取込Transaction、日報一意制約、通知・Token保持を整合した再Review対応版である。</x:v>
-      </x:c>
-      <x:c r="C19" s="240"/>
-      <x:c r="D19" s="240"/>
-      <x:c r="E19" s="240"/>
-      <x:c r="F19" s="240"/>
-      <x:c r="G19" s="240"/>
-      <x:c r="H19" s="240"/>
+      <x:c r="B19"/>
+      <x:c r="C19"/>
+      <x:c r="D19"/>
+      <x:c r="E19"/>
+      <x:c r="F19"/>
+      <x:c r="G19"/>
+      <x:c r="H19"/>
     </x:row>
     <x:row r="20">
-      <x:c r="B20" s="240"/>
-      <x:c r="C20" s="240"/>
-      <x:c r="D20" s="240"/>
-      <x:c r="E20" s="240"/>
-      <x:c r="F20" s="240"/>
-      <x:c r="G20" s="240"/>
-      <x:c r="H20" s="240"/>
+      <x:c r="B20"/>
+      <x:c r="C20"/>
+      <x:c r="D20"/>
+      <x:c r="E20"/>
+      <x:c r="F20"/>
+      <x:c r="G20"/>
+      <x:c r="H20"/>
     </x:row>
     <x:row r="21">
       <x:c r="B21" s="240"/>
@@ -4525,17 +4519,15 @@
       <x:c r="I29" s="64"/>
     </x:row>
     <x:row r="30">
-      <x:c r="A30" s="88" t="str">
-        <x:v>Class名、Method名、SQLは詳細設計で定義する。ただし本SheetのURL、I/O、権限、Data範囲、Error契約はPG判断で変更しない。</x:v>
-      </x:c>
-      <x:c r="B30" s="89"/>
-      <x:c r="C30" s="89"/>
-      <x:c r="D30" s="89"/>
-      <x:c r="E30" s="89"/>
-      <x:c r="F30" s="89"/>
-      <x:c r="G30" s="89"/>
-      <x:c r="H30" s="89"/>
-      <x:c r="I30" s="90"/>
+      <x:c r="A30"/>
+      <x:c r="B30"/>
+      <x:c r="C30"/>
+      <x:c r="D30"/>
+      <x:c r="E30"/>
+      <x:c r="F30"/>
+      <x:c r="G30"/>
+      <x:c r="H30"/>
+      <x:c r="I30"/>
     </x:row>
     <x:row r="31">
       <x:c r="A31" s="91"/>

--- a/基本設計/10_API共通と認証_基本設計書.xlsx
+++ b/基本設計/10_API共通と認証_基本設計書.xlsx
@@ -2,16 +2,14 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00_表紙" sheetId="1" r:id="R446effeec1d74afc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_改訂履歴" sheetId="2" r:id="R8f07e1d5e77e4559"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="18_API一覧" sheetId="19" r:id="Rf3e0cf9789994f3a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="19_API共通I-O" sheetId="20" r:id="R936264e325324bcf"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="20_API主要項目処理" sheetId="21" r:id="R17c4f27076de4fa9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="21_エラーコード" sheetId="22" r:id="R59197ae24c944140"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="22_API処理・権限" sheetId="23" r:id="Rf1fa536a330845b6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="23_API項目定義" sheetId="24" r:id="Red899e757b90439c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="24_APIサンプル" sheetId="25" r:id="R1ff5d8fcdee64c92"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="25_API権限対応" sheetId="26" r:id="Rfbed900a7d6d4928"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00_表紙" sheetId="1" r:id="R84cc4ccf8b664f89"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_改訂履歴" sheetId="2" r:id="R14e99cd0657a4b1b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="18_API一覧" sheetId="19" r:id="R4387273638c94cc7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="19_API共通I-O" sheetId="20" r:id="R9124917b8c9c440d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="21_エラーコード" sheetId="22" r:id="R85e6074e324243fe"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="22_API処理・権限" sheetId="23" r:id="R1a362846ed4e40d2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="23_API項目定義" sheetId="24" r:id="R78c4b59547e34f12"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="24_APIサンプル" sheetId="25" r:id="R1b425e0f3f6e4f01"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -25,7 +23,7 @@
   <x:numFmts count="1">
     <x:numFmt numFmtId="200" formatCode="yyyy-mm-dd"/>
   </x:numFmts>
-  <x:fonts count="25">
+  <x:fonts count="27">
     <x:font>
       <x:sz val="11"/>
       <x:name val="Carlito"/>
@@ -164,8 +162,19 @@
       <x:color rgb="FF1F1F1F"/>
       <x:name val="Yu Gothic"/>
     </x:font>
+    <x:font>
+      <x:sz val="10"/>
+      <x:color rgb="FF18283A"/>
+      <x:name val="Yu Gothic"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="17"/>
+      <x:color rgb="FF193C61"/>
+      <x:name val="Yu Gothic"/>
+    </x:font>
   </x:fonts>
-  <x:fills count="29">
+  <x:fills count="31">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -307,8 +316,18 @@
         <x:fgColor rgb="FFFFF2CC"/>
       </x:patternFill>
     </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF234F77"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFF1F5FA"/>
+      </x:patternFill>
+    </x:fill>
   </x:fills>
-  <x:borders count="8">
+  <x:borders count="9">
     <x:border/>
     <x:border>
       <x:left style="thin">
@@ -366,11 +385,25 @@
         <x:color rgb="FFA6A6A6"/>
       </x:bottom>
     </x:border>
+    <x:border>
+      <x:left style="thin">
+        <x:color rgb="FFD4DEE8"/>
+      </x:left>
+      <x:right style="thin">
+        <x:color rgb="FFD4DEE8"/>
+      </x:right>
+      <x:top style="thin">
+        <x:color rgb="FFD4DEE8"/>
+      </x:top>
+      <x:bottom style="thin">
+        <x:color rgb="FFD4DEE8"/>
+      </x:bottom>
+    </x:border>
   </x:borders>
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="241">
+  <x:cellXfs count="259">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -868,6 +901,56 @@
     <x:xf numFmtId="0" fontId="24" fillId="28" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="23" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="25" fillId="29" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="29" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="25" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="25" fillId="30" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="14" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
@@ -1236,8 +1319,8 @@
     </x:row>
     <x:row r="11">
       <x:c r="B11"/>
-      <x:c r="C11" t="str">
-        <x:v>Ver.1.8</x:v>
+      <x:c r="C11" s="203" t="str">
+        <x:v>Ver.2.5</x:v>
       </x:c>
       <x:c r="D11"/>
       <x:c r="E11"/>
@@ -1246,8 +1329,8 @@
       <x:c r="H11"/>
     </x:row>
     <x:row r="12">
-      <x:c r="C12" s="235" t="str">
-        <x:v>文書番号</x:v>
+      <x:c r="C12" s="242" t="str">
+        <x:v>Document ID</x:v>
       </x:c>
       <x:c r="D12" s="196" t="str">
         <x:v>CW-BD-API-AUTH</x:v>
@@ -1259,8 +1342,8 @@
       <x:c r="C13" s="235" t="str">
         <x:v>版数</x:v>
       </x:c>
-      <x:c r="D13" s="196" t="str">
-        <x:v>Ver.1.8</x:v>
+      <x:c r="D13" s="243" t="str">
+        <x:v>Ver.2.5</x:v>
       </x:c>
       <x:c r="E13" s="196"/>
       <x:c r="F13" s="196"/>
@@ -1269,8 +1352,8 @@
       <x:c r="C14" s="235" t="str">
         <x:v>改訂日</x:v>
       </x:c>
-      <x:c r="D14" s="196" t="str">
-        <x:v>2026-08-12</x:v>
+      <x:c r="D14" s="243" t="str">
+        <x:v>2026-09-24</x:v>
       </x:c>
       <x:c r="E14" s="196"/>
       <x:c r="F14" s="196"/>
@@ -1291,24 +1374,29 @@
       <x:c r="C16" s="235" t="str">
         <x:v>状態</x:v>
       </x:c>
-      <x:c r="D16" s="196" t="str">
-        <x:v>レビュー待ち</x:v>
+      <x:c r="D16" s="243" t="str">
+        <x:v>Review中</x:v>
       </x:c>
       <x:c r="E16" s="196"/>
       <x:c r="F16" s="196"/>
     </x:row>
-    <x:row r="17">
-      <x:c r="A17"/>
-      <x:c r="C17"/>
-      <x:c r="D17"/>
+    <x:row r="17" ht="26" customHeight="1">
+      <x:c r="A17" s="245"/>
+      <x:c r="B17" s="245"/>
+      <x:c r="C17" s="245"/>
+      <x:c r="D17" s="245"/>
       <x:c r="E17"/>
       <x:c r="F17"/>
     </x:row>
-    <x:row r="18">
-      <x:c r="A18"/>
-      <x:c r="B18"/>
-      <x:c r="C18"/>
-      <x:c r="D18"/>
+    <x:row r="18" ht="26" customHeight="1">
+      <x:c r="A18" s="245"/>
+      <x:c r="B18" s="245"/>
+      <x:c r="C18" s="245" t="str">
+        <x:v>Baseline ID</x:v>
+      </x:c>
+      <x:c r="D18" s="245" t="str">
+        <x:v>BL-2026-09-24</x:v>
+      </x:c>
       <x:c r="E18"/>
       <x:c r="F18"/>
     </x:row>
@@ -1375,546 +1463,6 @@
     <x:mergeCell ref="D15:F15"/>
     <x:mergeCell ref="D16:F16"/>
     <x:mergeCell ref="B19:H21"/>
-  </x:mergeCells>
-  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</x:worksheet>
-</file>
-
-<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:sheetFormatPr defaultRowHeight="15"/>
-  <x:cols>
-    <x:col min="1" max="1" width="18" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="28" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="48" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="24" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="42" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="62" hidden="0" customWidth="1"/>
-  </x:cols>
-  <x:sheetData>
-    <x:row r="1">
-      <x:c r="A1" s="138" t="str">
-        <x:v>API権限対応</x:v>
-      </x:c>
-      <x:c r="B1" s="138"/>
-      <x:c r="C1" s="138"/>
-      <x:c r="D1" s="138"/>
-      <x:c r="E1" s="138"/>
-      <x:c r="F1" s="138"/>
-    </x:row>
-    <x:row r="2">
-      <x:c r="A2" s="138"/>
-      <x:c r="B2" s="138"/>
-      <x:c r="C2" s="138"/>
-      <x:c r="D2" s="138"/>
-      <x:c r="E2" s="138"/>
-      <x:c r="F2" s="138"/>
-    </x:row>
-    <x:row r="3">
-      <x:c r="A3" s="141" t="str">
-        <x:v>システム名</x:v>
-      </x:c>
-      <x:c r="B3" s="139" t="str">
-        <x:v>Company WorkHub</x:v>
-      </x:c>
-      <x:c r="C3" s="141" t="str">
-        <x:v>文書番号</x:v>
-      </x:c>
-      <x:c r="D3" s="139" t="str">
-        <x:v>CW-BD-10-PERM</x:v>
-      </x:c>
-      <x:c r="E3" s="139"/>
-      <x:c r="F3" s="139"/>
-    </x:row>
-    <x:row r="4">
-      <x:c r="A4" s="141" t="str">
-        <x:v>版数</x:v>
-      </x:c>
-      <x:c r="B4" s="139" t="str">
-        <x:v>Ver.1.8</x:v>
-      </x:c>
-      <x:c r="C4" s="141" t="str">
-        <x:v>改訂日</x:v>
-      </x:c>
-      <x:c r="D4" s="139" t="str">
-        <x:v>2026-08-12</x:v>
-      </x:c>
-      <x:c r="E4" s="139"/>
-      <x:c r="F4" s="139"/>
-    </x:row>
-    <x:row r="6">
-      <x:c r="A6" s="142" t="str">
-        <x:v>1. API・Permission・Data範囲</x:v>
-      </x:c>
-      <x:c r="B6" s="142"/>
-      <x:c r="C6" s="142"/>
-      <x:c r="D6" s="142"/>
-      <x:c r="E6" s="142"/>
-      <x:c r="F6" s="142"/>
-    </x:row>
-    <x:row r="7">
-      <x:c r="A7" s="147" t="str">
-        <x:v>API ID</x:v>
-      </x:c>
-      <x:c r="B7" s="147" t="str">
-        <x:v>API名</x:v>
-      </x:c>
-      <x:c r="C7" s="147" t="str">
-        <x:v>Permission Code</x:v>
-      </x:c>
-      <x:c r="D7" s="147" t="str">
-        <x:v>許可Role</x:v>
-      </x:c>
-      <x:c r="E7" s="147" t="str">
-        <x:v>Data範囲</x:v>
-      </x:c>
-      <x:c r="F7" s="147" t="str">
-        <x:v>判定方式</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="8">
-      <x:c r="A8" s="151" t="str">
-        <x:v>API-AUTH-001</x:v>
-      </x:c>
-      <x:c r="B8" s="151" t="str">
-        <x:v>ログイン</x:v>
-      </x:c>
-      <x:c r="C8" s="151" t="str">
-        <x:v>-（認証/本人共通）</x:v>
-      </x:c>
-      <x:c r="D8" s="151" t="str">
-        <x:v>不要</x:v>
-      </x:c>
-      <x:c r="E8" s="151" t="str">
-        <x:v>未認証</x:v>
-      </x:c>
-      <x:c r="F8" s="151" t="str">
-        <x:v>認証・本人/共通条件をServiceで判定</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9">
-      <x:c r="A9" s="151" t="str">
-        <x:v>API-AUTH-002</x:v>
-      </x:c>
-      <x:c r="B9" s="151" t="str">
-        <x:v>ログアウト</x:v>
-      </x:c>
-      <x:c r="C9" s="151" t="str">
-        <x:v>-（認証/本人共通）</x:v>
-      </x:c>
-      <x:c r="D9" s="151" t="str">
-        <x:v>全員</x:v>
-      </x:c>
-      <x:c r="E9" s="151" t="str">
-        <x:v>本人Tokenのみ</x:v>
-      </x:c>
-      <x:c r="F9" s="151" t="str">
-        <x:v>認証・本人/共通条件をServiceで判定</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10">
-      <x:c r="A10" s="151" t="str">
-        <x:v>API-AUTH-003</x:v>
-      </x:c>
-      <x:c r="B10" s="151" t="str">
-        <x:v>Token更新</x:v>
-      </x:c>
-      <x:c r="C10" s="151" t="str">
-        <x:v>-（認証/本人共通）</x:v>
-      </x:c>
-      <x:c r="D10" s="151" t="str">
-        <x:v>Refresh Cookie</x:v>
-      </x:c>
-      <x:c r="E10" s="151" t="str">
-        <x:v>有効・未失効Token</x:v>
-      </x:c>
-      <x:c r="F10" s="151" t="str">
-        <x:v>認証・本人/共通条件をServiceで判定</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11">
-      <x:c r="A11" s="151" t="str">
-        <x:v>API-AUTH-004</x:v>
-      </x:c>
-      <x:c r="B11" s="151" t="str">
-        <x:v>現在ユーザー取得</x:v>
-      </x:c>
-      <x:c r="C11" s="151" t="str">
-        <x:v>-（認証/本人共通）</x:v>
-      </x:c>
-      <x:c r="D11" s="151" t="str">
-        <x:v>全員</x:v>
-      </x:c>
-      <x:c r="E11" s="151" t="str">
-        <x:v>本人</x:v>
-      </x:c>
-      <x:c r="F11" s="151" t="str">
-        <x:v>認証・本人/共通条件をServiceで判定</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12">
-      <x:c r="A12" s="151" t="str">
-        <x:v>API-AUTH-005</x:v>
-      </x:c>
-      <x:c r="B12" s="151" t="str">
-        <x:v>パスワード変更</x:v>
-      </x:c>
-      <x:c r="C12" s="151" t="str">
-        <x:v>-（認証/本人共通）</x:v>
-      </x:c>
-      <x:c r="D12" s="151" t="str">
-        <x:v>全員</x:v>
-      </x:c>
-      <x:c r="E12" s="151" t="str">
-        <x:v>本人</x:v>
-      </x:c>
-      <x:c r="F12" s="151" t="str">
-        <x:v>認証・本人/共通条件をServiceで判定</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="13">
-      <x:c r="A13" s="151" t="str">
-        <x:v>API-DASH-001</x:v>
-      </x:c>
-      <x:c r="B13" s="151" t="str">
-        <x:v>ホーム集計取得</x:v>
-      </x:c>
-      <x:c r="C13" s="151" t="str">
-        <x:v>PERM-DASH-READ</x:v>
-      </x:c>
-      <x:c r="D13" s="151" t="str">
-        <x:v>全員</x:v>
-      </x:c>
-      <x:c r="E13" s="151" t="str">
-        <x:v>ADMIN=全社, PM=担当PJ, EMP=本人・参加PJ</x:v>
-      </x:c>
-      <x:c r="F13" s="151" t="str">
-        <x:v>hasAuthority('PERM-DASH-READ') + Data範囲をServiceで再判定</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="14">
-      <x:c r="A14" s="151" t="str">
-        <x:v>API-MST-001</x:v>
-      </x:c>
-      <x:c r="B14" s="151" t="str">
-        <x:v>部門選択肢</x:v>
-      </x:c>
-      <x:c r="C14" s="151" t="str">
-        <x:v>-（認証/本人共通）</x:v>
-      </x:c>
-      <x:c r="D14" s="151" t="str">
-        <x:v>全員</x:v>
-      </x:c>
-      <x:c r="E14" s="151" t="str">
-        <x:v>有効部門</x:v>
-      </x:c>
-      <x:c r="F14" s="151" t="str">
-        <x:v>認証・本人/共通条件をServiceで判定</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="15">
-      <x:c r="A15" s="151" t="str">
-        <x:v>API-MST-002</x:v>
-      </x:c>
-      <x:c r="B15" s="151" t="str">
-        <x:v>社員選択肢</x:v>
-      </x:c>
-      <x:c r="C15" s="151" t="str">
-        <x:v>PERM-EMP-READ</x:v>
-      </x:c>
-      <x:c r="D15" s="151" t="str">
-        <x:v>管理者/PM</x:v>
-      </x:c>
-      <x:c r="E15" s="151" t="str">
-        <x:v>ADMIN=全社, PM=担当PJ候補</x:v>
-      </x:c>
-      <x:c r="F15" s="151" t="str">
-        <x:v>hasAuthority('PERM-EMP-READ') + Data範囲をServiceで再判定</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="16">
-      <x:c r="A16" s="151" t="str">
-        <x:v>API-MST-003</x:v>
-      </x:c>
-      <x:c r="B16" s="151" t="str">
-        <x:v>PJ選択肢</x:v>
-      </x:c>
-      <x:c r="C16" s="151" t="str">
-        <x:v>PERM-PRJ-READ</x:v>
-      </x:c>
-      <x:c r="D16" s="151" t="str">
-        <x:v>全員</x:v>
-      </x:c>
-      <x:c r="E16" s="151" t="str">
-        <x:v>権限範囲内PJ</x:v>
-      </x:c>
-      <x:c r="F16" s="151" t="str">
-        <x:v>hasAuthority('PERM-PRJ-READ') + Data範囲をServiceで再判定</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="17">
-      <x:c r="A17" s="151" t="str">
-        <x:v>API-MST-004</x:v>
-      </x:c>
-      <x:c r="B17" s="151" t="str">
-        <x:v>Role/権限選択肢</x:v>
-      </x:c>
-      <x:c r="C17" s="151" t="str">
-        <x:v>PERM-ROLE-ADMIN</x:v>
-      </x:c>
-      <x:c r="D17" s="151" t="str">
-        <x:v>管理者</x:v>
-      </x:c>
-      <x:c r="E17" s="151" t="str">
-        <x:v>管理者のみ</x:v>
-      </x:c>
-      <x:c r="F17" s="151" t="str">
-        <x:v>hasAuthority('PERM-ROLE-ADMIN') + Data範囲をServiceで再判定</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18">
-      <x:c r="A18" s="151" t="str">
-        <x:v>API-USR-001</x:v>
-      </x:c>
-      <x:c r="B18" s="151" t="str">
-        <x:v>ユーザー検索</x:v>
-      </x:c>
-      <x:c r="C18" s="151" t="str">
-        <x:v>PERM-USER-ADMIN</x:v>
-      </x:c>
-      <x:c r="D18" s="151" t="str">
-        <x:v>管理者</x:v>
-      </x:c>
-      <x:c r="E18" s="151" t="str">
-        <x:v>管理者のみ</x:v>
-      </x:c>
-      <x:c r="F18" s="151" t="str">
-        <x:v>hasAuthority('PERM-USER-ADMIN') + Data範囲をServiceで再判定</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19">
-      <x:c r="A19" s="151" t="str">
-        <x:v>API-USR-002</x:v>
-      </x:c>
-      <x:c r="B19" s="151" t="str">
-        <x:v>ユーザー詳細</x:v>
-      </x:c>
-      <x:c r="C19" s="151" t="str">
-        <x:v>PERM-USER-ADMIN</x:v>
-      </x:c>
-      <x:c r="D19" s="151" t="str">
-        <x:v>管理者</x:v>
-      </x:c>
-      <x:c r="E19" s="151" t="str">
-        <x:v>管理者のみ</x:v>
-      </x:c>
-      <x:c r="F19" s="151" t="str">
-        <x:v>hasAuthority('PERM-USER-ADMIN') + Data範囲をServiceで再判定</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="20">
-      <x:c r="A20" s="151" t="str">
-        <x:v>API-USR-003</x:v>
-      </x:c>
-      <x:c r="B20" s="151" t="str">
-        <x:v>ユーザー状態・Role更新</x:v>
-      </x:c>
-      <x:c r="C20" s="151" t="str">
-        <x:v>PERM-USER-ADMIN</x:v>
-      </x:c>
-      <x:c r="D20" s="151" t="str">
-        <x:v>管理者</x:v>
-      </x:c>
-      <x:c r="E20" s="151" t="str">
-        <x:v>管理者のみ; 自身のADMIN剥奪禁止</x:v>
-      </x:c>
-      <x:c r="F20" s="151" t="str">
-        <x:v>hasAuthority('PERM-USER-ADMIN') + Data範囲をServiceで再判定</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="21">
-      <x:c r="A21" s="151" t="str">
-        <x:v>API-USR-004</x:v>
-      </x:c>
-      <x:c r="B21" s="151" t="str">
-        <x:v>パスワードリセット</x:v>
-      </x:c>
-      <x:c r="C21" s="151" t="str">
-        <x:v>PERM-USER-ADMIN</x:v>
-      </x:c>
-      <x:c r="D21" s="151" t="str">
-        <x:v>管理者</x:v>
-      </x:c>
-      <x:c r="E21" s="151" t="str">
-        <x:v>管理者のみ; 有効User</x:v>
-      </x:c>
-      <x:c r="F21" s="151" t="str">
-        <x:v>hasAuthority('PERM-USER-ADMIN') + Data範囲をServiceで再判定</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="22">
-      <x:c r="A22" s="151" t="str">
-        <x:v>API-ROLE-001</x:v>
-      </x:c>
-      <x:c r="B22" s="151" t="str">
-        <x:v>Role一覧</x:v>
-      </x:c>
-      <x:c r="C22" s="151" t="str">
-        <x:v>PERM-ROLE-ADMIN</x:v>
-      </x:c>
-      <x:c r="D22" s="151" t="str">
-        <x:v>管理者</x:v>
-      </x:c>
-      <x:c r="E22" s="151" t="str">
-        <x:v>管理者のみ</x:v>
-      </x:c>
-      <x:c r="F22" s="151" t="str">
-        <x:v>hasAuthority('PERM-ROLE-ADMIN') + Data範囲をServiceで再判定</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="23">
-      <x:c r="A23" s="151" t="str">
-        <x:v>API-ROLE-002</x:v>
-      </x:c>
-      <x:c r="B23" s="151" t="str">
-        <x:v>Role詳細</x:v>
-      </x:c>
-      <x:c r="C23" s="151" t="str">
-        <x:v>PERM-ROLE-ADMIN</x:v>
-      </x:c>
-      <x:c r="D23" s="151" t="str">
-        <x:v>管理者</x:v>
-      </x:c>
-      <x:c r="E23" s="151" t="str">
-        <x:v>管理者のみ</x:v>
-      </x:c>
-      <x:c r="F23" s="151" t="str">
-        <x:v>hasAuthority('PERM-ROLE-ADMIN') + Data範囲をServiceで再判定</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="24">
-      <x:c r="A24" s="151" t="str">
-        <x:v>API-ROLE-003</x:v>
-      </x:c>
-      <x:c r="B24" s="151" t="str">
-        <x:v>Role登録</x:v>
-      </x:c>
-      <x:c r="C24" s="151" t="str">
-        <x:v>PERM-ROLE-ADMIN</x:v>
-      </x:c>
-      <x:c r="D24" s="151" t="str">
-        <x:v>管理者</x:v>
-      </x:c>
-      <x:c r="E24" s="151" t="str">
-        <x:v>管理者のみ</x:v>
-      </x:c>
-      <x:c r="F24" s="151" t="str">
-        <x:v>hasAuthority('PERM-ROLE-ADMIN') + Data範囲をServiceで再判定</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="25">
-      <x:c r="A25" s="151" t="str">
-        <x:v>API-ROLE-004</x:v>
-      </x:c>
-      <x:c r="B25" s="151" t="str">
-        <x:v>Role更新</x:v>
-      </x:c>
-      <x:c r="C25" s="151" t="str">
-        <x:v>PERM-ROLE-ADMIN</x:v>
-      </x:c>
-      <x:c r="D25" s="151" t="str">
-        <x:v>管理者</x:v>
-      </x:c>
-      <x:c r="E25" s="151" t="str">
-        <x:v>組込Role Code変更禁止</x:v>
-      </x:c>
-      <x:c r="F25" s="151" t="str">
-        <x:v>hasAuthority('PERM-ROLE-ADMIN') + Data範囲をServiceで再判定</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="26">
-      <x:c r="A26" s="151" t="str">
-        <x:v>API-ROLE-005</x:v>
-      </x:c>
-      <x:c r="B26" s="151" t="str">
-        <x:v>Role状態変更</x:v>
-      </x:c>
-      <x:c r="C26" s="151" t="str">
-        <x:v>PERM-ROLE-ADMIN</x:v>
-      </x:c>
-      <x:c r="D26" s="151" t="str">
-        <x:v>管理者</x:v>
-      </x:c>
-      <x:c r="E26" s="151" t="str">
-        <x:v>使用中Role停止時確認</x:v>
-      </x:c>
-      <x:c r="F26" s="151" t="str">
-        <x:v>hasAuthority('PERM-ROLE-ADMIN') + Data範囲をServiceで再判定</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="27">
-      <x:c r="A27" s="151" t="str">
-        <x:v>API-LOG-001</x:v>
-      </x:c>
-      <x:c r="B27" s="151" t="str">
-        <x:v>操作Log検索</x:v>
-      </x:c>
-      <x:c r="C27" s="151" t="str">
-        <x:v>PERM-LOG-READ</x:v>
-      </x:c>
-      <x:c r="D27" s="151" t="str">
-        <x:v>管理者</x:v>
-      </x:c>
-      <x:c r="E27" s="151" t="str">
-        <x:v>管理者のみ</x:v>
-      </x:c>
-      <x:c r="F27" s="151" t="str">
-        <x:v>hasAuthority('PERM-LOG-READ') + Data範囲をServiceで再判定</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="28">
-      <x:c r="A28" s="151" t="str">
-        <x:v>API-LOG-002</x:v>
-      </x:c>
-      <x:c r="B28" s="151" t="str">
-        <x:v>操作Log詳細</x:v>
-      </x:c>
-      <x:c r="C28" s="151" t="str">
-        <x:v>PERM-LOG-READ</x:v>
-      </x:c>
-      <x:c r="D28" s="151" t="str">
-        <x:v>管理者</x:v>
-      </x:c>
-      <x:c r="E28" s="151" t="str">
-        <x:v>管理者のみ</x:v>
-      </x:c>
-      <x:c r="F28" s="151" t="str">
-        <x:v>hasAuthority('PERM-LOG-READ') + Data範囲をServiceで再判定</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="30">
-      <x:c r="A30" s="155" t="str">
-        <x:v>ControllerのRole表示だけで認可しない。Service層でPermission Code、本人/PJ Member/担当PM等のData範囲、対象Dataの存在を再判定する。</x:v>
-      </x:c>
-      <x:c r="B30" s="155"/>
-      <x:c r="C30" s="155"/>
-      <x:c r="D30" s="155"/>
-      <x:c r="E30" s="155"/>
-      <x:c r="F30" s="155"/>
-    </x:row>
-    <x:row r="31">
-      <x:c r="A31" s="155"/>
-      <x:c r="B31" s="155"/>
-      <x:c r="C31" s="155"/>
-      <x:c r="D31" s="155"/>
-      <x:c r="E31" s="155"/>
-      <x:c r="F31" s="155"/>
-    </x:row>
-  </x:sheetData>
-  <x:mergeCells>
-    <x:mergeCell ref="A1:F2"/>
-    <x:mergeCell ref="A6:F6"/>
-    <x:mergeCell ref="A30:F31"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
@@ -1956,41 +1504,29 @@
       <x:c r="G2" s="172"/>
       <x:c r="H2" s="172"/>
     </x:row>
-    <x:row r="3">
-      <x:c r="A3" s="174" t="str">
-        <x:v>システム名</x:v>
-      </x:c>
-      <x:c r="B3" s="139" t="str">
-        <x:v>Company WorkHub</x:v>
-      </x:c>
-      <x:c r="C3" s="139"/>
-      <x:c r="D3" s="174" t="str">
-        <x:v>文書番号</x:v>
-      </x:c>
-      <x:c r="E3" s="139" t="str">
-        <x:v>DOCUMENT-REVISION</x:v>
-      </x:c>
-      <x:c r="F3" s="139"/>
-      <x:c r="G3" s="139"/>
-      <x:c r="H3" s="139"/>
-    </x:row>
-    <x:row r="4">
-      <x:c r="A4" s="174" t="str">
-        <x:v>版数</x:v>
-      </x:c>
-      <x:c r="B4" s="139" t="str">
-        <x:v>Ver.1.8</x:v>
-      </x:c>
-      <x:c r="C4" s="139"/>
-      <x:c r="D4" s="174" t="str">
-        <x:v>改訂日</x:v>
-      </x:c>
-      <x:c r="E4" s="139" t="str">
-        <x:v>2026-08-12</x:v>
-      </x:c>
-      <x:c r="F4" s="139"/>
-      <x:c r="G4" s="139"/>
-      <x:c r="H4" s="139"/>
+    <x:row r="3" ht="24" customHeight="1">
+      <x:c r="A3" s="246" t="str">
+        <x:v>システム名：Company WorkHub</x:v>
+      </x:c>
+      <x:c r="B3" s="63"/>
+      <x:c r="C3" s="63"/>
+      <x:c r="D3" s="246"/>
+      <x:c r="E3" s="63"/>
+      <x:c r="F3" s="63"/>
+      <x:c r="G3" s="63"/>
+      <x:c r="H3" s="63"/>
+    </x:row>
+    <x:row r="4" ht="24" customHeight="1">
+      <x:c r="A4" s="246" t="str">
+        <x:v>版数：Ver.2.5    改訂日：2026-09-24    Baseline：BL-2026-09-24</x:v>
+      </x:c>
+      <x:c r="B4" s="63"/>
+      <x:c r="C4" s="63"/>
+      <x:c r="D4" s="246"/>
+      <x:c r="E4" s="63"/>
+      <x:c r="F4" s="63"/>
+      <x:c r="G4" s="63"/>
+      <x:c r="H4" s="63"/>
     </x:row>
     <x:row r="5">
       <x:c r="A5"/>
@@ -2022,7 +1558,7 @@
         <x:v>改訂日</x:v>
       </x:c>
       <x:c r="C7" s="181" t="str">
-        <x:v>2026-08-12</x:v>
+        <x:v>改訂内容</x:v>
       </x:c>
       <x:c r="D7" s="181" t="str">
         <x:v>作成者</x:v>
@@ -2060,7 +1596,7 @@
         <x:v>-</x:v>
       </x:c>
       <x:c r="G8" s="67" t="str">
-        <x:v>作成済</x:v>
+        <x:v>作成中</x:v>
       </x:c>
       <x:c r="H8" s="67" t="str">
         <x:v>基本設計初版</x:v>
@@ -2086,7 +1622,7 @@
         <x:v>-</x:v>
       </x:c>
       <x:c r="G9" s="67" t="str">
-        <x:v>レビュー待ち</x:v>
+        <x:v>Review中</x:v>
       </x:c>
       <x:c r="H9" s="67" t="str">
         <x:v>Leader Review後Baseline化</x:v>
@@ -2112,7 +1648,7 @@
         <x:v>-</x:v>
       </x:c>
       <x:c r="G10" s="67" t="str">
-        <x:v>レビュー待ち</x:v>
+        <x:v>Review中</x:v>
       </x:c>
       <x:c r="H10" s="67" t="str">
         <x:v>Review指摘対応</x:v>
@@ -2138,7 +1674,7 @@
         <x:v>-</x:v>
       </x:c>
       <x:c r="G11" s="67" t="str">
-        <x:v>レビュー待ち</x:v>
+        <x:v>Review中</x:v>
       </x:c>
       <x:c r="H11" s="67" t="str">
         <x:v>再監査指摘対応</x:v>
@@ -2164,7 +1700,7 @@
         <x:v>-</x:v>
       </x:c>
       <x:c r="G12" s="67" t="str">
-        <x:v>レビュー待ち</x:v>
+        <x:v>Review中</x:v>
       </x:c>
       <x:c r="H12" s="67" t="str">
         <x:v>再監査第2回指摘対応</x:v>
@@ -2189,8 +1725,8 @@
       <x:c r="F13" t="str">
         <x:v>-</x:v>
       </x:c>
-      <x:c r="G13" t="str">
-        <x:v>レビュー待ち</x:v>
+      <x:c r="G13" s="203" t="str">
+        <x:v>Review中</x:v>
       </x:c>
       <x:c r="H13" t="str">
         <x:v>再監査残項対応</x:v>
@@ -2215,8 +1751,8 @@
       <x:c r="F14" t="str">
         <x:v>-</x:v>
       </x:c>
-      <x:c r="G14" t="str">
-        <x:v>レビュー待ち</x:v>
+      <x:c r="G14" s="203" t="str">
+        <x:v>Review中</x:v>
       </x:c>
       <x:c r="H14" t="str">
         <x:v>再Review指摘対応</x:v>
@@ -2241,25 +1777,153 @@
       <x:c r="F15" t="str">
         <x:v>-</x:v>
       </x:c>
-      <x:c r="G15" t="str">
-        <x:v>レビュー待ち</x:v>
+      <x:c r="G15" s="203" t="str">
+        <x:v>Review中</x:v>
       </x:c>
       <x:c r="H15" t="str">
         <x:v>最大10回の反復監査対応</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16">
+      <x:c r="A16" t="str">
+        <x:v>1.9</x:v>
+      </x:c>
+      <x:c r="B16" t="str">
+        <x:v>2026-08-17</x:v>
+      </x:c>
+      <x:c r="C16" t="str">
+        <x:v>Dashboard集計条件・Role範囲・Response通知項目を明確化</x:v>
+      </x:c>
+      <x:c r="D16" t="str">
+        <x:v>Project Leader</x:v>
+      </x:c>
+      <x:c r="E16" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="F16" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="G16" s="203" t="str">
+        <x:v>Review中</x:v>
+      </x:c>
+      <x:c r="H16" t="str">
+        <x:v>04再Review影響反映</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17">
+      <x:c r="A17" t="str">
+        <x:v>2.0</x:v>
+      </x:c>
+      <x:c r="B17" t="str">
+        <x:v>2026-09-09</x:v>
+      </x:c>
+      <x:c r="C17" t="str">
+        <x:v>七項目Review指摘対応：画面・API・DB項目、論理削除、認証限流、日報関連Task、Baseline判定を整合</x:v>
+      </x:c>
+      <x:c r="D17" t="str">
+        <x:v>Project Leader</x:v>
+      </x:c>
+      <x:c r="E17" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="F17" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="G17" t="str">
+        <x:v>レビュー済</x:v>
+      </x:c>
+      <x:c r="H17" t="str">
+        <x:v>Leader最終承認待ち</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" ht="110" customHeight="1">
+      <x:c r="A18" s="241" t="str">
+        <x:v>Ver.2.3</x:v>
+      </x:c>
+      <x:c r="B18" s="241" t="str">
+        <x:v>2026-09-18</x:v>
+      </x:c>
+      <x:c r="C18" s="241" t="str">
+        <x:v>内容・関連Reviewの既確定仕様を整合。業務未決事項は承認待ちとして管理。</x:v>
+      </x:c>
+      <x:c r="D18" s="241" t="str">
+        <x:v>Project Leader</x:v>
+      </x:c>
+      <x:c r="E18" s="241" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="F18" s="241" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="G18" s="241" t="str">
+        <x:v>Review中</x:v>
+      </x:c>
+      <x:c r="H18" s="241" t="str">
+        <x:v>2026-09-18指摘対応。正式承認を示すものではない。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" ht="40" customHeight="1">
+      <x:c r="A19" s="241" t="str">
+        <x:v>Ver.2.4</x:v>
+      </x:c>
+      <x:c r="B19" s="241" t="str">
+        <x:v>2026-09-18</x:v>
+      </x:c>
+      <x:c r="C19" s="241" t="str">
+        <x:v>待確認12項目の方針選定、業務/API/DB/画面/運用を連動修正。章立て維持。</x:v>
+      </x:c>
+      <x:c r="D19" s="241" t="str">
+        <x:v>Project Leader</x:v>
+      </x:c>
+      <x:c r="E19" s="241" t="str">
+        <x:v>未実施</x:v>
+      </x:c>
+      <x:c r="F19" s="241" t="str">
+        <x:v>未承認</x:v>
+      </x:c>
+      <x:c r="G19" s="241" t="str">
+        <x:v>Review中</x:v>
+      </x:c>
+      <x:c r="H19" s="241" t="str">
+        <x:v>一般社内管理Systemの範囲。旧版はBackup保管。</x:v>
+      </x:c>
+      <x:c r="I19" s="241"/>
+      <x:c r="J19" s="241"/>
+      <x:c r="K19" s="241"/>
+      <x:c r="L19" s="241"/>
+    </x:row>
+    <x:row r="20" ht="100" customHeight="1">
+      <x:c r="A20" s="245" t="str">
+        <x:v>Ver.2.5</x:v>
+      </x:c>
+      <x:c r="B20" s="245" t="str">
+        <x:v>2026-09-24</x:v>
+      </x:c>
+      <x:c r="C20" s="245" t="str">
+        <x:v>共通規則・正本参照・構成・文書管理を統合修正。Baseline承認前の最終整合修正。</x:v>
+      </x:c>
+      <x:c r="D20" s="245" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="E20" s="245" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="F20" s="245" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="G20" s="245" t="str">
+        <x:v>修正済</x:v>
+      </x:c>
+      <x:c r="H20" s="245" t="str">
+        <x:v>BL-2026-09-24。責任者・Review者・承認者はProject Leaderが記入。</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
     <x:mergeCell ref="A1:H2"/>
-    <x:mergeCell ref="A3:B3"/>
-    <x:mergeCell ref="C3:D3"/>
-    <x:mergeCell ref="E3:F3"/>
-    <x:mergeCell ref="G3:H3"/>
-    <x:mergeCell ref="A4:B4"/>
-    <x:mergeCell ref="C4:D4"/>
-    <x:mergeCell ref="E4:F4"/>
-    <x:mergeCell ref="G4:H4"/>
     <x:mergeCell ref="A6:H6"/>
+    <x:mergeCell ref="A3:H3"/>
+    <x:mergeCell ref="A4:H4"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
@@ -2308,36 +1972,28 @@
       <x:c r="A3" s="62" t="str">
         <x:v>システム名</x:v>
       </x:c>
-      <x:c r="B3" s="63" t="str">
-        <x:v>Company WorkHub</x:v>
-      </x:c>
+      <x:c r="B3" s="63" t="str"/>
       <x:c r="C3" s="63"/>
       <x:c r="D3" s="63"/>
-      <x:c r="E3" s="62" t="str">
-        <x:v>文書番号</x:v>
-      </x:c>
-      <x:c r="F3" s="63" t="str">
-        <x:v>CW-BD-API-CMN-LIST</x:v>
-      </x:c>
+      <x:c r="E3" s="246" t="str">
+        <x:v>章ID</x:v>
+      </x:c>
+      <x:c r="F3" s="63" t="str"/>
       <x:c r="G3" s="63"/>
       <x:c r="H3" s="63"/>
       <x:c r="I3" s="63"/>
     </x:row>
     <x:row r="4">
-      <x:c r="A4" s="62" t="str">
-        <x:v>版数</x:v>
-      </x:c>
-      <x:c r="B4" s="63" t="str">
-        <x:v>Ver.1.8</x:v>
-      </x:c>
+      <x:c r="A4" s="246" t="str">
+        <x:v>版数：Ver.2.5</x:v>
+      </x:c>
+      <x:c r="B4" s="63"/>
       <x:c r="C4" s="63"/>
       <x:c r="D4" s="63"/>
-      <x:c r="E4" s="62" t="str">
-        <x:v>改訂日</x:v>
-      </x:c>
-      <x:c r="F4" s="63" t="str">
-        <x:v>2026-08-12</x:v>
-      </x:c>
+      <x:c r="E4" s="246" t="str">
+        <x:v>改訂日：2026-09-24</x:v>
+      </x:c>
+      <x:c r="F4" s="63"/>
       <x:c r="G4" s="63"/>
       <x:c r="H4" s="63"/>
       <x:c r="I4" s="63"/>
@@ -2395,7 +2051,7 @@
         <x:v>Error Code</x:v>
       </x:c>
     </x:row>
-    <x:row r="8" ht="30" customHeight="1">
+    <x:row r="8" ht="39" customHeight="1">
       <x:c r="A8" s="67" t="str">
         <x:v>API-AUTH-001</x:v>
       </x:c>
@@ -2409,22 +2065,22 @@
         <x:v>ログイン</x:v>
       </x:c>
       <x:c r="E8" s="67" t="str">
-        <x:v>不要</x:v>
+        <x:v>02／13_API権限対応：API-AUTH-001</x:v>
       </x:c>
       <x:c r="F8" s="67" t="str">
-        <x:v>body: username String(1..50), password String(1..100)</x:v>
+        <x:v>23_API項目定義：API-AUTH-001 Request</x:v>
       </x:c>
       <x:c r="G8" s="67" t="str">
-        <x:v>accessToken, expiresIn, user{id,username,name,roles,permissions}</x:v>
+        <x:v>23_API項目定義：API-AUTH-001 Response（正本）</x:v>
       </x:c>
       <x:c r="H8" s="67" t="str">
         <x:v>SCR-001</x:v>
       </x:c>
       <x:c r="I8" s="67" t="str">
-        <x:v>AUTH-4001, AUTH-4004, AUTH-4005,COMMON-5000</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" ht="30" customHeight="1">
+        <x:v>22_API処理・権限!F8／21_エラーコード</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" ht="39" customHeight="1">
       <x:c r="A9" s="67" t="str">
         <x:v>API-AUTH-002</x:v>
       </x:c>
@@ -2438,22 +2094,22 @@
         <x:v>ログアウト</x:v>
       </x:c>
       <x:c r="E9" s="67" t="str">
-        <x:v>全員</x:v>
+        <x:v>02／13_API権限対応：API-AUTH-002</x:v>
       </x:c>
       <x:c r="F9" s="67" t="str">
-        <x:v>header: Authorization; cookie: refreshToken</x:v>
+        <x:v>23_API項目定義：API-AUTH-002 Request</x:v>
       </x:c>
       <x:c r="G9" s="67" t="str">
-        <x:v>204 No Content</x:v>
+        <x:v>23_API項目定義：API-AUTH-002 Response（正本）</x:v>
       </x:c>
       <x:c r="H9" s="67" t="str">
         <x:v>共通Header</x:v>
       </x:c>
       <x:c r="I9" s="67" t="str">
-        <x:v>AUTH-4002,COMMON-5000</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10" ht="30" customHeight="1">
+        <x:v>22_API処理・権限!F9／21_エラーコード</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" ht="39" customHeight="1">
       <x:c r="A10" s="67" t="str">
         <x:v>API-AUTH-003</x:v>
       </x:c>
@@ -2467,22 +2123,22 @@
         <x:v>Token更新</x:v>
       </x:c>
       <x:c r="E10" s="67" t="str">
-        <x:v>Refresh Cookie</x:v>
+        <x:v>02／13_API権限対応：API-AUTH-003</x:v>
       </x:c>
       <x:c r="F10" s="67" t="str">
-        <x:v>cookie: refreshToken HttpOnly</x:v>
+        <x:v>23_API項目定義：API-AUTH-003 Request</x:v>
       </x:c>
       <x:c r="G10" s="67" t="str">
-        <x:v>accessToken, expiresIn</x:v>
+        <x:v>23_API項目定義：API-AUTH-003 Response（正本）</x:v>
       </x:c>
       <x:c r="H10" s="67" t="str">
         <x:v>共通Interceptor</x:v>
       </x:c>
       <x:c r="I10" s="67" t="str">
-        <x:v>AUTH-4002, AUTH-4003</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" ht="30" customHeight="1">
+        <x:v>22_API処理・権限!F10／21_エラーコード</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" ht="39" customHeight="1">
       <x:c r="A11" s="67" t="str">
         <x:v>API-AUTH-004</x:v>
       </x:c>
@@ -2496,22 +2152,22 @@
         <x:v>現在ユーザー取得</x:v>
       </x:c>
       <x:c r="E11" s="67" t="str">
-        <x:v>全員</x:v>
+        <x:v>02／13_API権限対応：API-AUTH-004</x:v>
       </x:c>
       <x:c r="F11" s="67" t="str">
-        <x:v>なし</x:v>
+        <x:v>23_API項目定義：API-AUTH-004 Request</x:v>
       </x:c>
       <x:c r="G11" s="67" t="str">
-        <x:v>user{id,employeeId,name,roles,permissions,menus}</x:v>
+        <x:v>23_API項目定義：API-AUTH-004 Response（正本）</x:v>
       </x:c>
       <x:c r="H11" s="67" t="str">
         <x:v>共通Layout</x:v>
       </x:c>
       <x:c r="I11" s="67" t="str">
-        <x:v>AUTH-4002, AUTH-4005</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12" ht="30" customHeight="1">
+        <x:v>22_API処理・権限!F11／21_エラーコード</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" ht="39" customHeight="1">
       <x:c r="A12" s="67" t="str">
         <x:v>API-AUTH-005</x:v>
       </x:c>
@@ -2525,22 +2181,22 @@
         <x:v>パスワード変更</x:v>
       </x:c>
       <x:c r="E12" s="67" t="str">
-        <x:v>全員</x:v>
+        <x:v>02／13_API権限対応：API-AUTH-005</x:v>
       </x:c>
       <x:c r="F12" s="67" t="str">
-        <x:v>body: currentPassword String, newPassword String(8..64), confirmPassword String</x:v>
+        <x:v>23_API項目定義：API-AUTH-005 Request</x:v>
       </x:c>
       <x:c r="G12" s="67" t="str">
-        <x:v>204 No Content</x:v>
+        <x:v>23_API項目定義：API-AUTH-005 Response（正本）</x:v>
       </x:c>
       <x:c r="H12" s="67" t="str">
         <x:v>SCR-026</x:v>
       </x:c>
       <x:c r="I12" s="67" t="str">
-        <x:v>AUTH-4001, AUTH-4002,COMMON-4000</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="13" ht="30" customHeight="1">
+        <x:v>22_API処理・権限!F12／21_エラーコード</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" ht="39" customHeight="1">
       <x:c r="A13" s="67" t="str">
         <x:v>API-DASH-001</x:v>
       </x:c>
@@ -2554,22 +2210,22 @@
         <x:v>ホーム集計取得</x:v>
       </x:c>
       <x:c r="E13" s="67" t="str">
-        <x:v>全員</x:v>
+        <x:v>02／13_API権限対応：API-DASH-001</x:v>
       </x:c>
       <x:c r="F13" s="67" t="str">
-        <x:v>query: periodFrom Date, periodTo Date</x:v>
+        <x:v>23_API項目定義：API-DASH-001 Request</x:v>
       </x:c>
       <x:c r="G13" s="67" t="str">
-        <x:v>projectCount,taskStatusCounts,dueSoonCount,reportSubmittedCount,recentNotifications[]</x:v>
+        <x:v>23_API項目定義：API-DASH-001 Response（正本）</x:v>
       </x:c>
       <x:c r="H13" s="67" t="str">
         <x:v>SCR-002</x:v>
       </x:c>
       <x:c r="I13" s="67" t="str">
-        <x:v>COMMON-4000, COMMON-5000</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="14" ht="30" customHeight="1">
+        <x:v>22_API処理・権限!F13／21_エラーコード</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" ht="39" customHeight="1">
       <x:c r="A14" s="67" t="str">
         <x:v>API-MST-001</x:v>
       </x:c>
@@ -2583,22 +2239,22 @@
         <x:v>部門選択肢</x:v>
       </x:c>
       <x:c r="E14" s="67" t="str">
-        <x:v>全員</x:v>
+        <x:v>02／13_API権限対応：API-MST-001</x:v>
       </x:c>
       <x:c r="F14" s="67" t="str">
-        <x:v>query: activeOnly Boolean=true</x:v>
+        <x:v>23_API項目定義：API-MST-001 Request</x:v>
       </x:c>
       <x:c r="G14" s="67" t="str">
-        <x:v>departments[{id,code,name,parentId}]</x:v>
+        <x:v>23_API項目定義：API-MST-001 Response（正本）</x:v>
       </x:c>
       <x:c r="H14" s="67" t="str">
         <x:v>SCR-003, SCR-004, SCR-007, SCR-021</x:v>
       </x:c>
       <x:c r="I14" s="67" t="str">
-        <x:v>COMMON-5000</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="15" ht="30" customHeight="1">
+        <x:v>22_API処理・権限!F14／21_エラーコード</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" ht="39" customHeight="1">
       <x:c r="A15" s="67" t="str">
         <x:v>API-MST-002</x:v>
       </x:c>
@@ -2612,22 +2268,22 @@
         <x:v>社員選択肢</x:v>
       </x:c>
       <x:c r="E15" s="67" t="str">
-        <x:v>管理者/PM</x:v>
+        <x:v>02／13_API権限対応：API-MST-002</x:v>
       </x:c>
       <x:c r="F15" s="67" t="str">
-        <x:v>query: projectId Long?, keyword String?, activeOnly Boolean=true</x:v>
+        <x:v>23_API項目定義：API-MST-002 Request</x:v>
       </x:c>
       <x:c r="G15" s="67" t="str">
-        <x:v>employees[{id,code,name,departmentId}]</x:v>
+        <x:v>23_API項目定義：API-MST-002 Response（正本）</x:v>
       </x:c>
       <x:c r="H15" s="67" t="str">
         <x:v>SCR-007, SCR-009, SCR-012, SCR-013, SCR-015, SCR-021</x:v>
       </x:c>
       <x:c r="I15" s="67" t="str">
-        <x:v>AUTH-4006</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="16" ht="30" customHeight="1">
+        <x:v>22_API処理・権限!F15／21_エラーコード</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" ht="39" customHeight="1">
       <x:c r="A16" s="67" t="str">
         <x:v>API-MST-003</x:v>
       </x:c>
@@ -2641,22 +2297,22 @@
         <x:v>PJ選択肢</x:v>
       </x:c>
       <x:c r="E16" s="67" t="str">
-        <x:v>全員</x:v>
+        <x:v>02／13_API権限対応：API-MST-003</x:v>
       </x:c>
       <x:c r="F16" s="67" t="str">
-        <x:v>query: activeOnly Boolean=true</x:v>
+        <x:v>23_API項目定義：API-MST-003 Request</x:v>
       </x:c>
       <x:c r="G16" s="67" t="str">
-        <x:v>projects[{id,code,name,role}]</x:v>
+        <x:v>23_API項目定義：API-MST-003 Response（正本）</x:v>
       </x:c>
       <x:c r="H16" s="67" t="str">
         <x:v>SCR-013, SCR-015, SCR-018, SCR-019, SCR-020, SCR-021</x:v>
       </x:c>
       <x:c r="I16" s="67" t="str">
-        <x:v>AUTH-4006</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="17" ht="30" customHeight="1">
+        <x:v>22_API処理・権限!F16／21_エラーコード</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" ht="39" customHeight="1">
       <x:c r="A17" s="67" t="str">
         <x:v>API-MST-004</x:v>
       </x:c>
@@ -2670,22 +2326,22 @@
         <x:v>Role/権限選択肢</x:v>
       </x:c>
       <x:c r="E17" s="67" t="str">
-        <x:v>管理者</x:v>
+        <x:v>02／13_API権限対応：API-MST-004</x:v>
       </x:c>
       <x:c r="F17" s="67" t="str">
-        <x:v>なし</x:v>
+        <x:v>23_API項目定義：API-MST-004 Request</x:v>
       </x:c>
       <x:c r="G17" s="67" t="str">
-        <x:v>roles[],permissions[]</x:v>
+        <x:v>23_API項目定義：API-MST-004 Response（正本）</x:v>
       </x:c>
       <x:c r="H17" s="67" t="str">
         <x:v>SCR-004, SCR-023, SCR-024</x:v>
       </x:c>
       <x:c r="I17" s="67" t="str">
-        <x:v>AUTH-4006</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" ht="30" customHeight="1">
+        <x:v>22_API処理・権限!F17／21_エラーコード</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" ht="39" customHeight="1">
       <x:c r="A18" s="67" t="str">
         <x:v>API-USR-001</x:v>
       </x:c>
@@ -2699,22 +2355,22 @@
         <x:v>ユーザー検索</x:v>
       </x:c>
       <x:c r="E18" s="67" t="str">
-        <x:v>管理者</x:v>
+        <x:v>02／13_API権限対応：API-USR-001</x:v>
       </x:c>
       <x:c r="F18" s="67" t="str">
-        <x:v>query: username,name,status,locked,page,size,sort</x:v>
+        <x:v>23_API項目定義：API-USR-001 Request</x:v>
       </x:c>
       <x:c r="G18" s="67" t="str">
-        <x:v>Page&lt;UserSummary&gt;</x:v>
+        <x:v>23_API項目定義：API-USR-001 Response（正本）</x:v>
       </x:c>
       <x:c r="H18" s="67" t="str">
         <x:v>SCR-023</x:v>
       </x:c>
       <x:c r="I18" s="67" t="str">
-        <x:v>COMMON-4000</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" ht="30" customHeight="1">
+        <x:v>22_API処理・権限!F18／21_エラーコード</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" ht="39" customHeight="1">
       <x:c r="A19" s="67" t="str">
         <x:v>API-USR-002</x:v>
       </x:c>
@@ -2728,22 +2384,22 @@
         <x:v>ユーザー詳細</x:v>
       </x:c>
       <x:c r="E19" s="67" t="str">
-        <x:v>管理者</x:v>
+        <x:v>02／13_API権限対応：API-USR-002</x:v>
       </x:c>
       <x:c r="F19" s="67" t="str">
-        <x:v>path: id Long</x:v>
+        <x:v>23_API項目定義：API-USR-002 Request</x:v>
       </x:c>
       <x:c r="G19" s="67" t="str">
-        <x:v>id,username,employee,status,lockedUntil,roles,version</x:v>
+        <x:v>23_API項目定義：API-USR-002 Response（正本）</x:v>
       </x:c>
       <x:c r="H19" s="67" t="str">
         <x:v>SCR-023</x:v>
       </x:c>
       <x:c r="I19" s="67" t="str">
-        <x:v>COMMON-4040</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="20" ht="30" customHeight="1">
+        <x:v>22_API処理・権限!F19／21_エラーコード</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" ht="39" customHeight="1">
       <x:c r="A20" s="67" t="str">
         <x:v>API-USR-003</x:v>
       </x:c>
@@ -2757,22 +2413,22 @@
         <x:v>ユーザー状態・Role更新</x:v>
       </x:c>
       <x:c r="E20" s="67" t="str">
-        <x:v>管理者</x:v>
+        <x:v>02／13_API権限対応：API-USR-003</x:v>
       </x:c>
       <x:c r="F20" s="67" t="str">
-        <x:v>path: id; body: enabled Boolean, roleIds Long[], version Integer</x:v>
+        <x:v>23_API項目定義：API-USR-003 Request</x:v>
       </x:c>
       <x:c r="G20" s="67" t="str">
-        <x:v>id,enabled,roles,version</x:v>
+        <x:v>23_API項目定義：API-USR-003 Response（正本）</x:v>
       </x:c>
       <x:c r="H20" s="67" t="str">
         <x:v>SCR-023</x:v>
       </x:c>
       <x:c r="I20" s="67" t="str">
-        <x:v>COMMON-4000, COMMON-4040, COMMON-4090</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="21" ht="30" customHeight="1">
+        <x:v>22_API処理・権限!F20／21_エラーコード</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" ht="39" customHeight="1">
       <x:c r="A21" s="67" t="str">
         <x:v>API-USR-004</x:v>
       </x:c>
@@ -2786,22 +2442,22 @@
         <x:v>パスワードリセット</x:v>
       </x:c>
       <x:c r="E21" s="67" t="str">
-        <x:v>管理者</x:v>
+        <x:v>02／13_API権限対応：API-USR-004</x:v>
       </x:c>
       <x:c r="F21" s="67" t="str">
-        <x:v>path: id; header: X-Idempotency-Key</x:v>
+        <x:v>23_API項目定義：API-USR-004 Request</x:v>
       </x:c>
       <x:c r="G21" s="67" t="str">
-        <x:v>temporaryPassword（一回表示）</x:v>
+        <x:v>23_API項目定義：API-USR-004 Response（正本）</x:v>
       </x:c>
       <x:c r="H21" s="67" t="str">
         <x:v>SCR-023</x:v>
       </x:c>
       <x:c r="I21" s="67" t="str">
-        <x:v>COMMON-4040, COMMON-4090</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="22" ht="30" customHeight="1">
+        <x:v>22_API処理・権限!F21／21_エラーコード</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" ht="39" customHeight="1">
       <x:c r="A22" s="67" t="str">
         <x:v>API-ROLE-001</x:v>
       </x:c>
@@ -2815,22 +2471,22 @@
         <x:v>Role一覧</x:v>
       </x:c>
       <x:c r="E22" s="67" t="str">
-        <x:v>管理者</x:v>
+        <x:v>02／13_API権限対応：API-ROLE-001</x:v>
       </x:c>
       <x:c r="F22" s="67" t="str">
-        <x:v>query: status,page,size</x:v>
+        <x:v>23_API項目定義：API-ROLE-001 Request</x:v>
       </x:c>
       <x:c r="G22" s="67" t="str">
-        <x:v>Page&lt;RoleSummary&gt;</x:v>
+        <x:v>23_API項目定義：API-ROLE-001 Response（正本）</x:v>
       </x:c>
       <x:c r="H22" s="67" t="str">
         <x:v>SCR-024</x:v>
       </x:c>
       <x:c r="I22" s="67" t="str">
-        <x:v>AUTH-4006</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="23" ht="30" customHeight="1">
+        <x:v>22_API処理・権限!F22／21_エラーコード</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23" ht="39" customHeight="1">
       <x:c r="A23" s="67" t="str">
         <x:v>API-ROLE-002</x:v>
       </x:c>
@@ -2844,22 +2500,22 @@
         <x:v>Role詳細</x:v>
       </x:c>
       <x:c r="E23" s="67" t="str">
-        <x:v>管理者</x:v>
+        <x:v>02／13_API権限対応：API-ROLE-002</x:v>
       </x:c>
       <x:c r="F23" s="67" t="str">
-        <x:v>path: id Long</x:v>
+        <x:v>23_API項目定義：API-ROLE-002 Request</x:v>
       </x:c>
       <x:c r="G23" s="67" t="str">
-        <x:v>id,roleCode,roleName,description,status,permissionIds,version</x:v>
+        <x:v>23_API項目定義：API-ROLE-002 Response（正本）</x:v>
       </x:c>
       <x:c r="H23" s="67" t="str">
         <x:v>SCR-024</x:v>
       </x:c>
       <x:c r="I23" s="67" t="str">
-        <x:v>COMMON-4040</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="24" ht="30" customHeight="1">
+        <x:v>22_API処理・権限!F23／21_エラーコード</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24" ht="39" customHeight="1">
       <x:c r="A24" s="67" t="str">
         <x:v>API-ROLE-003</x:v>
       </x:c>
@@ -2873,22 +2529,22 @@
         <x:v>Role登録</x:v>
       </x:c>
       <x:c r="E24" s="67" t="str">
-        <x:v>管理者</x:v>
+        <x:v>02／13_API権限対応：API-ROLE-003</x:v>
       </x:c>
       <x:c r="F24" s="67" t="str">
-        <x:v>body: roleCode String(1..50),roleName String(1..100),description String(0..500),permissionIds[]; header: X-Idempotency-Key</x:v>
+        <x:v>23_API項目定義：API-ROLE-003 Request</x:v>
       </x:c>
       <x:c r="G24" s="67" t="str">
-        <x:v>id,roleCode,version</x:v>
+        <x:v>23_API項目定義：API-ROLE-003 Response（正本）</x:v>
       </x:c>
       <x:c r="H24" s="67" t="str">
         <x:v>SCR-024</x:v>
       </x:c>
       <x:c r="I24" s="67" t="str">
-        <x:v>COMMON-4000, COMMON-4090</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="25" ht="30" customHeight="1">
+        <x:v>22_API処理・権限!F24／21_エラーコード</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25" ht="39" customHeight="1">
       <x:c r="A25" s="67" t="str">
         <x:v>API-ROLE-004</x:v>
       </x:c>
@@ -2902,22 +2558,22 @@
         <x:v>Role更新</x:v>
       </x:c>
       <x:c r="E25" s="67" t="str">
-        <x:v>管理者</x:v>
+        <x:v>02／13_API権限対応：API-ROLE-004</x:v>
       </x:c>
       <x:c r="F25" s="67" t="str">
-        <x:v>path: id; body: roleName,description,permissionIds[],version</x:v>
+        <x:v>23_API項目定義：API-ROLE-004 Request</x:v>
       </x:c>
       <x:c r="G25" s="67" t="str">
-        <x:v>id,status,permissionIds,version</x:v>
+        <x:v>23_API項目定義：API-ROLE-004 Response（正本）</x:v>
       </x:c>
       <x:c r="H25" s="67" t="str">
         <x:v>SCR-024</x:v>
       </x:c>
       <x:c r="I25" s="67" t="str">
-        <x:v>COMMON-4000, COMMON-4040, COMMON-4090</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="26" ht="30" customHeight="1">
+        <x:v>22_API処理・権限!F25／21_エラーコード</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26" ht="39" customHeight="1">
       <x:c r="A26" s="67" t="str">
         <x:v>API-ROLE-005</x:v>
       </x:c>
@@ -2931,22 +2587,22 @@
         <x:v>Role状態変更</x:v>
       </x:c>
       <x:c r="E26" s="67" t="str">
-        <x:v>管理者</x:v>
+        <x:v>02／13_API権限対応：API-ROLE-005</x:v>
       </x:c>
       <x:c r="F26" s="67" t="str">
-        <x:v>path: id; body: status,version</x:v>
+        <x:v>23_API項目定義：API-ROLE-005 Request</x:v>
       </x:c>
       <x:c r="G26" s="67" t="str">
-        <x:v>id,status,version</x:v>
+        <x:v>23_API項目定義：API-ROLE-005 Response（正本）</x:v>
       </x:c>
       <x:c r="H26" s="67" t="str">
         <x:v>SCR-024</x:v>
       </x:c>
       <x:c r="I26" s="67" t="str">
-        <x:v>COMMON-4040, COMMON-4090</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="27" ht="30" customHeight="1">
+        <x:v>22_API処理・権限!F26／21_エラーコード</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27" ht="39" customHeight="1">
       <x:c r="A27" s="67" t="str">
         <x:v>API-LOG-001</x:v>
       </x:c>
@@ -2960,22 +2616,22 @@
         <x:v>操作Log検索</x:v>
       </x:c>
       <x:c r="E27" s="67" t="str">
-        <x:v>管理者</x:v>
+        <x:v>02／13_API権限対応：API-LOG-001</x:v>
       </x:c>
       <x:c r="F27" s="67" t="str">
-        <x:v>query: from,to,userId,module,action,result,traceId,page,size,sort</x:v>
+        <x:v>23_API項目定義：API-LOG-001 Request</x:v>
       </x:c>
       <x:c r="G27" s="67" t="str">
-        <x:v>Page&lt;OperationLogSummary&gt;</x:v>
+        <x:v>23_API項目定義：API-LOG-001 Response（正本）</x:v>
       </x:c>
       <x:c r="H27" s="67" t="str">
         <x:v>SCR-025</x:v>
       </x:c>
       <x:c r="I27" s="67" t="str">
-        <x:v>COMMON-4000</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="28" ht="30" customHeight="1">
+        <x:v>22_API処理・権限!F27／21_エラーコード</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28" ht="39" customHeight="1">
       <x:c r="A28" s="67" t="str">
         <x:v>API-LOG-002</x:v>
       </x:c>
@@ -2989,19 +2645,19 @@
         <x:v>操作Log詳細</x:v>
       </x:c>
       <x:c r="E28" s="67" t="str">
-        <x:v>管理者</x:v>
+        <x:v>02／13_API権限対応：API-LOG-002</x:v>
       </x:c>
       <x:c r="F28" s="67" t="str">
-        <x:v>path: id Long</x:v>
+        <x:v>23_API項目定義：API-LOG-002 Request</x:v>
       </x:c>
       <x:c r="G28" s="67" t="str">
-        <x:v>マスキング済Log詳細</x:v>
+        <x:v>23_API項目定義：API-LOG-002 Response（正本）</x:v>
       </x:c>
       <x:c r="H28" s="67" t="str">
         <x:v>SCR-025</x:v>
       </x:c>
       <x:c r="I28" s="67" t="str">
-        <x:v>COMMON-4040</x:v>
+        <x:v>22_API処理・権限!F28／21_エラーコード</x:v>
       </x:c>
     </x:row>
     <x:row r="29">
@@ -3341,8 +2997,8 @@
         <x:v>Company WorkHub</x:v>
       </x:c>
       <x:c r="D3" s="21"/>
-      <x:c r="E3" s="23" t="str">
-        <x:v>文書番号</x:v>
+      <x:c r="E3" s="247" t="str">
+        <x:v>章ID</x:v>
       </x:c>
       <x:c r="F3" s="23"/>
       <x:c r="G3" s="21" t="str">
@@ -3351,12 +3007,12 @@
       <x:c r="H3" s="21"/>
     </x:row>
     <x:row r="4">
-      <x:c r="A4" s="23" t="str">
-        <x:v>版数</x:v>
+      <x:c r="A4" s="247" t="str">
+        <x:v>版数：Ver.2.5</x:v>
       </x:c>
       <x:c r="B4" s="23"/>
-      <x:c r="C4" s="21" t="str">
-        <x:v>Ver.1.8</x:v>
+      <x:c r="C4" s="248" t="str">
+        <x:v>Ver.2.5</x:v>
       </x:c>
       <x:c r="D4" s="21"/>
       <x:c r="E4" s="23" t="str">
@@ -3493,7 +3149,7 @@
         <x:v>X-Idempotency-Key</x:v>
       </x:c>
       <x:c r="D11" s="33" t="str">
-        <x:v>登録系推奨</x:v>
+        <x:v>登録系必須</x:v>
       </x:c>
       <x:c r="E11" s="33" t="str">
         <x:v>UUID</x:v>
@@ -3549,7 +3205,7 @@
         <x:v>処理成功</x:v>
       </x:c>
       <x:c r="F13" s="33" t="str">
-        <x:v>画面表示用Message</x:v>
+        <x:v>最終文言は18／31_メッセージと31B_ErrorMessage対応を参照。</x:v>
       </x:c>
       <x:c r="G13" s="33" t="str">
         <x:v>-</x:v>
@@ -3749,6 +3405,300 @@
       <x:c r="F23" s="17"/>
       <x:c r="G23" s="17"/>
       <x:c r="H23" s="17"/>
+    </x:row>
+    <x:row r="24" ht="110" customHeight="1">
+      <x:c r="A24" s="241" t="n">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="B24" s="241" t="str">
+        <x:v>Error Response</x:v>
+      </x:c>
+      <x:c r="C24" s="241" t="str">
+        <x:v>errors</x:v>
+      </x:c>
+      <x:c r="D24" s="241" t="str">
+        <x:v>Error時必須</x:v>
+      </x:c>
+      <x:c r="E24" s="241" t="str">
+        <x:v>Array&lt;Object&gt;。0件は[]</x:v>
+      </x:c>
+      <x:c r="F24" s="241" t="str">
+        <x:v>入力項目に紐付くErrorのみ格納。全体業務Errorは空配列。成功Responseでは省略</x:v>
+      </x:c>
+      <x:c r="G24" s="241" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="H24" s="241" t="str">
+        <x:v>dataは失敗時Null</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25" ht="110" customHeight="1">
+      <x:c r="A25" s="241" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="B25" s="241" t="str">
+        <x:v>Error Response</x:v>
+      </x:c>
+      <x:c r="C25" s="241" t="str">
+        <x:v>errors[].field</x:v>
+      </x:c>
+      <x:c r="D25" s="241" t="str">
+        <x:v>○</x:v>
+      </x:c>
+      <x:c r="E25" s="241" t="str">
+        <x:v>String、最大200</x:v>
+      </x:c>
+      <x:c r="F25" s="241" t="str">
+        <x:v>Requestのbody/query内のField Path。例：email、taskIds[0]。Prefix body/queryは付けない。画面項目Mappingは各画面定義</x:v>
+      </x:c>
+      <x:c r="G25" s="241" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="H25" s="241" t="str">
+        <x:v>パスワード入力値そのものは返さない</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26" ht="40" customHeight="1">
+      <x:c r="A26" s="241" t="n">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="B26" s="241" t="str">
+        <x:v>Error Response</x:v>
+      </x:c>
+      <x:c r="C26" s="241" t="str">
+        <x:v>errors[].message</x:v>
+      </x:c>
+      <x:c r="D26" s="241" t="str">
+        <x:v>○</x:v>
+      </x:c>
+      <x:c r="E26" s="241" t="str">
+        <x:v>String、最大200</x:v>
+      </x:c>
+      <x:c r="F26" s="241" t="str">
+        <x:v>18／31V_ValidationMessageの日本語文言をParameter展開。内部例外文言を返さない。</x:v>
+      </x:c>
+      <x:c r="G26" s="241" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="H26" s="241" t="str">
+        <x:v>HTML不可。Frontendは文字列表示</x:v>
+      </x:c>
+      <x:c r="I26" s="241"/>
+      <x:c r="J26" s="241"/>
+      <x:c r="K26" s="241"/>
+      <x:c r="L26" s="241"/>
+    </x:row>
+    <x:row r="27" ht="110" customHeight="1">
+      <x:c r="A27" s="241" t="n">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="B27" s="241" t="str">
+        <x:v>Error Response</x:v>
+      </x:c>
+      <x:c r="C27" s="241" t="str">
+        <x:v>errors[].code</x:v>
+      </x:c>
+      <x:c r="D27" s="241" t="str">
+        <x:v>○</x:v>
+      </x:c>
+      <x:c r="E27" s="241" t="str">
+        <x:v>String、最大30</x:v>
+      </x:c>
+      <x:c r="F27" s="241" t="str">
+        <x:v>外側codeと同じ既定Business Error Code。新Message IDを意味しない</x:v>
+      </x:c>
+      <x:c r="G27" s="241" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="H27" s="241" t="str">
+        <x:v>同一項目は定義順の先頭Errorを表示</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28" ht="110" customHeight="1">
+      <x:c r="A28" s="241" t="n">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="B28" s="241" t="str">
+        <x:v>Error表示規則</x:v>
+      </x:c>
+      <x:c r="C28" s="241" t="str">
+        <x:v>code/message/errors</x:v>
+      </x:c>
+      <x:c r="D28" s="241" t="str">
+        <x:v>○</x:v>
+      </x:c>
+      <x:c r="E28" s="241" t="str">
+        <x:v>18／32_例外処理参照</x:v>
+      </x:c>
+      <x:c r="F28" s="241" t="str">
+        <x:v>COMMON-4000の上部はMSG-E-006。項目下はerrors[].message。未対応項目は上部に表示。全Error文言は18／31B・31Vを参照。</x:v>
+      </x:c>
+      <x:c r="G28" s="241" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="H28" s="241" t="str">
+        <x:v>MSG-E-006をParameter Templateとして扱わない</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29" ht="40" customHeight="1">
+      <x:c r="A29" s="241" t="n">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="B29" s="241" t="str">
+        <x:v>Error Response例</x:v>
+      </x:c>
+      <x:c r="C29" s="241" t="str">
+        <x:v>COMMON-4000</x:v>
+      </x:c>
+      <x:c r="D29" s="241" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="E29" s="241" t="str">
+        <x:v>参考資料：COMMON-4000。code/message/data/timestamp/traceId/errorsを返す。errors[].field=email、errors[].code=COMMON-4000、errors[].messageはMSG-V-003に「メールアドレス」を設定。</x:v>
+      </x:c>
+      <x:c r="F29" s="241" t="str">
+        <x:v>errorsは失敗時のみ必須。入力値は含めない。</x:v>
+      </x:c>
+      <x:c r="G29" s="241" t="str">
+        <x:v>400</x:v>
+      </x:c>
+      <x:c r="H29" s="241" t="str">
+        <x:v>参考資料。文言は18／31V_ValidationMessage、構造は本Sheet。</x:v>
+      </x:c>
+      <x:c r="I29" s="241"/>
+      <x:c r="J29" s="241"/>
+      <x:c r="K29" s="241"/>
+      <x:c r="L29" s="241"/>
+    </x:row>
+    <x:row r="30" ht="100" customHeight="1">
+      <x:c r="A30" s="245" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="B30" s="245" t="str">
+        <x:v>Response Header</x:v>
+      </x:c>
+      <x:c r="C30" s="245" t="str">
+        <x:v>Retry-After</x:v>
+      </x:c>
+      <x:c r="D30" s="245" t="str">
+        <x:v>HTTP 429時</x:v>
+      </x:c>
+      <x:c r="E30" s="245" t="str">
+        <x:v>Integer／秒</x:v>
+      </x:c>
+      <x:c r="F30" s="245" t="str">
+        <x:v>非負整数。欠落・整数でない・負数は60秒。HTTP-date形式は本契約対象外。</x:v>
+      </x:c>
+      <x:c r="G30" s="245" t="str">
+        <x:v>AUTH-4290</x:v>
+      </x:c>
+      <x:c r="H30" s="245" t="str">
+        <x:v>残秒0まで再送不可。0は待機不要。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31" ht="100" customHeight="1">
+      <x:c r="A31" s="245" t="n">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="B31" s="245" t="str">
+        <x:v>Response規則</x:v>
+      </x:c>
+      <x:c r="C31" s="245" t="str">
+        <x:v>204</x:v>
+      </x:c>
+      <x:c r="D31" s="245" t="str">
+        <x:v>必須</x:v>
+      </x:c>
+      <x:c r="E31" s="245" t="str">
+        <x:v>Bodyなし</x:v>
+      </x:c>
+      <x:c r="F31" s="245" t="str">
+        <x:v>JSON Envelope、JSON null、空Objectを送信しない。</x:v>
+      </x:c>
+      <x:c r="G31" s="245" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="H31" s="245" t="str">
+        <x:v>各API項目定義に204条件を記載。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32" ht="100" customHeight="1">
+      <x:c r="A32" s="245" t="n">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="B32" s="245" t="str">
+        <x:v>Response規則</x:v>
+      </x:c>
+      <x:c r="C32" s="245" t="str">
+        <x:v>Download</x:v>
+      </x:c>
+      <x:c r="D32" s="245" t="str">
+        <x:v>Binary応答時</x:v>
+      </x:c>
+      <x:c r="E32" s="245" t="str">
+        <x:v>HTTP 200</x:v>
+      </x:c>
+      <x:c r="F32" s="245" t="str">
+        <x:v>Content-Type=実際のMIME、Content-Disposition=attachment; filename="..."（日本語はfilename*併記）、Body=Binary Stream。JSON Envelope対象外。</x:v>
+      </x:c>
+      <x:c r="G32" s="245" t="str">
+        <x:v>Error時JSON</x:v>
+      </x:c>
+      <x:c r="H32" s="245" t="str">
+        <x:v>API-EMP-007:0件は204/Bodyなし。API-TASK-010:200 Binary。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33" ht="100" customHeight="1">
+      <x:c r="A33" s="245" t="n">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="B33" s="245" t="str">
+        <x:v>Client共通</x:v>
+      </x:c>
+      <x:c r="C33" s="245" t="str">
+        <x:v>2xx Schema不一致</x:v>
+      </x:c>
+      <x:c r="D33" s="245" t="str">
+        <x:v>共通Client</x:v>
+      </x:c>
+      <x:c r="E33" s="245" t="str">
+        <x:v>COMMON-5000相当</x:v>
+      </x:c>
+      <x:c r="F33" s="245" t="str">
+        <x:v>必須欠落/Null不許可/型・階層不一致を画面反映前に拒否。部分State更新不可。traceIdを記録しMSG-E-001。認証確立前AUTH-004失敗時は取得Token/Sessionを破棄。</x:v>
+      </x:c>
+      <x:c r="G33" s="245" t="str">
+        <x:v>サーバCode新設なし</x:v>
+      </x:c>
+      <x:c r="H33" s="245" t="str">
+        <x:v>204とBinaryはJSON検証除外。traceId欠落はRequest側追跡IDを使用、秘密値は記録しない。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34" ht="100" customHeight="1">
+      <x:c r="A34" s="245" t="n">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="B34" s="245" t="str">
+        <x:v>共通認証Error</x:v>
+      </x:c>
+      <x:c r="C34" s="245" t="str">
+        <x:v>保護API全体</x:v>
+      </x:c>
+      <x:c r="D34" s="245" t="str">
+        <x:v>共通適用</x:v>
+      </x:c>
+      <x:c r="E34" s="245" t="str">
+        <x:v>21_エラーコード参照</x:v>
+      </x:c>
+      <x:c r="F34" s="245" t="str">
+        <x:v>Token不存在=AUTH-4002、無効/期限切れ=AUTH-4003、停止User=AUTH-4005、Permission/Data Scope不許可=AUTH-4006。</x:v>
+      </x:c>
+      <x:c r="G34" s="245" t="str">
+        <x:v>401/403</x:v>
+      </x:c>
+      <x:c r="H34" s="245" t="str">
+        <x:v>各Domainは共通Errorを再定義せず本規則を適用。</x:v>
+      </x:c>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -3772,751 +3722,499 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="20" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="72" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="72" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="22" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="48" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="42" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="24" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="24" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="24" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="24" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="24" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="24" hidden="0" customWidth="1"/>
     <x:col min="7" max="7" width="24" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="34" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="28" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="24" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1">
-      <x:c r="A1" s="68" t="str">
-        <x:v>API外部契約</x:v>
-      </x:c>
-      <x:c r="B1" s="68"/>
-      <x:c r="C1" s="68"/>
-      <x:c r="D1" s="68"/>
-      <x:c r="E1" s="68"/>
-      <x:c r="F1" s="68"/>
-      <x:c r="G1" s="68"/>
-      <x:c r="H1" s="68"/>
-      <x:c r="I1" s="68"/>
+      <x:c r="A1" s="252" t="str">
+        <x:v>21_エラーコード</x:v>
+      </x:c>
+      <x:c r="B1" s="251"/>
+      <x:c r="C1" s="251"/>
+      <x:c r="D1" s="251"/>
+      <x:c r="E1" s="251"/>
+      <x:c r="F1" s="251"/>
+      <x:c r="G1" s="251"/>
+      <x:c r="H1" s="251"/>
     </x:row>
     <x:row r="2">
-      <x:c r="A2" s="68"/>
-      <x:c r="B2" s="68"/>
-      <x:c r="C2" s="68"/>
-      <x:c r="D2" s="68"/>
-      <x:c r="E2" s="68"/>
-      <x:c r="F2" s="68"/>
-      <x:c r="G2" s="68"/>
-      <x:c r="H2" s="68"/>
-      <x:c r="I2" s="68"/>
+      <x:c r="A2" s="251"/>
+      <x:c r="B2" s="251"/>
+      <x:c r="C2" s="251"/>
+      <x:c r="D2" s="251"/>
+      <x:c r="E2" s="251"/>
+      <x:c r="F2" s="251"/>
+      <x:c r="G2" s="251"/>
+      <x:c r="H2" s="251"/>
     </x:row>
     <x:row r="3">
-      <x:c r="A3" s="62" t="str">
-        <x:v>システム名</x:v>
-      </x:c>
-      <x:c r="B3" s="63" t="str">
+      <x:c r="A3" s="251" t="str">
         <x:v>Company WorkHub</x:v>
       </x:c>
-      <x:c r="C3" s="63"/>
-      <x:c r="D3" s="63"/>
-      <x:c r="E3" s="62" t="str">
-        <x:v>文書番号</x:v>
-      </x:c>
-      <x:c r="F3" s="63" t="str">
-        <x:v>CW-BD-API-CMN-CONTRACT</x:v>
-      </x:c>
-      <x:c r="G3" s="63"/>
-      <x:c r="H3" s="63"/>
-      <x:c r="I3" s="63"/>
+      <x:c r="B3" s="251"/>
+      <x:c r="C3" s="251"/>
+      <x:c r="D3" s="251"/>
+      <x:c r="E3" s="251"/>
+      <x:c r="F3" s="251"/>
+      <x:c r="G3" s="251"/>
+      <x:c r="H3" s="251"/>
     </x:row>
     <x:row r="4">
-      <x:c r="A4" s="62" t="str">
-        <x:v>版数</x:v>
-      </x:c>
-      <x:c r="B4" s="63" t="str">
-        <x:v>Ver.1.8</x:v>
-      </x:c>
-      <x:c r="C4" s="63"/>
-      <x:c r="D4" s="63"/>
-      <x:c r="E4" s="62" t="str">
-        <x:v>改訂日</x:v>
-      </x:c>
-      <x:c r="F4" s="63" t="str">
-        <x:v>2026-08-12</x:v>
-      </x:c>
-      <x:c r="G4" s="63"/>
-      <x:c r="H4" s="63"/>
-      <x:c r="I4" s="63"/>
+      <x:c r="A4" s="251"/>
+      <x:c r="B4" s="251"/>
+      <x:c r="C4" s="251"/>
+      <x:c r="D4" s="251"/>
+      <x:c r="E4" s="251"/>
+      <x:c r="F4" s="251"/>
+      <x:c r="G4" s="251"/>
+      <x:c r="H4" s="251"/>
     </x:row>
     <x:row r="5">
-      <x:c r="A5" s="64"/>
-      <x:c r="B5" s="64"/>
-      <x:c r="C5" s="64"/>
-      <x:c r="D5" s="64"/>
-      <x:c r="E5" s="64"/>
-      <x:c r="F5" s="64"/>
-      <x:c r="G5" s="64"/>
-      <x:c r="H5" s="64"/>
-      <x:c r="I5" s="64"/>
+      <x:c r="A5" s="251" t="str">
+        <x:v>BL-2026-09-24 / Review中</x:v>
+      </x:c>
+      <x:c r="B5" s="251"/>
+      <x:c r="C5" s="251"/>
+      <x:c r="D5" s="251"/>
+      <x:c r="E5" s="251"/>
+      <x:c r="F5" s="251"/>
+      <x:c r="G5" s="251"/>
+      <x:c r="H5" s="251"/>
     </x:row>
     <x:row r="6" ht="22" customHeight="1">
-      <x:c r="A6" s="65" t="str">
-        <x:v>1. 共通・認証・管理 Request/Response・権限契約</x:v>
-      </x:c>
-      <x:c r="B6" s="65"/>
-      <x:c r="C6" s="65"/>
-      <x:c r="D6" s="65"/>
-      <x:c r="E6" s="65"/>
-      <x:c r="F6" s="65"/>
-      <x:c r="G6" s="65"/>
-      <x:c r="H6" s="65"/>
-      <x:c r="I6" s="65"/>
-    </x:row>
-    <x:row r="7">
-      <x:c r="A7" s="66" t="str">
-        <x:v>API ID</x:v>
-      </x:c>
-      <x:c r="B7" s="66" t="str">
-        <x:v>Request定義</x:v>
-      </x:c>
-      <x:c r="C7" s="66" t="str">
-        <x:v>Response定義</x:v>
-      </x:c>
-      <x:c r="D7" s="66" t="str">
-        <x:v>Role</x:v>
-      </x:c>
-      <x:c r="E7" s="66" t="str">
-        <x:v>Data範囲</x:v>
-      </x:c>
-      <x:c r="F7" s="66" t="str">
-        <x:v>参照・更新Table</x:v>
-      </x:c>
-      <x:c r="G7" s="66" t="str">
-        <x:v>Transaction</x:v>
-      </x:c>
-      <x:c r="H7" s="66" t="str">
+      <x:c r="A6" s="251"/>
+      <x:c r="B6" s="251"/>
+      <x:c r="C6" s="251"/>
+      <x:c r="D6" s="251"/>
+      <x:c r="E6" s="251"/>
+      <x:c r="F6" s="251"/>
+      <x:c r="G6" s="251"/>
+      <x:c r="H6" s="251"/>
+    </x:row>
+    <x:row r="7" ht="32" customHeight="1">
+      <x:c r="A7" s="254" t="str">
         <x:v>Error Code</x:v>
       </x:c>
-      <x:c r="I7" s="66" t="str">
-        <x:v>利用画面</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="8" ht="30" customHeight="1">
-      <x:c r="A8" s="67" t="str">
-        <x:v>API-AUTH-001</x:v>
-      </x:c>
-      <x:c r="B8" s="67" t="str">
-        <x:v>body: username String(1..50), password String(1..100)</x:v>
-      </x:c>
-      <x:c r="C8" s="67" t="str">
-        <x:v>accessToken, expiresIn, user{id,username,name,roles,permissions}</x:v>
-      </x:c>
-      <x:c r="D8" s="67" t="str">
-        <x:v>不要</x:v>
-      </x:c>
-      <x:c r="E8" s="67" t="str">
-        <x:v>未認証</x:v>
-      </x:c>
-      <x:c r="F8" s="67" t="str">
-        <x:v>users,roles,permissions,login_histories / Redis</x:v>
-      </x:c>
-      <x:c r="G8" s="67" t="str">
-        <x:v>TX-011</x:v>
-      </x:c>
-      <x:c r="H8" s="67" t="str">
-        <x:v>AUTH-4001, AUTH-4004, AUTH-4005,COMMON-5000</x:v>
-      </x:c>
-      <x:c r="I8" s="67" t="str">
-        <x:v>SCR-001</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" ht="30" customHeight="1">
-      <x:c r="A9" s="67" t="str">
-        <x:v>API-AUTH-002</x:v>
-      </x:c>
-      <x:c r="B9" s="67" t="str">
-        <x:v>header: Authorization; cookie: refreshToken</x:v>
-      </x:c>
-      <x:c r="C9" s="67" t="str">
-        <x:v>204 No Content</x:v>
-      </x:c>
-      <x:c r="D9" s="67" t="str">
-        <x:v>全員</x:v>
-      </x:c>
-      <x:c r="E9" s="67" t="str">
-        <x:v>本人Tokenのみ</x:v>
-      </x:c>
-      <x:c r="F9" s="67" t="str">
-        <x:v>refresh_tokens / Redis</x:v>
-      </x:c>
-      <x:c r="G9" s="67" t="str">
-        <x:v>TX-012</x:v>
-      </x:c>
-      <x:c r="H9" s="67" t="str">
-        <x:v>AUTH-4002,COMMON-5000</x:v>
-      </x:c>
-      <x:c r="I9" s="67" t="str">
-        <x:v>共通Header</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10" ht="30" customHeight="1">
-      <x:c r="A10" s="67" t="str">
-        <x:v>API-AUTH-003</x:v>
-      </x:c>
-      <x:c r="B10" s="67" t="str">
-        <x:v>cookie: refreshToken HttpOnly</x:v>
-      </x:c>
-      <x:c r="C10" s="67" t="str">
-        <x:v>accessToken, expiresIn</x:v>
-      </x:c>
-      <x:c r="D10" s="67" t="str">
-        <x:v>Refresh Cookie</x:v>
-      </x:c>
-      <x:c r="E10" s="67" t="str">
-        <x:v>有効・未失効Token</x:v>
-      </x:c>
-      <x:c r="F10" s="67" t="str">
-        <x:v>refresh_tokens / Redis</x:v>
-      </x:c>
-      <x:c r="G10" s="67" t="str">
-        <x:v>TX-013</x:v>
-      </x:c>
-      <x:c r="H10" s="67" t="str">
-        <x:v>AUTH-4002, AUTH-4003</x:v>
-      </x:c>
-      <x:c r="I10" s="67" t="str">
-        <x:v>共通Interceptor</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" ht="30" customHeight="1">
-      <x:c r="A11" s="67" t="str">
-        <x:v>API-AUTH-004</x:v>
-      </x:c>
-      <x:c r="B11" s="67" t="str">
-        <x:v>なし</x:v>
-      </x:c>
-      <x:c r="C11" s="67" t="str">
-        <x:v>user{id,employeeId,name,roles,permissions,menus}</x:v>
-      </x:c>
-      <x:c r="D11" s="67" t="str">
-        <x:v>全員</x:v>
-      </x:c>
-      <x:c r="E11" s="67" t="str">
-        <x:v>本人</x:v>
-      </x:c>
-      <x:c r="F11" s="67" t="str">
-        <x:v>users,employees,roles,permissions</x:v>
-      </x:c>
-      <x:c r="G11" s="67" t="str">
-        <x:v>参照</x:v>
-      </x:c>
-      <x:c r="H11" s="67" t="str">
-        <x:v>AUTH-4002, AUTH-4005</x:v>
-      </x:c>
-      <x:c r="I11" s="67" t="str">
-        <x:v>共通Layout</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12" ht="30" customHeight="1">
-      <x:c r="A12" s="67" t="str">
-        <x:v>API-AUTH-005</x:v>
-      </x:c>
-      <x:c r="B12" s="67" t="str">
-        <x:v>body: currentPassword String, newPassword String(8..64), confirmPassword String</x:v>
-      </x:c>
-      <x:c r="C12" s="67" t="str">
-        <x:v>204 No Content</x:v>
-      </x:c>
-      <x:c r="D12" s="67" t="str">
-        <x:v>全員</x:v>
-      </x:c>
-      <x:c r="E12" s="67" t="str">
-        <x:v>本人</x:v>
-      </x:c>
-      <x:c r="F12" s="67" t="str">
-        <x:v>users,refresh_tokens / Redis</x:v>
-      </x:c>
-      <x:c r="G12" s="67" t="str">
-        <x:v>TX-014</x:v>
-      </x:c>
-      <x:c r="H12" s="67" t="str">
-        <x:v>AUTH-4001, AUTH-4002,COMMON-4000</x:v>
-      </x:c>
-      <x:c r="I12" s="67" t="str">
-        <x:v>SCR-026</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="13" ht="30" customHeight="1">
-      <x:c r="A13" s="67" t="str">
-        <x:v>API-DASH-001</x:v>
-      </x:c>
-      <x:c r="B13" s="67" t="str">
-        <x:v>query: periodFrom Date, periodTo Date</x:v>
-      </x:c>
-      <x:c r="C13" s="67" t="str">
-        <x:v>projectCount,taskStatusCounts,dueSoonCount,reportSubmittedCount,recentNotifications[]</x:v>
-      </x:c>
-      <x:c r="D13" s="67" t="str">
-        <x:v>全員</x:v>
-      </x:c>
-      <x:c r="E13" s="67" t="str">
-        <x:v>ADMIN=全社, PM=担当PJ, EMP=本人・参加PJ</x:v>
-      </x:c>
-      <x:c r="F13" s="67" t="str">
-        <x:v>projects,tasks,daily_reports,notifications</x:v>
-      </x:c>
-      <x:c r="G13" s="67" t="str">
-        <x:v>参照</x:v>
-      </x:c>
-      <x:c r="H13" s="67" t="str">
-        <x:v>COMMON-4000, COMMON-5000</x:v>
-      </x:c>
-      <x:c r="I13" s="67" t="str">
-        <x:v>SCR-002</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="14" ht="30" customHeight="1">
-      <x:c r="A14" s="67" t="str">
-        <x:v>API-MST-001</x:v>
-      </x:c>
-      <x:c r="B14" s="67" t="str">
-        <x:v>query: activeOnly Boolean=true</x:v>
-      </x:c>
-      <x:c r="C14" s="67" t="str">
-        <x:v>departments[{id,code,name,parentId}]</x:v>
-      </x:c>
-      <x:c r="D14" s="67" t="str">
-        <x:v>全員</x:v>
-      </x:c>
-      <x:c r="E14" s="67" t="str">
-        <x:v>有効部門</x:v>
-      </x:c>
-      <x:c r="F14" s="67" t="str">
-        <x:v>departments / Redis</x:v>
-      </x:c>
-      <x:c r="G14" s="67" t="str">
-        <x:v>参照</x:v>
-      </x:c>
-      <x:c r="H14" s="67" t="str">
+      <x:c r="B7" s="254" t="str">
+        <x:v>分類</x:v>
+      </x:c>
+      <x:c r="C7" s="254" t="str">
+        <x:v>業務上の意味</x:v>
+      </x:c>
+      <x:c r="D7" s="254" t="str">
+        <x:v>HTTP Status</x:v>
+      </x:c>
+      <x:c r="E7" s="254" t="str">
+        <x:v>Message参照</x:v>
+      </x:c>
+      <x:c r="F7" s="254" t="str">
+        <x:v>Log Level</x:v>
+      </x:c>
+      <x:c r="G7" s="254" t="str">
+        <x:v>再試行</x:v>
+      </x:c>
+      <x:c r="H7" s="254" t="str">
+        <x:v>備考</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" ht="42" customHeight="1">
+      <x:c r="A8" s="256" t="str">
+        <x:v>COMMON-0000</x:v>
+      </x:c>
+      <x:c r="B8" s="256" t="str">
+        <x:v>成功</x:v>
+      </x:c>
+      <x:c r="C8" s="256" t="str">
+        <x:v>処理成功</x:v>
+      </x:c>
+      <x:c r="D8" s="256" t="str">
+        <x:v>200 / 201</x:v>
+      </x:c>
+      <x:c r="E8" s="256" t="str">
+        <x:v>18／31B_ErrorMessage対応参照</x:v>
+      </x:c>
+      <x:c r="F8" s="256" t="str">
+        <x:v>INFO</x:v>
+      </x:c>
+      <x:c r="G8" s="256" t="str">
+        <x:v>不可</x:v>
+      </x:c>
+      <x:c r="H8" s="256" t="str">
+        <x:v>成功時のHTTPは19_API共通I-OのHTTP Status規則に従う。照会・更新200、登録201。204はBodyなしのためCodeを送信しない。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" ht="42" customHeight="1">
+      <x:c r="A9" s="255" t="str">
+        <x:v>COMMON-4000</x:v>
+      </x:c>
+      <x:c r="B9" s="255" t="str">
+        <x:v>入力</x:v>
+      </x:c>
+      <x:c r="C9" s="255" t="str">
+        <x:v>Request parameter error</x:v>
+      </x:c>
+      <x:c r="D9" s="255" t="n">
+        <x:v>400</x:v>
+      </x:c>
+      <x:c r="E9" s="255" t="str">
+        <x:v>18／31B_ErrorMessage対応参照</x:v>
+      </x:c>
+      <x:c r="F9" s="255" t="str">
+        <x:v>WARN</x:v>
+      </x:c>
+      <x:c r="G9" s="255" t="str">
+        <x:v>不可</x:v>
+      </x:c>
+      <x:c r="H9" s="255" t="str"/>
+    </x:row>
+    <x:row r="10" ht="42" customHeight="1">
+      <x:c r="A10" s="256" t="str">
+        <x:v>COMMON-4040</x:v>
+      </x:c>
+      <x:c r="B10" s="256" t="str">
+        <x:v>Data</x:v>
+      </x:c>
+      <x:c r="C10" s="256" t="str">
+        <x:v>Data存在しない</x:v>
+      </x:c>
+      <x:c r="D10" s="256" t="n">
+        <x:v>404</x:v>
+      </x:c>
+      <x:c r="E10" s="256" t="str">
+        <x:v>18／31B_ErrorMessage対応参照</x:v>
+      </x:c>
+      <x:c r="F10" s="256" t="str">
+        <x:v>WARN</x:v>
+      </x:c>
+      <x:c r="G10" s="256" t="str">
+        <x:v>不可</x:v>
+      </x:c>
+      <x:c r="H10" s="256" t="str"/>
+    </x:row>
+    <x:row r="11" ht="42" customHeight="1">
+      <x:c r="A11" s="255" t="str">
+        <x:v>COMMON-4090</x:v>
+      </x:c>
+      <x:c r="B11" s="255" t="str">
+        <x:v>競合</x:v>
+      </x:c>
+      <x:c r="C11" s="255" t="str">
+        <x:v>並行更新Conflict</x:v>
+      </x:c>
+      <x:c r="D11" s="255" t="n">
+        <x:v>409</x:v>
+      </x:c>
+      <x:c r="E11" s="255" t="str">
+        <x:v>18／31B_ErrorMessage対応参照</x:v>
+      </x:c>
+      <x:c r="F11" s="255" t="str">
+        <x:v>WARN</x:v>
+      </x:c>
+      <x:c r="G11" s="255" t="str">
+        <x:v>不可</x:v>
+      </x:c>
+      <x:c r="H11" s="255" t="str"/>
+    </x:row>
+    <x:row r="12" ht="42" customHeight="1">
+      <x:c r="A12" s="256" t="str">
         <x:v>COMMON-5000</x:v>
       </x:c>
-      <x:c r="I14" s="67" t="str">
-        <x:v>SCR-003, SCR-004, SCR-007, SCR-021</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="15" ht="30" customHeight="1">
-      <x:c r="A15" s="67" t="str">
-        <x:v>API-MST-002</x:v>
-      </x:c>
-      <x:c r="B15" s="67" t="str">
-        <x:v>query: projectId Long?, keyword String?, activeOnly Boolean=true</x:v>
-      </x:c>
-      <x:c r="C15" s="67" t="str">
-        <x:v>employees[{id,code,name,departmentId}]</x:v>
-      </x:c>
-      <x:c r="D15" s="67" t="str">
-        <x:v>管理者/PM</x:v>
-      </x:c>
-      <x:c r="E15" s="67" t="str">
-        <x:v>ADMIN=全社, PM=担当PJ候補</x:v>
-      </x:c>
-      <x:c r="F15" s="67" t="str">
-        <x:v>employees,project_members</x:v>
-      </x:c>
-      <x:c r="G15" s="67" t="str">
-        <x:v>参照</x:v>
-      </x:c>
-      <x:c r="H15" s="67" t="str">
+      <x:c r="B12" s="256" t="str">
+        <x:v>System</x:v>
+      </x:c>
+      <x:c r="C12" s="256" t="str">
+        <x:v>System error</x:v>
+      </x:c>
+      <x:c r="D12" s="256" t="n">
+        <x:v>500</x:v>
+      </x:c>
+      <x:c r="E12" s="256" t="str">
+        <x:v>18／31B_ErrorMessage対応参照</x:v>
+      </x:c>
+      <x:c r="F12" s="256" t="str">
+        <x:v>ERROR</x:v>
+      </x:c>
+      <x:c r="G12" s="256" t="str">
+        <x:v>可</x:v>
+      </x:c>
+      <x:c r="H12" s="256" t="str"/>
+    </x:row>
+    <x:row r="13" ht="42" customHeight="1">
+      <x:c r="A13" s="255" t="str">
+        <x:v>AUTH-4001</x:v>
+      </x:c>
+      <x:c r="B13" s="255" t="str">
+        <x:v>認証</x:v>
+      </x:c>
+      <x:c r="C13" s="255" t="str">
+        <x:v>User名またはPassword誤り</x:v>
+      </x:c>
+      <x:c r="D13" s="255" t="n">
+        <x:v>401</x:v>
+      </x:c>
+      <x:c r="E13" s="255" t="str">
+        <x:v>18／31B_ErrorMessage対応参照</x:v>
+      </x:c>
+      <x:c r="F13" s="255" t="str">
+        <x:v>WARN</x:v>
+      </x:c>
+      <x:c r="G13" s="255" t="str">
+        <x:v>不可</x:v>
+      </x:c>
+      <x:c r="H13" s="255" t="str"/>
+    </x:row>
+    <x:row r="14" ht="42" customHeight="1">
+      <x:c r="A14" s="256" t="str">
+        <x:v>AUTH-4002</x:v>
+      </x:c>
+      <x:c r="B14" s="256" t="str">
+        <x:v>認証</x:v>
+      </x:c>
+      <x:c r="C14" s="256" t="str">
+        <x:v>Token不存在</x:v>
+      </x:c>
+      <x:c r="D14" s="256" t="n">
+        <x:v>401</x:v>
+      </x:c>
+      <x:c r="E14" s="256" t="str">
+        <x:v>18／31B_ErrorMessage対応参照</x:v>
+      </x:c>
+      <x:c r="F14" s="256" t="str">
+        <x:v>WARN</x:v>
+      </x:c>
+      <x:c r="G14" s="256" t="str">
+        <x:v>不可</x:v>
+      </x:c>
+      <x:c r="H14" s="256" t="str"/>
+    </x:row>
+    <x:row r="15" ht="42" customHeight="1">
+      <x:c r="A15" s="255" t="str">
+        <x:v>AUTH-4003</x:v>
+      </x:c>
+      <x:c r="B15" s="255" t="str">
+        <x:v>認証</x:v>
+      </x:c>
+      <x:c r="C15" s="255" t="str">
+        <x:v>Token無効・期限切れ</x:v>
+      </x:c>
+      <x:c r="D15" s="255" t="n">
+        <x:v>401</x:v>
+      </x:c>
+      <x:c r="E15" s="255" t="str">
+        <x:v>18／31B_ErrorMessage対応参照</x:v>
+      </x:c>
+      <x:c r="F15" s="255" t="str">
+        <x:v>WARN</x:v>
+      </x:c>
+      <x:c r="G15" s="255" t="str">
+        <x:v>不可</x:v>
+      </x:c>
+      <x:c r="H15" s="255" t="str"/>
+    </x:row>
+    <x:row r="16" ht="42" customHeight="1">
+      <x:c r="A16" s="256" t="str">
+        <x:v>AUTH-4004</x:v>
+      </x:c>
+      <x:c r="B16" s="256" t="str">
+        <x:v>認証</x:v>
+      </x:c>
+      <x:c r="C16" s="256" t="str">
+        <x:v>User Lock</x:v>
+      </x:c>
+      <x:c r="D16" s="256" t="n">
+        <x:v>423</x:v>
+      </x:c>
+      <x:c r="E16" s="256" t="str">
+        <x:v>18／31B_ErrorMessage対応参照</x:v>
+      </x:c>
+      <x:c r="F16" s="256" t="str">
+        <x:v>WARN</x:v>
+      </x:c>
+      <x:c r="G16" s="256" t="str">
+        <x:v>不可</x:v>
+      </x:c>
+      <x:c r="H16" s="256" t="str"/>
+    </x:row>
+    <x:row r="17" ht="42" customHeight="1">
+      <x:c r="A17" s="255" t="str">
+        <x:v>AUTH-4005</x:v>
+      </x:c>
+      <x:c r="B17" s="255" t="str">
+        <x:v>認証</x:v>
+      </x:c>
+      <x:c r="C17" s="255" t="str">
+        <x:v>User停止</x:v>
+      </x:c>
+      <x:c r="D17" s="255" t="n">
+        <x:v>403</x:v>
+      </x:c>
+      <x:c r="E17" s="255" t="str">
+        <x:v>18／31B_ErrorMessage対応参照</x:v>
+      </x:c>
+      <x:c r="F17" s="255" t="str">
+        <x:v>WARN</x:v>
+      </x:c>
+      <x:c r="G17" s="255" t="str">
+        <x:v>不可</x:v>
+      </x:c>
+      <x:c r="H17" s="255" t="str"/>
+    </x:row>
+    <x:row r="18" ht="42" customHeight="1">
+      <x:c r="A18" s="256" t="str">
         <x:v>AUTH-4006</x:v>
       </x:c>
-      <x:c r="I15" s="67" t="str">
-        <x:v>SCR-007, SCR-009, SCR-012, SCR-013, SCR-015, SCR-021</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="16" ht="30" customHeight="1">
-      <x:c r="A16" s="67" t="str">
-        <x:v>API-MST-003</x:v>
-      </x:c>
-      <x:c r="B16" s="67" t="str">
-        <x:v>query: activeOnly Boolean=true</x:v>
-      </x:c>
-      <x:c r="C16" s="67" t="str">
-        <x:v>projects[{id,code,name,role}]</x:v>
-      </x:c>
-      <x:c r="D16" s="67" t="str">
-        <x:v>全員</x:v>
-      </x:c>
-      <x:c r="E16" s="67" t="str">
-        <x:v>権限範囲内PJ</x:v>
-      </x:c>
-      <x:c r="F16" s="67" t="str">
-        <x:v>projects,project_members</x:v>
-      </x:c>
-      <x:c r="G16" s="67" t="str">
-        <x:v>参照</x:v>
-      </x:c>
-      <x:c r="H16" s="67" t="str">
-        <x:v>AUTH-4006</x:v>
-      </x:c>
-      <x:c r="I16" s="67" t="str">
-        <x:v>SCR-013, SCR-015, SCR-018, SCR-019, SCR-020, SCR-021</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="17" ht="30" customHeight="1">
-      <x:c r="A17" s="67" t="str">
-        <x:v>API-MST-004</x:v>
-      </x:c>
-      <x:c r="B17" s="67" t="str">
-        <x:v>なし</x:v>
-      </x:c>
-      <x:c r="C17" s="67" t="str">
-        <x:v>roles[],permissions[]</x:v>
-      </x:c>
-      <x:c r="D17" s="67" t="str">
-        <x:v>管理者</x:v>
-      </x:c>
-      <x:c r="E17" s="67" t="str">
-        <x:v>管理者のみ</x:v>
-      </x:c>
-      <x:c r="F17" s="67" t="str">
-        <x:v>roles,permissions</x:v>
-      </x:c>
-      <x:c r="G17" s="67" t="str">
-        <x:v>参照</x:v>
-      </x:c>
-      <x:c r="H17" s="67" t="str">
-        <x:v>AUTH-4006</x:v>
-      </x:c>
-      <x:c r="I17" s="67" t="str">
-        <x:v>SCR-004, SCR-023, SCR-024</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" ht="30" customHeight="1">
-      <x:c r="A18" s="67" t="str">
-        <x:v>API-USR-001</x:v>
-      </x:c>
-      <x:c r="B18" s="67" t="str">
-        <x:v>query: username,name,status,locked,page,size,sort</x:v>
-      </x:c>
-      <x:c r="C18" s="67" t="str">
-        <x:v>Page&lt;UserSummary&gt;</x:v>
-      </x:c>
-      <x:c r="D18" s="67" t="str">
-        <x:v>管理者</x:v>
-      </x:c>
-      <x:c r="E18" s="67" t="str">
-        <x:v>管理者のみ</x:v>
-      </x:c>
-      <x:c r="F18" s="67" t="str">
-        <x:v>users,employees,user_roles,roles</x:v>
-      </x:c>
-      <x:c r="G18" s="67" t="str">
-        <x:v>参照</x:v>
-      </x:c>
-      <x:c r="H18" s="67" t="str">
-        <x:v>COMMON-4000</x:v>
-      </x:c>
-      <x:c r="I18" s="67" t="str">
-        <x:v>SCR-023</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" ht="30" customHeight="1">
-      <x:c r="A19" s="67" t="str">
-        <x:v>API-USR-002</x:v>
-      </x:c>
-      <x:c r="B19" s="67" t="str">
-        <x:v>path: id Long</x:v>
-      </x:c>
-      <x:c r="C19" s="67" t="str">
-        <x:v>id,username,employee,status,lockedUntil,roles,version</x:v>
-      </x:c>
-      <x:c r="D19" s="67" t="str">
-        <x:v>管理者</x:v>
-      </x:c>
-      <x:c r="E19" s="67" t="str">
-        <x:v>管理者のみ</x:v>
-      </x:c>
-      <x:c r="F19" s="67" t="str">
-        <x:v>users,employees,user_roles,roles</x:v>
-      </x:c>
-      <x:c r="G19" s="67" t="str">
-        <x:v>参照</x:v>
-      </x:c>
-      <x:c r="H19" s="67" t="str">
-        <x:v>COMMON-4040</x:v>
-      </x:c>
-      <x:c r="I19" s="67" t="str">
-        <x:v>SCR-023</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="20" ht="30" customHeight="1">
-      <x:c r="A20" s="67" t="str">
-        <x:v>API-USR-003</x:v>
-      </x:c>
-      <x:c r="B20" s="67" t="str">
-        <x:v>path: id; body: enabled Boolean, roleIds Long[], version Integer</x:v>
-      </x:c>
-      <x:c r="C20" s="67" t="str">
-        <x:v>id,enabled,roles,version</x:v>
-      </x:c>
-      <x:c r="D20" s="67" t="str">
-        <x:v>管理者</x:v>
-      </x:c>
-      <x:c r="E20" s="67" t="str">
-        <x:v>管理者のみ; 自身のADMIN剥奪禁止</x:v>
-      </x:c>
-      <x:c r="F20" s="67" t="str">
-        <x:v>users,user_roles,operation_logs / Redis</x:v>
-      </x:c>
-      <x:c r="G20" s="67" t="str">
-        <x:v>TX-010</x:v>
-      </x:c>
-      <x:c r="H20" s="67" t="str">
-        <x:v>COMMON-4000, COMMON-4040, COMMON-4090</x:v>
-      </x:c>
-      <x:c r="I20" s="67" t="str">
-        <x:v>SCR-023</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="21" ht="30" customHeight="1">
-      <x:c r="A21" s="67" t="str">
-        <x:v>API-USR-004</x:v>
-      </x:c>
-      <x:c r="B21" s="67" t="str">
-        <x:v>path: id; header: X-Idempotency-Key</x:v>
-      </x:c>
-      <x:c r="C21" s="67" t="str">
-        <x:v>temporaryPassword（一回表示）</x:v>
-      </x:c>
-      <x:c r="D21" s="67" t="str">
-        <x:v>管理者</x:v>
-      </x:c>
-      <x:c r="E21" s="67" t="str">
-        <x:v>管理者のみ; 有効User</x:v>
-      </x:c>
-      <x:c r="F21" s="67" t="str">
-        <x:v>users,refresh_tokens,operation_logs / Redis</x:v>
-      </x:c>
-      <x:c r="G21" s="67" t="str">
-        <x:v>TX-014</x:v>
-      </x:c>
-      <x:c r="H21" s="67" t="str">
-        <x:v>COMMON-4040, COMMON-4090</x:v>
-      </x:c>
-      <x:c r="I21" s="67" t="str">
-        <x:v>SCR-023</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="22" ht="30" customHeight="1">
-      <x:c r="A22" s="67" t="str">
-        <x:v>API-ROLE-001</x:v>
-      </x:c>
-      <x:c r="B22" s="67" t="str">
-        <x:v>query: status,page,size</x:v>
-      </x:c>
-      <x:c r="C22" s="67" t="str">
-        <x:v>Page&lt;RoleSummary&gt;</x:v>
-      </x:c>
-      <x:c r="D22" s="67" t="str">
-        <x:v>管理者</x:v>
-      </x:c>
-      <x:c r="E22" s="67" t="str">
-        <x:v>管理者のみ</x:v>
-      </x:c>
-      <x:c r="F22" s="67" t="str">
-        <x:v>roles,role_permissions</x:v>
-      </x:c>
-      <x:c r="G22" s="67" t="str">
-        <x:v>参照</x:v>
-      </x:c>
-      <x:c r="H22" s="67" t="str">
-        <x:v>AUTH-4006</x:v>
-      </x:c>
-      <x:c r="I22" s="67" t="str">
-        <x:v>SCR-024</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="23" ht="30" customHeight="1">
-      <x:c r="A23" s="67" t="str">
-        <x:v>API-ROLE-002</x:v>
-      </x:c>
-      <x:c r="B23" s="67" t="str">
-        <x:v>path: id Long</x:v>
-      </x:c>
-      <x:c r="C23" s="67" t="str">
-        <x:v>id,roleCode,roleName,description,status,permissionIds,version</x:v>
-      </x:c>
-      <x:c r="D23" s="67" t="str">
-        <x:v>管理者</x:v>
-      </x:c>
-      <x:c r="E23" s="67" t="str">
-        <x:v>管理者のみ</x:v>
-      </x:c>
-      <x:c r="F23" s="67" t="str">
-        <x:v>roles,role_permissions,permissions</x:v>
-      </x:c>
-      <x:c r="G23" s="67" t="str">
-        <x:v>参照</x:v>
-      </x:c>
-      <x:c r="H23" s="67" t="str">
-        <x:v>COMMON-4040</x:v>
-      </x:c>
-      <x:c r="I23" s="67" t="str">
-        <x:v>SCR-024</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="24" ht="30" customHeight="1">
-      <x:c r="A24" s="67" t="str">
-        <x:v>API-ROLE-003</x:v>
-      </x:c>
-      <x:c r="B24" s="67" t="str">
-        <x:v>body: roleCode String(1..50),roleName String(1..100),description String(0..500),permissionIds[]; header: X-Idempotency-Key</x:v>
-      </x:c>
-      <x:c r="C24" s="67" t="str">
-        <x:v>id,roleCode,version</x:v>
-      </x:c>
-      <x:c r="D24" s="67" t="str">
-        <x:v>管理者</x:v>
-      </x:c>
-      <x:c r="E24" s="67" t="str">
-        <x:v>管理者のみ</x:v>
-      </x:c>
-      <x:c r="F24" s="67" t="str">
-        <x:v>roles,role_permissions,operation_logs</x:v>
-      </x:c>
-      <x:c r="G24" s="67" t="str">
-        <x:v>TX-008</x:v>
-      </x:c>
-      <x:c r="H24" s="67" t="str">
-        <x:v>COMMON-4000, COMMON-4090</x:v>
-      </x:c>
-      <x:c r="I24" s="67" t="str">
-        <x:v>SCR-024</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="25" ht="30" customHeight="1">
-      <x:c r="A25" s="67" t="str">
-        <x:v>API-ROLE-004</x:v>
-      </x:c>
-      <x:c r="B25" s="67" t="str">
-        <x:v>path: id; body: roleName,description,permissionIds[],version</x:v>
-      </x:c>
-      <x:c r="C25" s="67" t="str">
-        <x:v>id,status,permissionIds,version</x:v>
-      </x:c>
-      <x:c r="D25" s="67" t="str">
-        <x:v>管理者</x:v>
-      </x:c>
-      <x:c r="E25" s="67" t="str">
-        <x:v>組込Role Code変更禁止</x:v>
-      </x:c>
-      <x:c r="F25" s="67" t="str">
-        <x:v>roles,role_permissions,operation_logs / Redis</x:v>
-      </x:c>
-      <x:c r="G25" s="67" t="str">
-        <x:v>TX-008</x:v>
-      </x:c>
-      <x:c r="H25" s="67" t="str">
-        <x:v>COMMON-4000, COMMON-4040, COMMON-4090</x:v>
-      </x:c>
-      <x:c r="I25" s="67" t="str">
-        <x:v>SCR-024</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="26" ht="30" customHeight="1">
-      <x:c r="A26" s="67" t="str">
-        <x:v>API-ROLE-005</x:v>
-      </x:c>
-      <x:c r="B26" s="67" t="str">
-        <x:v>path: id; body: status,version</x:v>
-      </x:c>
-      <x:c r="C26" s="67" t="str">
-        <x:v>id,status,version</x:v>
-      </x:c>
-      <x:c r="D26" s="67" t="str">
-        <x:v>管理者</x:v>
-      </x:c>
-      <x:c r="E26" s="67" t="str">
-        <x:v>使用中Role停止時確認</x:v>
-      </x:c>
-      <x:c r="F26" s="67" t="str">
-        <x:v>roles,user_roles,operation_logs / Redis</x:v>
-      </x:c>
-      <x:c r="G26" s="67" t="str">
-        <x:v>TX-008</x:v>
-      </x:c>
-      <x:c r="H26" s="67" t="str">
-        <x:v>COMMON-4040, COMMON-4090</x:v>
-      </x:c>
-      <x:c r="I26" s="67" t="str">
-        <x:v>SCR-024</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="27" ht="30" customHeight="1">
-      <x:c r="A27" s="67" t="str">
-        <x:v>API-LOG-001</x:v>
-      </x:c>
-      <x:c r="B27" s="67" t="str">
-        <x:v>query: from,to,userId,module,action,result,traceId,page,size,sort</x:v>
-      </x:c>
-      <x:c r="C27" s="67" t="str">
-        <x:v>Page&lt;OperationLogSummary&gt;</x:v>
-      </x:c>
-      <x:c r="D27" s="67" t="str">
-        <x:v>管理者</x:v>
-      </x:c>
-      <x:c r="E27" s="67" t="str">
-        <x:v>管理者のみ</x:v>
-      </x:c>
-      <x:c r="F27" s="67" t="str">
-        <x:v>operation_logs</x:v>
-      </x:c>
-      <x:c r="G27" s="67" t="str">
-        <x:v>参照</x:v>
-      </x:c>
-      <x:c r="H27" s="67" t="str">
-        <x:v>COMMON-4000</x:v>
-      </x:c>
-      <x:c r="I27" s="67" t="str">
-        <x:v>SCR-025</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="28" ht="30" customHeight="1">
-      <x:c r="A28" s="67" t="str">
-        <x:v>API-LOG-002</x:v>
-      </x:c>
-      <x:c r="B28" s="67" t="str">
-        <x:v>path: id Long</x:v>
-      </x:c>
-      <x:c r="C28" s="67" t="str">
-        <x:v>マスキング済Log詳細</x:v>
-      </x:c>
-      <x:c r="D28" s="67" t="str">
-        <x:v>管理者</x:v>
-      </x:c>
-      <x:c r="E28" s="67" t="str">
-        <x:v>管理者のみ</x:v>
-      </x:c>
-      <x:c r="F28" s="67" t="str">
-        <x:v>operation_logs</x:v>
-      </x:c>
-      <x:c r="G28" s="67" t="str">
-        <x:v>参照</x:v>
-      </x:c>
-      <x:c r="H28" s="67" t="str">
-        <x:v>COMMON-4040</x:v>
-      </x:c>
-      <x:c r="I28" s="67" t="str">
-        <x:v>SCR-025</x:v>
-      </x:c>
+      <x:c r="B18" s="256" t="str">
+        <x:v>権限</x:v>
+      </x:c>
+      <x:c r="C18" s="256" t="str">
+        <x:v>権限なし</x:v>
+      </x:c>
+      <x:c r="D18" s="256" t="n">
+        <x:v>403</x:v>
+      </x:c>
+      <x:c r="E18" s="256" t="str">
+        <x:v>18／31B_ErrorMessage対応参照</x:v>
+      </x:c>
+      <x:c r="F18" s="256" t="str">
+        <x:v>WARN</x:v>
+      </x:c>
+      <x:c r="G18" s="256" t="str">
+        <x:v>不可</x:v>
+      </x:c>
+      <x:c r="H18" s="256" t="str"/>
+    </x:row>
+    <x:row r="19" ht="57" customHeight="1">
+      <x:c r="A19" s="255" t="str">
+        <x:v>AUTH-4290</x:v>
+      </x:c>
+      <x:c r="B19" s="255" t="str">
+        <x:v>認証</x:v>
+      </x:c>
+      <x:c r="C19" s="255" t="str">
+        <x:v>Login試行回数超過</x:v>
+      </x:c>
+      <x:c r="D19" s="255" t="n">
+        <x:v>429</x:v>
+      </x:c>
+      <x:c r="E19" s="255" t="str">
+        <x:v>18／31B_ErrorMessage対応参照</x:v>
+      </x:c>
+      <x:c r="F19" s="255" t="str">
+        <x:v>WARN</x:v>
+      </x:c>
+      <x:c r="G19" s="255" t="str">
+        <x:v>可（60秒後）</x:v>
+      </x:c>
+      <x:c r="H19" s="255" t="str">
+        <x:v>IP/username単位10回/分。Retry-After: 60を返却</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20">
+      <x:c r="A20"/>
+      <x:c r="B20"/>
+      <x:c r="C20"/>
+      <x:c r="D20"/>
+      <x:c r="E20"/>
+      <x:c r="F20"/>
+      <x:c r="G20"/>
+      <x:c r="H20"/>
+    </x:row>
+    <x:row r="21">
+      <x:c r="A21"/>
+      <x:c r="B21"/>
+      <x:c r="C21"/>
+      <x:c r="D21"/>
+      <x:c r="E21"/>
+      <x:c r="F21"/>
+      <x:c r="G21"/>
+      <x:c r="H21"/>
+    </x:row>
+    <x:row r="22">
+      <x:c r="A22"/>
+      <x:c r="B22"/>
+      <x:c r="C22"/>
+      <x:c r="D22"/>
+      <x:c r="E22"/>
+      <x:c r="F22"/>
+      <x:c r="G22"/>
+      <x:c r="H22"/>
+    </x:row>
+    <x:row r="23">
+      <x:c r="A23"/>
+      <x:c r="B23"/>
+      <x:c r="C23"/>
+      <x:c r="D23"/>
+      <x:c r="E23"/>
+      <x:c r="F23"/>
+      <x:c r="G23"/>
+      <x:c r="H23"/>
+    </x:row>
+    <x:row r="24">
+      <x:c r="A24"/>
+      <x:c r="B24"/>
+      <x:c r="C24"/>
+      <x:c r="D24"/>
+      <x:c r="E24"/>
+      <x:c r="F24"/>
+      <x:c r="G24"/>
+      <x:c r="H24"/>
+    </x:row>
+    <x:row r="25">
+      <x:c r="A25"/>
+      <x:c r="B25"/>
+      <x:c r="C25"/>
+      <x:c r="D25"/>
+      <x:c r="E25"/>
+      <x:c r="F25"/>
+      <x:c r="G25"/>
+      <x:c r="H25"/>
+    </x:row>
+    <x:row r="26">
+      <x:c r="A26"/>
+      <x:c r="B26"/>
+      <x:c r="C26"/>
+      <x:c r="D26"/>
+      <x:c r="E26"/>
+      <x:c r="F26"/>
+      <x:c r="G26"/>
+      <x:c r="H26"/>
+    </x:row>
+    <x:row r="27">
+      <x:c r="A27"/>
+      <x:c r="B27"/>
+      <x:c r="C27"/>
+      <x:c r="D27"/>
+      <x:c r="E27"/>
+      <x:c r="F27"/>
+      <x:c r="G27"/>
+      <x:c r="H27"/>
+    </x:row>
+    <x:row r="28">
+      <x:c r="A28"/>
+      <x:c r="B28"/>
+      <x:c r="C28"/>
+      <x:c r="D28"/>
+      <x:c r="E28"/>
+      <x:c r="F28"/>
+      <x:c r="G28"/>
+      <x:c r="H28"/>
     </x:row>
     <x:row r="29">
-      <x:c r="A29" s="64"/>
-      <x:c r="B29" s="64"/>
-      <x:c r="C29" s="64"/>
-      <x:c r="D29" s="64"/>
-      <x:c r="E29" s="64"/>
-      <x:c r="F29" s="64"/>
-      <x:c r="G29" s="64"/>
-      <x:c r="H29" s="64"/>
-      <x:c r="I29" s="64"/>
+      <x:c r="A29"/>
+      <x:c r="B29"/>
+      <x:c r="C29"/>
+      <x:c r="D29"/>
+      <x:c r="E29"/>
+      <x:c r="F29"/>
+      <x:c r="G29"/>
+      <x:c r="H29"/>
     </x:row>
     <x:row r="30">
       <x:c r="A30"/>
@@ -4527,32 +4225,82 @@
       <x:c r="F30"/>
       <x:c r="G30"/>
       <x:c r="H30"/>
-      <x:c r="I30"/>
     </x:row>
     <x:row r="31">
-      <x:c r="A31" s="91"/>
-      <x:c r="B31" s="92"/>
-      <x:c r="C31" s="92"/>
-      <x:c r="D31" s="92"/>
-      <x:c r="E31" s="92"/>
-      <x:c r="F31" s="92"/>
-      <x:c r="G31" s="92"/>
-      <x:c r="H31" s="92"/>
-      <x:c r="I31" s="93"/>
+      <x:c r="A31"/>
+      <x:c r="B31"/>
+      <x:c r="C31"/>
+      <x:c r="D31"/>
+      <x:c r="E31"/>
+      <x:c r="F31"/>
+      <x:c r="G31"/>
+      <x:c r="H31"/>
+    </x:row>
+    <x:row r="32">
+      <x:c r="A32"/>
+      <x:c r="B32"/>
+      <x:c r="C32"/>
+      <x:c r="D32"/>
+      <x:c r="E32"/>
+      <x:c r="F32"/>
+      <x:c r="G32"/>
+      <x:c r="H32"/>
+    </x:row>
+    <x:row r="33">
+      <x:c r="A33"/>
+      <x:c r="B33"/>
+      <x:c r="C33"/>
+      <x:c r="D33"/>
+      <x:c r="E33"/>
+      <x:c r="F33"/>
+      <x:c r="G33"/>
+      <x:c r="H33"/>
+    </x:row>
+    <x:row r="34">
+      <x:c r="A34"/>
+      <x:c r="B34"/>
+      <x:c r="C34"/>
+      <x:c r="D34"/>
+      <x:c r="E34"/>
+      <x:c r="F34"/>
+      <x:c r="G34"/>
+      <x:c r="H34"/>
+    </x:row>
+    <x:row r="35">
+      <x:c r="A35"/>
+      <x:c r="B35"/>
+      <x:c r="C35"/>
+      <x:c r="D35"/>
+      <x:c r="E35"/>
+      <x:c r="F35"/>
+      <x:c r="G35"/>
+      <x:c r="H35"/>
+    </x:row>
+    <x:row r="36">
+      <x:c r="A36"/>
+      <x:c r="B36"/>
+      <x:c r="C36"/>
+      <x:c r="D36"/>
+      <x:c r="E36"/>
+      <x:c r="F36"/>
+      <x:c r="G36"/>
+      <x:c r="H36"/>
+    </x:row>
+    <x:row r="37">
+      <x:c r="A37"/>
+      <x:c r="B37"/>
+      <x:c r="C37"/>
+      <x:c r="D37"/>
+      <x:c r="E37"/>
+      <x:c r="F37"/>
+      <x:c r="G37"/>
+      <x:c r="H37"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
-    <x:mergeCell ref="A1:I2"/>
-    <x:mergeCell ref="A3:B3"/>
-    <x:mergeCell ref="C3:D3"/>
-    <x:mergeCell ref="E3:F3"/>
-    <x:mergeCell ref="G3:I3"/>
-    <x:mergeCell ref="A4:B4"/>
-    <x:mergeCell ref="C4:D4"/>
-    <x:mergeCell ref="E4:F4"/>
-    <x:mergeCell ref="G4:I4"/>
-    <x:mergeCell ref="A6:I6"/>
-    <x:mergeCell ref="A30:I31"/>
+    <x:mergeCell ref="A1:H1"/>
+    <x:mergeCell ref="A3:H3"/>
+    <x:mergeCell ref="A5:H5"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
@@ -4563,593 +4311,14 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="20" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="16" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="46" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="14" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="50" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="14" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="14" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="22" hidden="0" customWidth="1"/>
-  </x:cols>
-  <x:sheetData>
-    <x:row r="1">
-      <x:c r="A1" s="20" t="str">
-        <x:v>業務エラーコード</x:v>
-      </x:c>
-      <x:c r="B1" s="20"/>
-      <x:c r="C1" s="20"/>
-      <x:c r="D1" s="20"/>
-      <x:c r="E1" s="20"/>
-      <x:c r="F1" s="20"/>
-      <x:c r="G1" s="20"/>
-      <x:c r="H1" s="20"/>
-    </x:row>
-    <x:row r="2">
-      <x:c r="A2" s="20"/>
-      <x:c r="B2" s="20"/>
-      <x:c r="C2" s="20"/>
-      <x:c r="D2" s="20"/>
-      <x:c r="E2" s="20"/>
-      <x:c r="F2" s="20"/>
-      <x:c r="G2" s="20"/>
-      <x:c r="H2" s="20"/>
-    </x:row>
-    <x:row r="3">
-      <x:c r="A3" s="23" t="str">
-        <x:v>システム名</x:v>
-      </x:c>
-      <x:c r="B3" s="23"/>
-      <x:c r="C3" s="21" t="str">
-        <x:v>Company WorkHub</x:v>
-      </x:c>
-      <x:c r="D3" s="21"/>
-      <x:c r="E3" s="23" t="str">
-        <x:v>文書番号</x:v>
-      </x:c>
-      <x:c r="F3" s="23"/>
-      <x:c r="G3" s="21" t="str">
-        <x:v>CW-BD-053</x:v>
-      </x:c>
-      <x:c r="H3" s="21"/>
-    </x:row>
-    <x:row r="4">
-      <x:c r="A4" s="23" t="str">
-        <x:v>版数</x:v>
-      </x:c>
-      <x:c r="B4" s="23"/>
-      <x:c r="C4" s="21" t="str">
-        <x:v>Ver.1.8</x:v>
-      </x:c>
-      <x:c r="D4" s="21"/>
-      <x:c r="E4" s="23" t="str">
-        <x:v>作成日</x:v>
-      </x:c>
-      <x:c r="F4" s="23"/>
-      <x:c r="G4" s="24" t="n">
-        <x:v>46239</x:v>
-      </x:c>
-      <x:c r="H4" s="24"/>
-    </x:row>
-    <x:row r="6" ht="22" customHeight="1">
-      <x:c r="A6" s="26" t="str">
-        <x:v>1. Error Code</x:v>
-      </x:c>
-      <x:c r="B6" s="26"/>
-      <x:c r="C6" s="26"/>
-      <x:c r="D6" s="26"/>
-      <x:c r="E6" s="26"/>
-      <x:c r="F6" s="26"/>
-      <x:c r="G6" s="26"/>
-      <x:c r="H6" s="26"/>
-    </x:row>
-    <x:row r="7">
-      <x:c r="A7" s="31" t="str">
-        <x:v>Error Code</x:v>
-      </x:c>
-      <x:c r="B7" s="31" t="str">
-        <x:v>分類</x:v>
-      </x:c>
-      <x:c r="C7" s="31" t="str">
-        <x:v>意味</x:v>
-      </x:c>
-      <x:c r="D7" s="31" t="str">
-        <x:v>HTTP Status</x:v>
-      </x:c>
-      <x:c r="E7" s="31" t="str">
-        <x:v>画面Message</x:v>
-      </x:c>
-      <x:c r="F7" s="31" t="str">
-        <x:v>記録Level</x:v>
-      </x:c>
-      <x:c r="G7" s="31" t="str">
-        <x:v>再試行</x:v>
-      </x:c>
-      <x:c r="H7" s="31" t="str">
-        <x:v>備考</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="8">
-      <x:c r="A8" s="33" t="str">
-        <x:v>COMMON-0000</x:v>
-      </x:c>
-      <x:c r="B8" s="33" t="str">
-        <x:v>成功</x:v>
-      </x:c>
-      <x:c r="C8" s="33" t="str">
-        <x:v>処理成功</x:v>
-      </x:c>
-      <x:c r="D8" s="33" t="n">
-        <x:v>200</x:v>
-      </x:c>
-      <x:c r="E8" s="33" t="str">
-        <x:v>処理成功</x:v>
-      </x:c>
-      <x:c r="F8" s="33" t="str">
-        <x:v>INFO</x:v>
-      </x:c>
-      <x:c r="G8" s="33" t="str">
-        <x:v>不可</x:v>
-      </x:c>
-      <x:c r="H8" s="33"/>
-    </x:row>
-    <x:row r="9">
-      <x:c r="A9" s="33" t="str">
-        <x:v>COMMON-4000</x:v>
-      </x:c>
-      <x:c r="B9" s="33" t="str">
-        <x:v>入力</x:v>
-      </x:c>
-      <x:c r="C9" s="33" t="str">
-        <x:v>Request parameter error</x:v>
-      </x:c>
-      <x:c r="D9" s="33" t="n">
-        <x:v>400</x:v>
-      </x:c>
-      <x:c r="E9" s="33" t="str">
-        <x:v>入力または処理内容を確認してください。</x:v>
-      </x:c>
-      <x:c r="F9" s="33" t="str">
-        <x:v>WARN</x:v>
-      </x:c>
-      <x:c r="G9" s="33" t="str">
-        <x:v>不可</x:v>
-      </x:c>
-      <x:c r="H9" s="33"/>
-    </x:row>
-    <x:row r="10">
-      <x:c r="A10" s="33" t="str">
-        <x:v>COMMON-4040</x:v>
-      </x:c>
-      <x:c r="B10" s="33" t="str">
-        <x:v>Data</x:v>
-      </x:c>
-      <x:c r="C10" s="33" t="str">
-        <x:v>Data存在しない</x:v>
-      </x:c>
-      <x:c r="D10" s="33" t="n">
-        <x:v>404</x:v>
-      </x:c>
-      <x:c r="E10" s="33" t="str">
-        <x:v>入力または処理内容を確認してください。</x:v>
-      </x:c>
-      <x:c r="F10" s="33" t="str">
-        <x:v>WARN</x:v>
-      </x:c>
-      <x:c r="G10" s="33" t="str">
-        <x:v>不可</x:v>
-      </x:c>
-      <x:c r="H10" s="33"/>
-    </x:row>
-    <x:row r="11">
-      <x:c r="A11" s="33" t="str">
-        <x:v>COMMON-4090</x:v>
-      </x:c>
-      <x:c r="B11" s="33" t="str">
-        <x:v>競合</x:v>
-      </x:c>
-      <x:c r="C11" s="33" t="str">
-        <x:v>並行更新Conflict</x:v>
-      </x:c>
-      <x:c r="D11" s="33" t="n">
-        <x:v>409</x:v>
-      </x:c>
-      <x:c r="E11" s="33" t="str">
-        <x:v>入力または処理内容を確認してください。</x:v>
-      </x:c>
-      <x:c r="F11" s="33" t="str">
-        <x:v>WARN</x:v>
-      </x:c>
-      <x:c r="G11" s="33" t="str">
-        <x:v>不可</x:v>
-      </x:c>
-      <x:c r="H11" s="33"/>
-    </x:row>
-    <x:row r="12">
-      <x:c r="A12" s="33" t="str">
-        <x:v>COMMON-5000</x:v>
-      </x:c>
-      <x:c r="B12" s="33" t="str">
-        <x:v>System</x:v>
-      </x:c>
-      <x:c r="C12" s="33" t="str">
-        <x:v>System error</x:v>
-      </x:c>
-      <x:c r="D12" s="33" t="n">
-        <x:v>500</x:v>
-      </x:c>
-      <x:c r="E12" s="33" t="str">
-        <x:v>入力または処理内容を確認してください。</x:v>
-      </x:c>
-      <x:c r="F12" s="33" t="str">
-        <x:v>ERROR</x:v>
-      </x:c>
-      <x:c r="G12" s="33" t="str">
-        <x:v>可</x:v>
-      </x:c>
-      <x:c r="H12" s="33"/>
-    </x:row>
-    <x:row r="13">
-      <x:c r="A13" s="33" t="str">
-        <x:v>AUTH-4001</x:v>
-      </x:c>
-      <x:c r="B13" s="33" t="str">
-        <x:v>認証</x:v>
-      </x:c>
-      <x:c r="C13" s="33" t="str">
-        <x:v>User名またはPassword誤り</x:v>
-      </x:c>
-      <x:c r="D13" s="33" t="n">
-        <x:v>401</x:v>
-      </x:c>
-      <x:c r="E13" s="33" t="str">
-        <x:v>入力または処理内容を確認してください。</x:v>
-      </x:c>
-      <x:c r="F13" s="33" t="str">
-        <x:v>WARN</x:v>
-      </x:c>
-      <x:c r="G13" s="33" t="str">
-        <x:v>不可</x:v>
-      </x:c>
-      <x:c r="H13" s="33"/>
-    </x:row>
-    <x:row r="14">
-      <x:c r="A14" s="33" t="str">
-        <x:v>AUTH-4002</x:v>
-      </x:c>
-      <x:c r="B14" s="33" t="str">
-        <x:v>認証</x:v>
-      </x:c>
-      <x:c r="C14" s="33" t="str">
-        <x:v>Token無効</x:v>
-      </x:c>
-      <x:c r="D14" s="33" t="n">
-        <x:v>401</x:v>
-      </x:c>
-      <x:c r="E14" s="33" t="str">
-        <x:v>入力または処理内容を確認してください。</x:v>
-      </x:c>
-      <x:c r="F14" s="33" t="str">
-        <x:v>WARN</x:v>
-      </x:c>
-      <x:c r="G14" s="33" t="str">
-        <x:v>不可</x:v>
-      </x:c>
-      <x:c r="H14" s="33"/>
-    </x:row>
-    <x:row r="15">
-      <x:c r="A15" s="33" t="str">
-        <x:v>AUTH-4003</x:v>
-      </x:c>
-      <x:c r="B15" s="33" t="str">
-        <x:v>認証</x:v>
-      </x:c>
-      <x:c r="C15" s="33" t="str">
-        <x:v>Token期限切れ</x:v>
-      </x:c>
-      <x:c r="D15" s="33" t="n">
-        <x:v>401</x:v>
-      </x:c>
-      <x:c r="E15" s="33" t="str">
-        <x:v>入力または処理内容を確認してください。</x:v>
-      </x:c>
-      <x:c r="F15" s="33" t="str">
-        <x:v>WARN</x:v>
-      </x:c>
-      <x:c r="G15" s="33" t="str">
-        <x:v>不可</x:v>
-      </x:c>
-      <x:c r="H15" s="33"/>
-    </x:row>
-    <x:row r="16">
-      <x:c r="A16" s="33" t="str">
-        <x:v>AUTH-4004</x:v>
-      </x:c>
-      <x:c r="B16" s="33" t="str">
-        <x:v>認証</x:v>
-      </x:c>
-      <x:c r="C16" s="33" t="str">
-        <x:v>User Lock</x:v>
-      </x:c>
-      <x:c r="D16" s="33" t="n">
-        <x:v>423</x:v>
-      </x:c>
-      <x:c r="E16" s="33" t="str">
-        <x:v>入力または処理内容を確認してください。</x:v>
-      </x:c>
-      <x:c r="F16" s="33" t="str">
-        <x:v>WARN</x:v>
-      </x:c>
-      <x:c r="G16" s="33" t="str">
-        <x:v>不可</x:v>
-      </x:c>
-      <x:c r="H16" s="33"/>
-    </x:row>
-    <x:row r="17">
-      <x:c r="A17" s="33" t="str">
-        <x:v>AUTH-4005</x:v>
-      </x:c>
-      <x:c r="B17" s="33" t="str">
-        <x:v>認証</x:v>
-      </x:c>
-      <x:c r="C17" s="33" t="str">
-        <x:v>User停止</x:v>
-      </x:c>
-      <x:c r="D17" s="33" t="n">
-        <x:v>403</x:v>
-      </x:c>
-      <x:c r="E17" s="33" t="str">
-        <x:v>入力または処理内容を確認してください。</x:v>
-      </x:c>
-      <x:c r="F17" s="33" t="str">
-        <x:v>WARN</x:v>
-      </x:c>
-      <x:c r="G17" s="33" t="str">
-        <x:v>不可</x:v>
-      </x:c>
-      <x:c r="H17" s="33"/>
-    </x:row>
-    <x:row r="18">
-      <x:c r="A18" s="33" t="str">
-        <x:v>AUTH-4006</x:v>
-      </x:c>
-      <x:c r="B18" s="33" t="str">
-        <x:v>権限</x:v>
-      </x:c>
-      <x:c r="C18" s="33" t="str">
-        <x:v>権限なし</x:v>
-      </x:c>
-      <x:c r="D18" s="33" t="n">
-        <x:v>403</x:v>
-      </x:c>
-      <x:c r="E18" s="33" t="str">
-        <x:v>入力または処理内容を確認してください。</x:v>
-      </x:c>
-      <x:c r="F18" s="33" t="str">
-        <x:v>WARN</x:v>
-      </x:c>
-      <x:c r="G18" s="33" t="str">
-        <x:v>不可</x:v>
-      </x:c>
-      <x:c r="H18" s="33"/>
-    </x:row>
-    <x:row r="19">
-      <x:c r="A19"/>
-      <x:c r="B19"/>
-      <x:c r="C19"/>
-      <x:c r="D19"/>
-      <x:c r="E19"/>
-      <x:c r="F19"/>
-      <x:c r="G19"/>
-      <x:c r="H19"/>
-    </x:row>
-    <x:row r="20">
-      <x:c r="A20"/>
-      <x:c r="B20"/>
-      <x:c r="C20"/>
-      <x:c r="D20"/>
-      <x:c r="E20"/>
-      <x:c r="F20"/>
-      <x:c r="G20"/>
-      <x:c r="H20"/>
-    </x:row>
-    <x:row r="21">
-      <x:c r="A21"/>
-      <x:c r="B21"/>
-      <x:c r="C21"/>
-      <x:c r="D21"/>
-      <x:c r="E21"/>
-      <x:c r="F21"/>
-      <x:c r="G21"/>
-      <x:c r="H21"/>
-    </x:row>
-    <x:row r="22">
-      <x:c r="A22"/>
-      <x:c r="B22"/>
-      <x:c r="C22"/>
-      <x:c r="D22"/>
-      <x:c r="E22"/>
-      <x:c r="F22"/>
-      <x:c r="G22"/>
-      <x:c r="H22"/>
-    </x:row>
-    <x:row r="23">
-      <x:c r="A23"/>
-      <x:c r="B23"/>
-      <x:c r="C23"/>
-      <x:c r="D23"/>
-      <x:c r="E23"/>
-      <x:c r="F23"/>
-      <x:c r="G23"/>
-      <x:c r="H23"/>
-    </x:row>
-    <x:row r="24">
-      <x:c r="A24"/>
-      <x:c r="B24"/>
-      <x:c r="C24"/>
-      <x:c r="D24"/>
-      <x:c r="E24"/>
-      <x:c r="F24"/>
-      <x:c r="G24"/>
-      <x:c r="H24"/>
-    </x:row>
-    <x:row r="25">
-      <x:c r="A25"/>
-      <x:c r="B25"/>
-      <x:c r="C25"/>
-      <x:c r="D25"/>
-      <x:c r="E25"/>
-      <x:c r="F25"/>
-      <x:c r="G25"/>
-      <x:c r="H25"/>
-    </x:row>
-    <x:row r="26">
-      <x:c r="A26"/>
-      <x:c r="B26"/>
-      <x:c r="C26"/>
-      <x:c r="D26"/>
-      <x:c r="E26"/>
-      <x:c r="F26"/>
-      <x:c r="G26"/>
-      <x:c r="H26"/>
-    </x:row>
-    <x:row r="27">
-      <x:c r="A27"/>
-      <x:c r="B27"/>
-      <x:c r="C27"/>
-      <x:c r="D27"/>
-      <x:c r="E27"/>
-      <x:c r="F27"/>
-      <x:c r="G27"/>
-      <x:c r="H27"/>
-    </x:row>
-    <x:row r="28">
-      <x:c r="A28"/>
-      <x:c r="B28"/>
-      <x:c r="C28"/>
-      <x:c r="D28"/>
-      <x:c r="E28"/>
-      <x:c r="F28"/>
-      <x:c r="G28"/>
-      <x:c r="H28"/>
-    </x:row>
-    <x:row r="29">
-      <x:c r="A29"/>
-      <x:c r="B29"/>
-      <x:c r="C29"/>
-      <x:c r="D29"/>
-      <x:c r="E29"/>
-      <x:c r="F29"/>
-      <x:c r="G29"/>
-      <x:c r="H29"/>
-    </x:row>
-    <x:row r="30">
-      <x:c r="A30"/>
-      <x:c r="B30"/>
-      <x:c r="C30"/>
-      <x:c r="D30"/>
-      <x:c r="E30"/>
-      <x:c r="F30"/>
-      <x:c r="G30"/>
-      <x:c r="H30"/>
-    </x:row>
-    <x:row r="31">
-      <x:c r="A31"/>
-      <x:c r="B31"/>
-      <x:c r="C31"/>
-      <x:c r="D31"/>
-      <x:c r="E31"/>
-      <x:c r="F31"/>
-      <x:c r="G31"/>
-      <x:c r="H31"/>
-    </x:row>
-    <x:row r="32">
-      <x:c r="A32"/>
-      <x:c r="B32"/>
-      <x:c r="C32"/>
-      <x:c r="D32"/>
-      <x:c r="E32"/>
-      <x:c r="F32"/>
-      <x:c r="G32"/>
-      <x:c r="H32"/>
-    </x:row>
-    <x:row r="33">
-      <x:c r="A33"/>
-      <x:c r="B33"/>
-      <x:c r="C33"/>
-      <x:c r="D33"/>
-      <x:c r="E33"/>
-      <x:c r="F33"/>
-      <x:c r="G33"/>
-      <x:c r="H33"/>
-    </x:row>
-    <x:row r="34">
-      <x:c r="A34"/>
-      <x:c r="B34"/>
-      <x:c r="C34"/>
-      <x:c r="D34"/>
-      <x:c r="E34"/>
-      <x:c r="F34"/>
-      <x:c r="G34"/>
-      <x:c r="H34"/>
-    </x:row>
-    <x:row r="35">
-      <x:c r="A35"/>
-      <x:c r="B35"/>
-      <x:c r="C35"/>
-      <x:c r="D35"/>
-      <x:c r="E35"/>
-      <x:c r="F35"/>
-      <x:c r="G35"/>
-      <x:c r="H35"/>
-    </x:row>
-    <x:row r="36">
-      <x:c r="A36"/>
-      <x:c r="B36"/>
-      <x:c r="C36"/>
-      <x:c r="D36"/>
-      <x:c r="E36"/>
-      <x:c r="F36"/>
-      <x:c r="G36"/>
-      <x:c r="H36"/>
-    </x:row>
-    <x:row r="37">
-      <x:c r="A37"/>
-      <x:c r="B37"/>
-      <x:c r="C37"/>
-      <x:c r="D37"/>
-      <x:c r="E37"/>
-      <x:c r="F37"/>
-      <x:c r="G37"/>
-      <x:c r="H37"/>
-    </x:row>
-  </x:sheetData>
-  <x:mergeCells>
-    <x:mergeCell ref="A1:H2"/>
-    <x:mergeCell ref="A3:B3"/>
-    <x:mergeCell ref="C3:D3"/>
-    <x:mergeCell ref="E3:F3"/>
-    <x:mergeCell ref="G3:H3"/>
-    <x:mergeCell ref="A4:B4"/>
-    <x:mergeCell ref="C4:D4"/>
-    <x:mergeCell ref="E4:F4"/>
-    <x:mergeCell ref="G4:H4"/>
-    <x:mergeCell ref="A6:H6"/>
-  </x:mergeCells>
-  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</x:worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:sheetFormatPr defaultRowHeight="15"/>
-  <x:cols>
-    <x:col min="1" max="1" width="20" hidden="0" customWidth="1"/>
     <x:col min="2" max="2" width="28" hidden="0" customWidth="1"/>
     <x:col min="3" max="3" width="90" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="48" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="26" hidden="0" customWidth="1"/>
     <x:col min="6" max="6" width="34" hidden="0" customWidth="1"/>
     <x:col min="7" max="7" width="44" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="30" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="30" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1">
@@ -5180,8 +4349,8 @@
         <x:v>Company WorkHub</x:v>
       </x:c>
       <x:c r="C3" s="63"/>
-      <x:c r="D3" s="62" t="str">
-        <x:v>文書番号</x:v>
+      <x:c r="D3" s="246" t="str">
+        <x:v>章ID</x:v>
       </x:c>
       <x:c r="E3" s="63" t="str">
         <x:v>CW-BD-API-CMN-FLOW</x:v>
@@ -5194,14 +4363,14 @@
         <x:v>版数</x:v>
       </x:c>
       <x:c r="B4" s="63" t="str">
-        <x:v>Ver.1.8</x:v>
+        <x:v>Ver.2.5</x:v>
       </x:c>
       <x:c r="C4" s="63"/>
       <x:c r="D4" s="62" t="str">
         <x:v>改訂日</x:v>
       </x:c>
       <x:c r="E4" s="63" t="str">
-        <x:v>2026-08-12</x:v>
+        <x:v>2026-09-24</x:v>
       </x:c>
       <x:c r="F4" s="63"/>
       <x:c r="G4" s="63"/>
@@ -5236,8 +4405,8 @@
       <x:c r="C7" s="66" t="str">
         <x:v>処理概要</x:v>
       </x:c>
-      <x:c r="D7" s="66" t="str">
-        <x:v>Data範囲</x:v>
+      <x:c r="D7" s="257" t="str">
+        <x:v>認可参照</x:v>
       </x:c>
       <x:c r="E7" s="66" t="str">
         <x:v>Transaction</x:v>
@@ -5248,8 +4417,14 @@
       <x:c r="G7" s="66" t="str">
         <x:v>Log</x:v>
       </x:c>
-    </x:row>
-    <x:row r="8" ht="30" customHeight="1">
+      <x:c r="H7" s="203" t="str">
+        <x:v>関連Table</x:v>
+      </x:c>
+      <x:c r="I7" s="203" t="str">
+        <x:v>利用元・補足</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" ht="182" customHeight="1">
       <x:c r="A8" s="67" t="str">
         <x:v>API-AUTH-001</x:v>
       </x:c>
@@ -5257,22 +4432,30 @@
         <x:v>ログイン</x:v>
       </x:c>
       <x:c r="C8" s="67" t="str">
-        <x:v>1) 認証・権限・Data範囲を確認。2) body: username String(1..50), password String(1..100)を型・必須・桁・業務Ruleで検証。3) users,roles,permissions,login_histories / Redisを参照/更新。4) TX-AUTH-LOGINの境界でCommit/Rollback。5) accessToken, expiresIn, user{id,username,name,roles,permissions}を共通Response形式で返却。</x:v>
+        <x:v>1) 02の対応Permission/Data Scopeを判定。2) 23_API項目定義に従い入力を検証。3) users,roles,permissions,login_histories / Redisを参照/更新。4) TX-011の境界でCommit/Rollback。5) 23_API項目定義の正常Responseを返す。</x:v>
       </x:c>
       <x:c r="D8" s="67" t="str">
-        <x:v>未認証</x:v>
+        <x:v>02／13_API権限対応 API-AUTH-001
+Permission: -（認証/本人共通）
+Data Scope: DS-AUTH-001</x:v>
       </x:c>
       <x:c r="E8" s="67" t="str">
         <x:v>TX-011</x:v>
       </x:c>
       <x:c r="F8" s="67" t="str">
-        <x:v>AUTH-4001, AUTH-4004, AUTH-4005,COMMON-5000</x:v>
+        <x:v>AUTH-4001, AUTH-4004, AUTH-4005,COMMON-5000, AUTH-4290</x:v>
       </x:c>
       <x:c r="G8" s="67" t="str">
         <x:v>traceId付きLog。Password/Token/個人情報はMask</x:v>
       </x:c>
-    </x:row>
-    <x:row r="9" ht="30" customHeight="1">
+      <x:c r="H8" s="203" t="str">
+        <x:v>users,roles,permissions,login_histories / Redis</x:v>
+      </x:c>
+      <x:c r="I8" s="203" t="str">
+        <x:v>SCR-001</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" ht="117" customHeight="1">
       <x:c r="A9" s="67" t="str">
         <x:v>API-AUTH-002</x:v>
       </x:c>
@@ -5280,10 +4463,12 @@
         <x:v>ログアウト</x:v>
       </x:c>
       <x:c r="C9" s="67" t="str">
-        <x:v>1) 認証・権限・Data範囲を確認。2) header: Authorization; cookie: refreshTokenを型・必須・桁・業務Ruleで検証。3) refresh_tokens / Redisを参照/更新。4) TX-AUTH-LOGOUTの境界でCommit/Rollback。5) 204 No Contentを共通Response形式で返却。</x:v>
+        <x:v>1) 02の対応Permission/Data Scopeを判定。2) 23_API項目定義に従い入力を検証。3) refresh_tokens / Redisを参照/更新。4) TX-012の境界でCommit/Rollback。5) HTTP 204、Response Bodyなしで返却。</x:v>
       </x:c>
       <x:c r="D9" s="67" t="str">
-        <x:v>本人Tokenのみ</x:v>
+        <x:v>02／13_API権限対応 API-AUTH-002
+Permission: -（認証/本人共通）
+Data Scope: DS-AUTH-002</x:v>
       </x:c>
       <x:c r="E9" s="67" t="str">
         <x:v>TX-012</x:v>
@@ -5294,8 +4479,14 @@
       <x:c r="G9" s="67" t="str">
         <x:v>traceId付きLog。Password/Token/個人情報はMask</x:v>
       </x:c>
-    </x:row>
-    <x:row r="10" ht="30" customHeight="1">
+      <x:c r="H9" s="203" t="str">
+        <x:v>refresh_tokens / Redis</x:v>
+      </x:c>
+      <x:c r="I9" s="203" t="str">
+        <x:v>共通Header</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" ht="117" customHeight="1">
       <x:c r="A10" s="67" t="str">
         <x:v>API-AUTH-003</x:v>
       </x:c>
@@ -5303,10 +4494,12 @@
         <x:v>Token更新</x:v>
       </x:c>
       <x:c r="C10" s="67" t="str">
-        <x:v>1) 認証・権限・Data範囲を確認。2) cookie: refreshToken HttpOnlyを型・必須・桁・業務Ruleで検証。3) refresh_tokens / Redisを参照/更新。4) TX-AUTH-REFRESHの境界でCommit/Rollback。5) accessToken, expiresInを共通Response形式で返却。</x:v>
+        <x:v>1) 02の対応Permission/Data Scopeを判定。2) 23_API項目定義に従い入力を検証。3) refresh_tokens / Redisを参照/更新。4) TX-013の境界でCommit/Rollback。5) 23_API項目定義の正常Responseを返す。</x:v>
       </x:c>
       <x:c r="D10" s="67" t="str">
-        <x:v>有効・未失効Token</x:v>
+        <x:v>02／13_API権限対応 API-AUTH-003
+Permission: -（認証/本人共通）
+Data Scope: DS-AUTH-003</x:v>
       </x:c>
       <x:c r="E10" s="67" t="str">
         <x:v>TX-013</x:v>
@@ -5316,6 +4509,12 @@
       </x:c>
       <x:c r="G10" s="67" t="str">
         <x:v>traceId付きLog。Password/Token/個人情報はMask</x:v>
+      </x:c>
+      <x:c r="H10" s="203" t="str">
+        <x:v>refresh_tokens / Redis</x:v>
+      </x:c>
+      <x:c r="I10" s="203" t="str">
+        <x:v>共通Interceptor</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="30" customHeight="1">
@@ -5326,10 +4525,12 @@
         <x:v>現在ユーザー取得</x:v>
       </x:c>
       <x:c r="C11" s="67" t="str">
-        <x:v>1) 認証・権限・Data範囲を確認。2) なしを型・必須・桁・業務Ruleで検証。3) users,employees,roles,permissionsを参照/更新。4) 参照の境界でCommit/Rollback。5) user{id,employeeId,name,roles,permissions,menus}を共通Response形式で返却。</x:v>
+        <x:v>1) 02の対応Permission/Data Scopeを判定。2) 23_API項目定義に従い入力を検証。3) users,employees,roles,permissionsを参照。4) 業務Dataの更新なし。5) 23_API項目定義の正常Responseを返す。</x:v>
       </x:c>
       <x:c r="D11" s="67" t="str">
-        <x:v>本人</x:v>
+        <x:v>02／13_API権限対応 API-AUTH-004
+Permission: -（認証/本人共通）
+Data Scope: DS-AUTH-004</x:v>
       </x:c>
       <x:c r="E11" s="67" t="str">
         <x:v>参照</x:v>
@@ -5340,8 +4541,14 @@
       <x:c r="G11" s="67" t="str">
         <x:v>traceId付きLog。Password/Token/個人情報はMask</x:v>
       </x:c>
-    </x:row>
-    <x:row r="12" ht="30" customHeight="1">
+      <x:c r="H11" s="203" t="str">
+        <x:v>users,employees,roles,permissions</x:v>
+      </x:c>
+      <x:c r="I11" s="203" t="str">
+        <x:v>共通Layout</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" ht="143" customHeight="1">
       <x:c r="A12" s="67" t="str">
         <x:v>API-AUTH-005</x:v>
       </x:c>
@@ -5349,10 +4556,12 @@
         <x:v>パスワード変更</x:v>
       </x:c>
       <x:c r="C12" s="67" t="str">
-        <x:v>1) 認証・権限・Data範囲を確認。2) body: currentPassword String, newPassword String(8..64), confirmPassword Stringを型・必須・桁・業務Ruleで検証。3) users,refresh_tokens / Redisを参照/更新。4) TX-AUTH-PASSWORDの境界でCommit/Rollback。5) 204 No Contentを共通Response形式で返却。</x:v>
+        <x:v>1) 02の対応Permission/Data Scopeを判定。2) 23_API項目定義に従い入力を検証。3) users,refresh_tokens / Redisを参照/更新。4) TX-014の境界でCommit/Rollback。5) HTTP 204、Response Bodyなしで返却。</x:v>
       </x:c>
       <x:c r="D12" s="67" t="str">
-        <x:v>本人</x:v>
+        <x:v>02／13_API権限対応 API-AUTH-005
+Permission: -（認証/本人共通）
+Data Scope: DS-AUTH-005</x:v>
       </x:c>
       <x:c r="E12" s="67" t="str">
         <x:v>TX-014</x:v>
@@ -5363,8 +4572,14 @@
       <x:c r="G12" s="67" t="str">
         <x:v>traceId付きLog。Password/Token/個人情報はMask</x:v>
       </x:c>
-    </x:row>
-    <x:row r="13" ht="30" customHeight="1">
+      <x:c r="H12" s="203" t="str">
+        <x:v>users,refresh_tokens / Redis</x:v>
+      </x:c>
+      <x:c r="I12" s="203" t="str">
+        <x:v>SCR-026</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" ht="72" customHeight="1">
       <x:c r="A13" s="67" t="str">
         <x:v>API-DASH-001</x:v>
       </x:c>
@@ -5372,10 +4587,12 @@
         <x:v>ホーム集計取得</x:v>
       </x:c>
       <x:c r="C13" s="67" t="str">
-        <x:v>1) 認証・権限・Data範囲を確認。2) query: periodFrom Date, periodTo Dateを型・必須・桁・業務Ruleで検証。3) projects,tasks,daily_reports,notificationsを参照/更新。4) 参照の境界でCommit/Rollback。5) projectCount,taskStatusCounts,dueSoonCount,reportSubmittedCount,recentNotifications[]を共通Response形式で返却。</x:v>
+        <x:v>1) 認証後、PERM-DASH-READとRole別Data範囲を確認。2) periodFrom/periodTo省略時は当月初日/当日を補完し、実在日・開始&lt;=終了・最大366日を検証。3) 02／13_API権限対応 API-DASH-001のData Scopeで絞り込む。4) projectCount=指定期間と日程重複するPJ、taskStatusCounts=due_dateが期間内のTask、reportSubmittedCount=report_dateが期間内、dueSoonCount=System日～3日後の未完了Task、recentNotifications=本人の最新5件を集計。5) 共通Response形式で返却。</x:v>
       </x:c>
       <x:c r="D13" s="67" t="str">
-        <x:v>ADMIN=全社, PM=担当PJ, EMP=本人・参加PJ</x:v>
+        <x:v>02／13_API権限対応 API-DASH-001
+Permission: PERM-DASH-READ
+Data Scope: DS-DASH-001</x:v>
       </x:c>
       <x:c r="E13" s="67" t="str">
         <x:v>参照</x:v>
@@ -5385,6 +4602,12 @@
       </x:c>
       <x:c r="G13" s="67" t="str">
         <x:v>traceId付きLog。Password/Token/個人情報はMask</x:v>
+      </x:c>
+      <x:c r="H13" s="203" t="str">
+        <x:v>projects,project_members,tasks,daily_reports,notifications</x:v>
+      </x:c>
+      <x:c r="I13" s="203" t="str">
+        <x:v>SCR-002</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="30" customHeight="1">
@@ -5395,10 +4618,12 @@
         <x:v>部門選択肢</x:v>
       </x:c>
       <x:c r="C14" s="67" t="str">
-        <x:v>1) 認証・権限・Data範囲を確認。2) query: activeOnly Boolean=trueを型・必須・桁・業務Ruleで検証。3) departments / Redisを参照/更新。4) 参照の境界でCommit/Rollback。5) departments[{id,code,name,parentId}]を共通Response形式で返却。</x:v>
+        <x:v>1) 02の対応Permission/Data Scopeを判定。2) 23_API項目定義に従い入力を検証。3) departments / Redisを参照。4) 業務Dataの更新なし。5) 23_API項目定義の正常Responseを返す。</x:v>
       </x:c>
       <x:c r="D14" s="67" t="str">
-        <x:v>有効部門</x:v>
+        <x:v>02／13_API権限対応 API-MST-001
+Permission: -（認証/本人共通）
+Data Scope: DS-MST-001</x:v>
       </x:c>
       <x:c r="E14" s="67" t="str">
         <x:v>参照</x:v>
@@ -5409,8 +4634,14 @@
       <x:c r="G14" s="67" t="str">
         <x:v>traceId付きLog。Password/Token/個人情報はMask</x:v>
       </x:c>
-    </x:row>
-    <x:row r="15" ht="30" customHeight="1">
+      <x:c r="H14" s="203" t="str">
+        <x:v>departments / Redis</x:v>
+      </x:c>
+      <x:c r="I14" s="203" t="str">
+        <x:v>SCR-003, SCR-004, SCR-007, SCR-021</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" ht="222" customHeight="1">
       <x:c r="A15" s="67" t="str">
         <x:v>API-MST-002</x:v>
       </x:c>
@@ -5418,20 +4649,31 @@
         <x:v>社員選択肢</x:v>
       </x:c>
       <x:c r="C15" s="67" t="str">
-        <x:v>1) 認証・権限・Data範囲を確認。2) query: projectId Long?, keyword String?, activeOnly Boolean=trueを型・必須・桁・業務Ruleで検証。3) employees,project_membersを参照/更新。4) 参照の境界でCommit/Rollback。5) employees[{id,code,name,departmentId}]を共通Response形式で返却。</x:v>
+        <x:v>02／14_DataScope定義 DS-MST-002に従い候補を抽出。TASK_ASSIGNEEは指定PJの在籍ACTIVE Memberのみ。候補用途はid/employeeCode/name/departmentId/departmentNameだけを返し、nameKana/emailはNull。社員詳細閲覧権限は拡大しない。社員番号昇順、0件は[]。</x:v>
       </x:c>
       <x:c r="D15" s="67" t="str">
-        <x:v>ADMIN=全社, PM=担当PJ候補</x:v>
+        <x:v>02／13_API権限対応 API-MST-002
+Permission: DEFAULT:PERM-EMP-READ / PROJECT_PM:PERM-PRJ-WRITE / PROJECT_MEMBER:PERM-MEMBER-WRITE / TASK_ASSIGNEE:PERM-TASK-WRITE
+Data Scope: DS-MST-002</x:v>
       </x:c>
       <x:c r="E15" s="67" t="str">
         <x:v>参照</x:v>
       </x:c>
       <x:c r="F15" s="67" t="str">
-        <x:v>AUTH-4006</x:v>
+        <x:v>COMMON-4000, AUTH-4006</x:v>
       </x:c>
       <x:c r="G15" s="67" t="str">
         <x:v>traceId付きLog。Password/Token/個人情報はMask</x:v>
       </x:c>
+      <x:c r="H15" s="241" t="str">
+        <x:v>employees,project_members</x:v>
+      </x:c>
+      <x:c r="I15" s="241" t="str">
+        <x:v>SCR-007, SCR-009, SCR-012, SCR-013, SCR-015, SCR-021</x:v>
+      </x:c>
+      <x:c r="J15" s="241"/>
+      <x:c r="K15" s="241"/>
+      <x:c r="L15" s="241"/>
     </x:row>
     <x:row r="16" ht="30" customHeight="1">
       <x:c r="A16" s="67" t="str">
@@ -5441,10 +4683,12 @@
         <x:v>PJ選択肢</x:v>
       </x:c>
       <x:c r="C16" s="67" t="str">
-        <x:v>1) 認証・権限・Data範囲を確認。2) query: activeOnly Boolean=trueを型・必須・桁・業務Ruleで検証。3) projects,project_membersを参照/更新。4) 参照の境界でCommit/Rollback。5) projects[{id,code,name,role}]を共通Response形式で返却。</x:v>
+        <x:v>1) 02の対応Permission/Data Scopeを判定。2) 23_API項目定義に従い入力を検証。3) projects,project_membersを参照。4) 業務Dataの更新なし。5) 23_API項目定義の正常Responseを返す。</x:v>
       </x:c>
       <x:c r="D16" s="67" t="str">
-        <x:v>権限範囲内PJ</x:v>
+        <x:v>02／13_API権限対応 API-MST-003
+Permission: PERM-PRJ-READ
+Data Scope: DS-MST-003</x:v>
       </x:c>
       <x:c r="E16" s="67" t="str">
         <x:v>参照</x:v>
@@ -5454,6 +4698,12 @@
       </x:c>
       <x:c r="G16" s="67" t="str">
         <x:v>traceId付きLog。Password/Token/個人情報はMask</x:v>
+      </x:c>
+      <x:c r="H16" s="203" t="str">
+        <x:v>projects,project_members</x:v>
+      </x:c>
+      <x:c r="I16" s="203" t="str">
+        <x:v>SCR-013, SCR-015, SCR-018, SCR-019, SCR-020, SCR-021</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="30" customHeight="1">
@@ -5464,10 +4714,12 @@
         <x:v>Role/権限選択肢</x:v>
       </x:c>
       <x:c r="C17" s="67" t="str">
-        <x:v>1) 認証・権限・Data範囲を確認。2) なしを型・必須・桁・業務Ruleで検証。3) roles,permissionsを参照/更新。4) 参照の境界でCommit/Rollback。5) roles[],permissions[]を共通Response形式で返却。</x:v>
+        <x:v>1) 02の対応Permission/Data Scopeを判定。2) 23_API項目定義に従い入力を検証。3) roles,permissionsを参照。4) 業務Dataの更新なし。5) 23_API項目定義の正常Responseを返す。</x:v>
       </x:c>
       <x:c r="D17" s="67" t="str">
-        <x:v>管理者のみ</x:v>
+        <x:v>02／13_API権限対応 API-MST-004
+Permission: PERM-ROLE-ADMIN
+Data Scope: DS-MST-004</x:v>
       </x:c>
       <x:c r="E17" s="67" t="str">
         <x:v>参照</x:v>
@@ -5477,6 +4729,12 @@
       </x:c>
       <x:c r="G17" s="67" t="str">
         <x:v>traceId付きLog。Password/Token/個人情報はMask</x:v>
+      </x:c>
+      <x:c r="H17" s="203" t="str">
+        <x:v>roles,permissions</x:v>
+      </x:c>
+      <x:c r="I17" s="203" t="str">
+        <x:v>SCR-004, SCR-023, SCR-024</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="30" customHeight="1">
@@ -5487,10 +4745,12 @@
         <x:v>ユーザー検索</x:v>
       </x:c>
       <x:c r="C18" s="67" t="str">
-        <x:v>1) 認証・権限・Data範囲を確認。2) query: username,name,status,locked,page,size,sortを型・必須・桁・業務Ruleで検証。3) users,employees,user_roles,rolesを参照/更新。4) 参照の境界でCommit/Rollback。5) Page&lt;UserSummary&gt;を共通Response形式で返却。</x:v>
+        <x:v>1) 02の対応Permission/Data Scopeを判定。2) 23_API項目定義に従い入力を検証。3) users,employees,user_roles,rolesを参照。4) 業務Dataの更新なし。5) 23_API項目定義の正常Responseを返す。</x:v>
       </x:c>
       <x:c r="D18" s="67" t="str">
-        <x:v>管理者のみ</x:v>
+        <x:v>02／13_API権限対応 API-USR-001
+Permission: PERM-USER-ADMIN
+Data Scope: DS-USR-001</x:v>
       </x:c>
       <x:c r="E18" s="67" t="str">
         <x:v>参照</x:v>
@@ -5500,6 +4760,12 @@
       </x:c>
       <x:c r="G18" s="67" t="str">
         <x:v>traceId付きLog。Password/Token/個人情報はMask</x:v>
+      </x:c>
+      <x:c r="H18" s="203" t="str">
+        <x:v>users,employees,user_roles,roles</x:v>
+      </x:c>
+      <x:c r="I18" s="203" t="str">
+        <x:v>SCR-023</x:v>
       </x:c>
     </x:row>
     <x:row r="19" ht="30" customHeight="1">
@@ -5510,10 +4776,12 @@
         <x:v>ユーザー詳細</x:v>
       </x:c>
       <x:c r="C19" s="67" t="str">
-        <x:v>1) 認証・権限・Data範囲を確認。2) path: id Longを型・必須・桁・業務Ruleで検証。3) users,employees,user_roles,rolesを参照/更新。4) 参照の境界でCommit/Rollback。5) id,username,employee,status,lockedUntil,roles,versionを共通Response形式で返却。</x:v>
+        <x:v>1) 02の対応Permission/Data Scopeを判定。2) 23_API項目定義に従い入力を検証。3) users,employees,user_roles,rolesを参照。4) 業務Dataの更新なし。5) 23_API項目定義の正常Responseを返す。</x:v>
       </x:c>
       <x:c r="D19" s="67" t="str">
-        <x:v>管理者のみ</x:v>
+        <x:v>02／13_API権限対応 API-USR-002
+Permission: PERM-USER-ADMIN
+Data Scope: DS-USR-002</x:v>
       </x:c>
       <x:c r="E19" s="67" t="str">
         <x:v>参照</x:v>
@@ -5524,8 +4792,14 @@
       <x:c r="G19" s="67" t="str">
         <x:v>traceId付きLog。Password/Token/個人情報はMask</x:v>
       </x:c>
-    </x:row>
-    <x:row r="20" ht="30" customHeight="1">
+      <x:c r="H19" s="203" t="str">
+        <x:v>users,employees,user_roles,roles</x:v>
+      </x:c>
+      <x:c r="I19" s="203" t="str">
+        <x:v>SCR-023</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" ht="138" customHeight="1">
       <x:c r="A20" s="67" t="str">
         <x:v>API-USR-003</x:v>
       </x:c>
@@ -5533,10 +4807,12 @@
         <x:v>ユーザー状態・Role更新</x:v>
       </x:c>
       <x:c r="C20" s="67" t="str">
-        <x:v>1) 認証・権限・Data範囲を確認。2) path: id; body: enabled Boolean, roleIds Long[], version Integerを型・必須・桁・業務Ruleで検証。3) users,user_roles,operation_logs / Redisを参照/更新。4) TX-ROLE-USERの境界でCommit/Rollback。5) id,enabled,roles,versionを共通Response形式で返却。</x:v>
+        <x:v>ADMIN・対象/version確認。有効内蔵Roleを1つ以上、全RoleがACTIVE、重複IDなし。自身停止/ADMIN剥奪、最後の有効ADMIN消失、PLANNING/IN_PROGRESS/SUSPENDEDの現PMからROLE-PM削除または停止は禁止(COMMON-4000)。TX-010でRole/User割当を排他・更新・監査、Commit後Cache/Sessionへ反映。</x:v>
       </x:c>
       <x:c r="D20" s="67" t="str">
-        <x:v>管理者のみ; 自身のADMIN剥奪禁止</x:v>
+        <x:v>02／13_API権限対応 API-USR-003
+Permission: PERM-USER-ADMIN
+Data Scope: DS-USR-003</x:v>
       </x:c>
       <x:c r="E20" s="67" t="str">
         <x:v>TX-010</x:v>
@@ -5547,8 +4823,17 @@
       <x:c r="G20" s="67" t="str">
         <x:v>traceId付きLog。Password/Token/個人情報はMask</x:v>
       </x:c>
-    </x:row>
-    <x:row r="21" ht="30" customHeight="1">
+      <x:c r="H20" s="241" t="str">
+        <x:v>users,user_roles,operation_logs / Redis</x:v>
+      </x:c>
+      <x:c r="I20" s="241" t="str">
+        <x:v>SCR-023</x:v>
+      </x:c>
+      <x:c r="J20" s="241"/>
+      <x:c r="K20" s="241"/>
+      <x:c r="L20" s="241"/>
+    </x:row>
+    <x:row r="21" ht="166" customHeight="1">
       <x:c r="A21" s="67" t="str">
         <x:v>API-USR-004</x:v>
       </x:c>
@@ -5556,10 +4841,13 @@
         <x:v>パスワードリセット</x:v>
       </x:c>
       <x:c r="C21" s="67" t="str">
-        <x:v>1) 認証・権限・Data範囲を確認。2) path: id; header: X-Idempotency-Keyを型・必須・桁・業務Ruleで検証。3) users,refresh_tokens,operation_logs / Redisを参照/更新。4) TX-PASSWORD-RESETの境界でCommit/Rollback。5) temporaryPassword（一回表示）を共通Response形式で返却。</x:v>
+        <x:v>1) 02の対応Permission/Data Scopeを判定。2) 23_API項目定義に従い入力を検証。3) users,refresh_tokens,operation_logs / Redisを参照/更新。4) TX-014の境界でCommit/Rollback。5) 23_API項目定義の正常Responseを返す。
+再送はBR-API-002。初回だけ一時Password、同Key再送はNull、Reset再実行なし。</x:v>
       </x:c>
       <x:c r="D21" s="67" t="str">
-        <x:v>管理者のみ; 有効User</x:v>
+        <x:v>02／13_API権限対応 API-USR-004
+Permission: PERM-USER-ADMIN
+Data Scope: DS-USR-004</x:v>
       </x:c>
       <x:c r="E21" s="67" t="str">
         <x:v>TX-014</x:v>
@@ -5570,6 +4858,15 @@
       <x:c r="G21" s="67" t="str">
         <x:v>traceId付きLog。Password/Token/個人情報はMask</x:v>
       </x:c>
+      <x:c r="H21" s="241" t="str">
+        <x:v>users,refresh_tokens,operation_logs / Redis</x:v>
+      </x:c>
+      <x:c r="I21" s="241" t="str">
+        <x:v>SCR-023</x:v>
+      </x:c>
+      <x:c r="J21" s="241"/>
+      <x:c r="K21" s="241"/>
+      <x:c r="L21" s="241"/>
     </x:row>
     <x:row r="22" ht="30" customHeight="1">
       <x:c r="A22" s="67" t="str">
@@ -5579,10 +4876,12 @@
         <x:v>Role一覧</x:v>
       </x:c>
       <x:c r="C22" s="67" t="str">
-        <x:v>1) 認証・権限・Data範囲を確認。2) query: status,page,sizeを型・必須・桁・業務Ruleで検証。3) roles,role_permissionsを参照/更新。4) 参照の境界でCommit/Rollback。5) Page&lt;RoleSummary&gt;を共通Response形式で返却。</x:v>
+        <x:v>1) 02の対応Permission/Data Scopeを判定。2) 23_API項目定義に従い入力を検証。3) roles,role_permissionsを参照。4) 業務Dataの更新なし。5) 23_API項目定義の正常Responseを返す。</x:v>
       </x:c>
       <x:c r="D22" s="67" t="str">
-        <x:v>管理者のみ</x:v>
+        <x:v>02／13_API権限対応 API-ROLE-001
+Permission: PERM-ROLE-ADMIN
+Data Scope: DS-ROLE-001</x:v>
       </x:c>
       <x:c r="E22" s="67" t="str">
         <x:v>参照</x:v>
@@ -5592,6 +4891,12 @@
       </x:c>
       <x:c r="G22" s="67" t="str">
         <x:v>traceId付きLog。Password/Token/個人情報はMask</x:v>
+      </x:c>
+      <x:c r="H22" s="203" t="str">
+        <x:v>roles,role_permissions</x:v>
+      </x:c>
+      <x:c r="I22" s="203" t="str">
+        <x:v>SCR-024</x:v>
       </x:c>
     </x:row>
     <x:row r="23" ht="30" customHeight="1">
@@ -5602,10 +4907,12 @@
         <x:v>Role詳細</x:v>
       </x:c>
       <x:c r="C23" s="67" t="str">
-        <x:v>1) 認証・権限・Data範囲を確認。2) path: id Longを型・必須・桁・業務Ruleで検証。3) roles,role_permissions,permissionsを参照/更新。4) 参照の境界でCommit/Rollback。5) id,roleCode,roleName,description,status,permissionIds,versionを共通Response形式で返却。</x:v>
+        <x:v>1) 02の対応Permission/Data Scopeを判定。2) 23_API項目定義に従い入力を検証。3) roles,role_permissions,permissionsを参照。4) 業務Dataの更新なし。5) 23_API項目定義の正常Responseを返す。</x:v>
       </x:c>
       <x:c r="D23" s="67" t="str">
-        <x:v>管理者のみ</x:v>
+        <x:v>02／13_API権限対応 API-ROLE-002
+Permission: PERM-ROLE-ADMIN
+Data Scope: DS-ROLE-002</x:v>
       </x:c>
       <x:c r="E23" s="67" t="str">
         <x:v>参照</x:v>
@@ -5616,8 +4923,14 @@
       <x:c r="G23" s="67" t="str">
         <x:v>traceId付きLog。Password/Token/個人情報はMask</x:v>
       </x:c>
-    </x:row>
-    <x:row r="24" ht="30" customHeight="1">
+      <x:c r="H23" s="203" t="str">
+        <x:v>roles,role_permissions,permissions</x:v>
+      </x:c>
+      <x:c r="I23" s="203" t="str">
+        <x:v>SCR-024</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24" ht="182" customHeight="1">
       <x:c r="A24" s="67" t="str">
         <x:v>API-ROLE-003</x:v>
       </x:c>
@@ -5625,10 +4938,12 @@
         <x:v>Role登録</x:v>
       </x:c>
       <x:c r="C24" s="67" t="str">
-        <x:v>1) 認証・権限・Data範囲を確認。2) body: roleCode String(1..50),roleName String(1..100),description String(0..500),permissionIds[]; header: X-Idempotency-Keyを型・必須・桁・業務Ruleで検証。3) roles,role_permissions,operation_logsを参照/更新。4) TX-ROLEの境界でCommit/Rollback。5) id,roleCode,versionを共通Response形式で返却。</x:v>
+        <x:v>1) 02の対応Permission/Data Scopeを判定。2) 23_API項目定義に従い入力を検証。3) roles,role_permissions,operation_logsを参照/更新。4) TX-008の境界でCommit/Rollback。5) 23_API項目定義の正常Responseを返す。</x:v>
       </x:c>
       <x:c r="D24" s="67" t="str">
-        <x:v>管理者のみ</x:v>
+        <x:v>02／13_API権限対応 API-ROLE-003
+Permission: PERM-ROLE-ADMIN
+Data Scope: DS-ROLE-003</x:v>
       </x:c>
       <x:c r="E24" s="67" t="str">
         <x:v>TX-008</x:v>
@@ -5639,8 +4954,14 @@
       <x:c r="G24" s="67" t="str">
         <x:v>traceId付きLog。Password/Token/個人情報はMask</x:v>
       </x:c>
-    </x:row>
-    <x:row r="25" ht="30" customHeight="1">
+      <x:c r="H24" s="203" t="str">
+        <x:v>roles,role_permissions,operation_logs</x:v>
+      </x:c>
+      <x:c r="I24" s="203" t="str">
+        <x:v>SCR-024</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25" ht="124" customHeight="1">
       <x:c r="A25" s="67" t="str">
         <x:v>API-ROLE-004</x:v>
       </x:c>
@@ -5648,10 +4969,12 @@
         <x:v>Role更新</x:v>
       </x:c>
       <x:c r="C25" s="67" t="str">
-        <x:v>1) 認証・権限・Data範囲を確認。2) path: id; body: roleName,description,permissionIds[],versionを型・必須・桁・業務Ruleで検証。3) roles,role_permissions,operation_logs / Redisを参照/更新。4) TX-ROLEの境界でCommit/Rollback。5) id,status,permissionIds,versionを共通Response形式で返却。</x:v>
+        <x:v>認証/ADMIN・存在/version確認。全RoleのCodeは更新対象外。組込Roleは既存と同一permissionIdsのみ受付し名称/説明を変更。カスタムRoleは有効Permissionを置換。違反COMMON-4000。TX-008で監査まで一括Commit、失敗全Rollback。Commit後Cache失効。</x:v>
       </x:c>
       <x:c r="D25" s="67" t="str">
-        <x:v>組込Role Code変更禁止</x:v>
+        <x:v>02／13_API権限対応 API-ROLE-004
+Permission: PERM-ROLE-ADMIN
+Data Scope: DS-ROLE-004</x:v>
       </x:c>
       <x:c r="E25" s="67" t="str">
         <x:v>TX-008</x:v>
@@ -5662,8 +4985,17 @@
       <x:c r="G25" s="67" t="str">
         <x:v>traceId付きLog。Password/Token/個人情報はMask</x:v>
       </x:c>
-    </x:row>
-    <x:row r="26" ht="30" customHeight="1">
+      <x:c r="H25" s="241" t="str">
+        <x:v>roles,role_permissions,operation_logs / Redis</x:v>
+      </x:c>
+      <x:c r="I25" s="241" t="str">
+        <x:v>SCR-024</x:v>
+      </x:c>
+      <x:c r="J25" s="241"/>
+      <x:c r="K25" s="241"/>
+      <x:c r="L25" s="241"/>
+    </x:row>
+    <x:row r="26" ht="110" customHeight="1">
       <x:c r="A26" s="67" t="str">
         <x:v>API-ROLE-005</x:v>
       </x:c>
@@ -5671,20 +5003,31 @@
         <x:v>Role状態変更</x:v>
       </x:c>
       <x:c r="C26" s="67" t="str">
-        <x:v>1) 認証・権限・Data範囲を確認。2) path: id; body: status,versionを型・必須・桁・業務Ruleで検証。3) roles,user_roles,operation_logs / Redisを参照/更新。4) TX-ROLEの境界でCommit/Rollback。5) id,status,versionを共通Response形式で返却。</x:v>
+        <x:v>認証/ADMIN・存在/version確認。組込Roleは状態変更不可。カスタムRoleはACTIVE↔DISABLED、同状態不可。停止時user_rolesが1件でもあればCOMMON-4000（停止User含む）。TX-008でRole行を排他し割当と競合制御、成功後Cache失効。失敗旧状態保持。</x:v>
       </x:c>
       <x:c r="D26" s="67" t="str">
-        <x:v>使用中Role停止時確認</x:v>
+        <x:v>02／13_API権限対応 API-ROLE-005
+Permission: PERM-ROLE-ADMIN
+Data Scope: DS-ROLE-005</x:v>
       </x:c>
       <x:c r="E26" s="67" t="str">
         <x:v>TX-008</x:v>
       </x:c>
       <x:c r="F26" s="67" t="str">
-        <x:v>COMMON-4040, COMMON-4090</x:v>
+        <x:v>COMMON-4000, COMMON-4040, COMMON-4090</x:v>
       </x:c>
       <x:c r="G26" s="67" t="str">
         <x:v>traceId付きLog。Password/Token/個人情報はMask</x:v>
       </x:c>
+      <x:c r="H26" s="241" t="str">
+        <x:v>roles,user_roles,operation_logs / Redis</x:v>
+      </x:c>
+      <x:c r="I26" s="241" t="str">
+        <x:v>SCR-024</x:v>
+      </x:c>
+      <x:c r="J26" s="241"/>
+      <x:c r="K26" s="241"/>
+      <x:c r="L26" s="241"/>
     </x:row>
     <x:row r="27" ht="30" customHeight="1">
       <x:c r="A27" s="67" t="str">
@@ -5694,10 +5037,12 @@
         <x:v>操作Log検索</x:v>
       </x:c>
       <x:c r="C27" s="67" t="str">
-        <x:v>1) 認証・権限・Data範囲を確認。2) query: from,to,userId,module,action,result,traceId,page,size,sortを型・必須・桁・業務Ruleで検証。3) operation_logsを参照/更新。4) 参照の境界でCommit/Rollback。5) Page&lt;OperationLogSummary&gt;を共通Response形式で返却。</x:v>
+        <x:v>1) 02の対応Permission/Data Scopeを判定。2) 23_API項目定義に従い入力を検証。3) operation_logsを参照。4) 業務Dataの更新なし。5) 23_API項目定義の正常Responseを返す。</x:v>
       </x:c>
       <x:c r="D27" s="67" t="str">
-        <x:v>管理者のみ</x:v>
+        <x:v>02／13_API権限対応 API-LOG-001
+Permission: PERM-LOG-READ
+Data Scope: DS-LOG-001</x:v>
       </x:c>
       <x:c r="E27" s="67" t="str">
         <x:v>参照</x:v>
@@ -5707,6 +5052,12 @@
       </x:c>
       <x:c r="G27" s="67" t="str">
         <x:v>traceId付きLog。Password/Token/個人情報はMask</x:v>
+      </x:c>
+      <x:c r="H27" s="203" t="str">
+        <x:v>operation_logs</x:v>
+      </x:c>
+      <x:c r="I27" s="203" t="str">
+        <x:v>SCR-025</x:v>
       </x:c>
     </x:row>
     <x:row r="28" ht="30" customHeight="1">
@@ -5717,10 +5068,12 @@
         <x:v>操作Log詳細</x:v>
       </x:c>
       <x:c r="C28" s="67" t="str">
-        <x:v>1) 認証・権限・Data範囲を確認。2) path: id Longを型・必須・桁・業務Ruleで検証。3) operation_logsを参照/更新。4) 参照の境界でCommit/Rollback。5) マスキング済Log詳細を共通Response形式で返却。</x:v>
+        <x:v>1) 02の対応Permission/Data Scopeを判定。2) 23_API項目定義に従い入力を検証。3) operation_logsを参照。4) 業務Dataの更新なし。5) 23_API項目定義の正常Responseを返す。</x:v>
       </x:c>
       <x:c r="D28" s="67" t="str">
-        <x:v>管理者のみ</x:v>
+        <x:v>02／13_API権限対応 API-LOG-002
+Permission: PERM-LOG-READ
+Data Scope: DS-LOG-002</x:v>
       </x:c>
       <x:c r="E28" s="67" t="str">
         <x:v>参照</x:v>
@@ -5730,6 +5083,12 @@
       </x:c>
       <x:c r="G28" s="67" t="str">
         <x:v>traceId付きLog。Password/Token/個人情報はMask</x:v>
+      </x:c>
+      <x:c r="H28" s="203" t="str">
+        <x:v>operation_logs</x:v>
+      </x:c>
+      <x:c r="I28" s="203" t="str">
+        <x:v>SCR-025</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -5741,7 +5100,7 @@
 </x:worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
@@ -5796,8 +5155,8 @@
       <x:c r="C3" s="139"/>
       <x:c r="D3" s="139"/>
       <x:c r="E3" s="139"/>
-      <x:c r="F3" s="174" t="str">
-        <x:v>文書番号</x:v>
+      <x:c r="F3" s="246" t="str">
+        <x:v>章ID</x:v>
       </x:c>
       <x:c r="G3" s="139" t="str">
         <x:v>CW-BD-10-FIELD</x:v>
@@ -5811,8 +5170,8 @@
       <x:c r="A4" s="174" t="str">
         <x:v>版数</x:v>
       </x:c>
-      <x:c r="B4" s="139" t="str">
-        <x:v>Ver.1.8</x:v>
+      <x:c r="B4" s="63" t="str">
+        <x:v>Ver.2.5</x:v>
       </x:c>
       <x:c r="C4" s="139"/>
       <x:c r="D4" s="139"/>
@@ -5820,8 +5179,8 @@
       <x:c r="F4" s="174" t="str">
         <x:v>改訂日</x:v>
       </x:c>
-      <x:c r="G4" s="139" t="str">
-        <x:v>2026-08-12</x:v>
+      <x:c r="G4" s="63" t="str">
+        <x:v>2026-09-24</x:v>
       </x:c>
       <x:c r="H4" s="139"/>
       <x:c r="I4" s="139"/>
@@ -6487,10 +5846,10 @@
         <x:v>response.body</x:v>
       </x:c>
       <x:c r="E25" s="67" t="str">
-        <x:v>Null</x:v>
+        <x:v>Bodyなし</x:v>
       </x:c>
       <x:c r="F25" s="67" t="str">
-        <x:v>任意</x:v>
+        <x:v>送信禁止</x:v>
       </x:c>
       <x:c r="G25" s="67" t="str">
         <x:v>-</x:v>
@@ -6499,10 +5858,10 @@
         <x:v>No Content</x:v>
       </x:c>
       <x:c r="I25" s="67" t="str">
-        <x:v>可</x:v>
+        <x:v>該当なし</x:v>
       </x:c>
       <x:c r="J25" s="67" t="str">
-        <x:v>Response Bodyなし</x:v>
+        <x:v>HTTP 204。JSON null、Envelope、空Objectを送信しない。</x:v>
       </x:c>
       <x:c r="K25" s="67" t="str">
         <x:v>-</x:v>
@@ -7327,10 +6686,10 @@
         <x:v>response.body</x:v>
       </x:c>
       <x:c r="E49" s="67" t="str">
-        <x:v>Null</x:v>
+        <x:v>Bodyなし</x:v>
       </x:c>
       <x:c r="F49" s="67" t="str">
-        <x:v>任意</x:v>
+        <x:v>送信禁止</x:v>
       </x:c>
       <x:c r="G49" s="67" t="str">
         <x:v>-</x:v>
@@ -7339,10 +6698,10 @@
         <x:v>No Content</x:v>
       </x:c>
       <x:c r="I49" s="67" t="str">
-        <x:v>可</x:v>
+        <x:v>該当なし</x:v>
       </x:c>
       <x:c r="J49" s="67" t="str">
-        <x:v>Response Bodyなし</x:v>
+        <x:v>HTTP 204。JSON null、Envelope、空Objectを送信しない。</x:v>
       </x:c>
       <x:c r="K49" s="67" t="str">
         <x:v>-</x:v>
@@ -7377,7 +6736,7 @@
         <x:v>可</x:v>
       </x:c>
       <x:c r="J50" s="67" t="str">
-        <x:v>periodFrom</x:v>
+        <x:v>省略時は当月初日。periodToとの期間は最大366日</x:v>
       </x:c>
       <x:c r="K50" s="67" t="str">
         <x:v>Service DTO.period_from</x:v>
@@ -7412,7 +6771,7 @@
         <x:v>可</x:v>
       </x:c>
       <x:c r="J51" s="67" t="str">
-        <x:v>periodTo</x:v>
+        <x:v>省略時は当日。periodFromとの期間は最大366日</x:v>
       </x:c>
       <x:c r="K51" s="67" t="str">
         <x:v>Service DTO.period_to</x:v>
@@ -7622,10 +6981,10 @@
         <x:v>不可</x:v>
       </x:c>
       <x:c r="J57" s="67" t="str">
-        <x:v>参加PJ数</x:v>
+        <x:v>指定期間と日程が重複する権限範囲PJ数</x:v>
       </x:c>
       <x:c r="K57" s="67" t="str">
-        <x:v>projects集計</x:v>
+        <x:v>AGGREGATE: projects.start_date&lt;=:periodTo AND (projects.end_date IS NULL OR projects.end_date&gt;=:periodFrom) + Role範囲</x:v>
       </x:c>
     </x:row>
     <x:row r="58" ht="15" hidden="0" customHeight="1">
@@ -7657,10 +7016,10 @@
         <x:v>不可</x:v>
       </x:c>
       <x:c r="J58" s="67" t="str">
-        <x:v>Task状態別件数</x:v>
+        <x:v>期限日が指定期間内のTask状態別件数</x:v>
       </x:c>
       <x:c r="K58" s="67" t="str">
-        <x:v>tasks集計</x:v>
+        <x:v>AGGREGATE: tasks.due_date BETWEEN :periodFrom AND :periodTo + Role範囲 + deleted=false</x:v>
       </x:c>
     </x:row>
     <x:row r="59" ht="15" hidden="0" customHeight="1">
@@ -7695,7 +7054,7 @@
         <x:v>todo件数</x:v>
       </x:c>
       <x:c r="K59" s="67" t="str">
-        <x:v>AGGREGATE: COUNT(tasks.id) WHERE tasks.status = 'TODO'</x:v>
+        <x:v>AGGREGATE: 上記Task範囲 AND tasks.status='TODO'</x:v>
       </x:c>
     </x:row>
     <x:row r="60" ht="15" hidden="0" customHeight="1">
@@ -7730,7 +7089,7 @@
         <x:v>inProgress件数</x:v>
       </x:c>
       <x:c r="K60" s="67" t="str">
-        <x:v>AGGREGATE: COUNT(tasks.id) WHERE tasks.status = 'IN_PROGRESS'</x:v>
+        <x:v>AGGREGATE: 上記Task範囲 AND tasks.status='IN_PROGRESS'</x:v>
       </x:c>
     </x:row>
     <x:row r="61" ht="15" hidden="0" customHeight="1">
@@ -7765,7 +7124,7 @@
         <x:v>review件数</x:v>
       </x:c>
       <x:c r="K61" s="67" t="str">
-        <x:v>AGGREGATE: COUNT(tasks.id) WHERE tasks.status = 'REVIEW'</x:v>
+        <x:v>AGGREGATE: 上記Task範囲 AND tasks.status='REVIEW'</x:v>
       </x:c>
     </x:row>
     <x:row r="62" ht="15" hidden="0" customHeight="1">
@@ -7800,7 +7159,7 @@
         <x:v>completed件数</x:v>
       </x:c>
       <x:c r="K62" s="67" t="str">
-        <x:v>AGGREGATE: COUNT(tasks.id) WHERE tasks.status = 'COMPLETED'</x:v>
+        <x:v>AGGREGATE: 上記Task範囲 AND tasks.status='COMPLETED'</x:v>
       </x:c>
     </x:row>
     <x:row r="63" ht="15" hidden="0" customHeight="1">
@@ -7835,7 +7194,7 @@
         <x:v>cancelled件数</x:v>
       </x:c>
       <x:c r="K63" s="67" t="str">
-        <x:v>AGGREGATE: COUNT(tasks.id) WHERE tasks.status = 'CANCELLED'</x:v>
+        <x:v>AGGREGATE: 上記Task範囲 AND tasks.status='CANCELLED'</x:v>
       </x:c>
     </x:row>
     <x:row r="64" ht="15" hidden="0" customHeight="1">
@@ -7867,10 +7226,10 @@
         <x:v>不可</x:v>
       </x:c>
       <x:c r="J64" s="67" t="str">
-        <x:v>期限間近件数</x:v>
+        <x:v>System日から3日後までの未完了Task件数（期間非連動）</x:v>
       </x:c>
       <x:c r="K64" s="67" t="str">
-        <x:v>tasks集計</x:v>
+        <x:v>AGGREGATE: CURRENT_DATE&lt;=tasks.due_date&lt;=CURRENT_DATE+3 AND status NOT IN ('COMPLETED','CANCELLED') + Role範囲</x:v>
       </x:c>
     </x:row>
     <x:row r="65" ht="15" hidden="0" customHeight="1">
@@ -7902,10 +7261,10 @@
         <x:v>不可</x:v>
       </x:c>
       <x:c r="J65" s="67" t="str">
-        <x:v>日報提出件数</x:v>
+        <x:v>指定期間内の日報提出件数</x:v>
       </x:c>
       <x:c r="K65" s="67" t="str">
-        <x:v>daily_reports集計</x:v>
+        <x:v>AGGREGATE: daily_reports.report_date BETWEEN :periodFrom AND :periodTo + Role範囲</x:v>
       </x:c>
     </x:row>
     <x:row r="66" ht="15" hidden="0" customHeight="1">
@@ -7937,10 +7296,10 @@
         <x:v>不可</x:v>
       </x:c>
       <x:c r="J66" s="67" t="str">
-        <x:v>最新通知</x:v>
+        <x:v>本人の最新通知（期間非連動）</x:v>
       </x:c>
       <x:c r="K66" s="67" t="str">
-        <x:v>notifications</x:v>
+        <x:v>notifications WHERE user_id=:currentUserId ORDER BY created_at DESC,id DESC LIMIT 5</x:v>
       </x:c>
     </x:row>
     <x:row r="67" ht="15" hidden="0" customHeight="1">
@@ -8059,28 +7418,28 @@
         <x:v>body</x:v>
       </x:c>
       <x:c r="D70" s="67" t="str">
-        <x:v>response.body.data.recentNotifications[].content</x:v>
+        <x:v>response.body.data.recentNotifications[].createdAt</x:v>
       </x:c>
       <x:c r="E70" s="67" t="str">
-        <x:v>String</x:v>
+        <x:v>DateTime</x:v>
       </x:c>
       <x:c r="F70" s="67" t="str">
         <x:v>必須</x:v>
       </x:c>
       <x:c r="G70" s="67" t="str">
-        <x:v>最大1000</x:v>
+        <x:v>-</x:v>
       </x:c>
       <x:c r="H70" s="67" t="str">
-        <x:v>-</x:v>
+        <x:v>ISO-8601</x:v>
       </x:c>
       <x:c r="I70" s="67" t="str">
         <x:v>不可</x:v>
       </x:c>
       <x:c r="J70" s="67" t="str">
-        <x:v>内容</x:v>
+        <x:v>作成日時</x:v>
       </x:c>
       <x:c r="K70" s="67" t="str">
-        <x:v>notifications.content</x:v>
+        <x:v>notifications.created_at</x:v>
       </x:c>
     </x:row>
     <x:row r="71" ht="15" hidden="0" customHeight="1">
@@ -8094,28 +7453,28 @@
         <x:v>body</x:v>
       </x:c>
       <x:c r="D71" s="67" t="str">
-        <x:v>response.body.data.recentNotifications[].relatedType</x:v>
+        <x:v>response.body.data.recentNotifications[].isRead</x:v>
       </x:c>
       <x:c r="E71" s="67" t="str">
-        <x:v>String</x:v>
+        <x:v>Boolean</x:v>
       </x:c>
       <x:c r="F71" s="67" t="str">
-        <x:v>任意</x:v>
+        <x:v>必須</x:v>
       </x:c>
       <x:c r="G71" s="67" t="str">
-        <x:v>最大50</x:v>
+        <x:v>-</x:v>
       </x:c>
       <x:c r="H71" s="67" t="str">
-        <x:v>TASK/REPORT/SYSTEM</x:v>
+        <x:v>true/false</x:v>
       </x:c>
       <x:c r="I71" s="67" t="str">
-        <x:v>可</x:v>
+        <x:v>不可</x:v>
       </x:c>
       <x:c r="J71" s="67" t="str">
-        <x:v>関連種別</x:v>
+        <x:v>既読状態</x:v>
       </x:c>
       <x:c r="K71" s="67" t="str">
-        <x:v>notifications.related_type</x:v>
+        <x:v>notifications.is_read</x:v>
       </x:c>
     </x:row>
     <x:row r="72" ht="15" hidden="0" customHeight="1">
@@ -8418,7 +7777,7 @@
         <x:v>必須</x:v>
       </x:c>
       <x:c r="G80" s="67" t="str">
-        <x:v>最大20</x:v>
+        <x:v>最大30</x:v>
       </x:c>
       <x:c r="H80" s="67" t="str">
         <x:v>-</x:v>
@@ -8923,7 +8282,7 @@
         <x:v>employees.name</x:v>
       </x:c>
     </x:row>
-    <x:row r="95" ht="15" hidden="0" customHeight="1">
+    <x:row r="95" ht="36" hidden="0" customHeight="1">
       <x:c r="A95" s="67" t="str">
         <x:v>API-MST-002</x:v>
       </x:c>
@@ -8952,13 +8311,14 @@
         <x:v>可</x:v>
       </x:c>
       <x:c r="J95" s="67" t="str">
-        <x:v>氏名Kana</x:v>
+        <x:v>DEFAULTのみ。候補用途はNull。</x:v>
       </x:c>
       <x:c r="K95" s="67" t="str">
         <x:v>employees.name_kana</x:v>
       </x:c>
-    </x:row>
-    <x:row r="96" ht="15" hidden="0" customHeight="1">
+      <x:c r="L95" s="241"/>
+    </x:row>
+    <x:row r="96" ht="40" hidden="0" customHeight="1">
       <x:c r="A96" s="67" t="str">
         <x:v>API-MST-002</x:v>
       </x:c>
@@ -8984,14 +8344,15 @@
         <x:v>email</x:v>
       </x:c>
       <x:c r="I96" s="67" t="str">
-        <x:v>不可</x:v>
+        <x:v>可</x:v>
       </x:c>
       <x:c r="J96" s="67" t="str">
-        <x:v>Mail</x:v>
+        <x:v>DEFAULTのみ既存許可範囲で返却。候補用途はNull。</x:v>
       </x:c>
       <x:c r="K96" s="67" t="str">
         <x:v>employees.email</x:v>
       </x:c>
+      <x:c r="L96" s="241"/>
     </x:row>
     <x:row r="97" ht="15" hidden="0" customHeight="1">
       <x:c r="A97" s="67" t="str">
@@ -9398,7 +8759,7 @@
         <x:v>必須</x:v>
       </x:c>
       <x:c r="G108" s="67" t="str">
-        <x:v>最大100</x:v>
+        <x:v>最大200</x:v>
       </x:c>
       <x:c r="H108" s="67" t="str">
         <x:v>-</x:v>
@@ -9958,7 +9319,7 @@
         <x:v>必須</x:v>
       </x:c>
       <x:c r="G124" s="67" t="str">
-        <x:v>最大50</x:v>
+        <x:v>最大100</x:v>
       </x:c>
       <x:c r="H124" s="67" t="str">
         <x:v>PERM-*</x:v>
@@ -10101,7 +9462,7 @@
         <x:v>最大30</x:v>
       </x:c>
       <x:c r="H128" s="67" t="str">
-        <x:v>ACTIVE/DISABLED/LOCKED/PASSWORD_CHANGE_REQUIRED</x:v>
+        <x:v>ACTIVE/DISABLED/LOCKED</x:v>
       </x:c>
       <x:c r="I128" s="67" t="str">
         <x:v>可</x:v>
@@ -10110,7 +9471,7 @@
         <x:v>状態</x:v>
       </x:c>
       <x:c r="K128" s="67" t="str">
-        <x:v>FILTER/DERIVED: users.enabled, users.locked_until, users.password_must_change</x:v>
+        <x:v>16／26_ステータス定義 STATUS-USERの主状態を導出。passwordMustChangeとは独立。</x:v>
       </x:c>
     </x:row>
     <x:row r="129" ht="15" hidden="0" customHeight="1">
@@ -10661,7 +10022,7 @@
         <x:v>最大30</x:v>
       </x:c>
       <x:c r="H144" s="67" t="str">
-        <x:v>ACTIVE/DISABLED/LOCKED/PASSWORD_CHANGE_REQUIRED</x:v>
+        <x:v>ACTIVE/DISABLED/LOCKED</x:v>
       </x:c>
       <x:c r="I144" s="67" t="str">
         <x:v>不可</x:v>
@@ -10670,7 +10031,7 @@
         <x:v>User状態</x:v>
       </x:c>
       <x:c r="K144" s="67" t="str">
-        <x:v>DERIVED: users.enabled / locked_until / password_must_change; priority=DISABLED→LOCKED→PASSWORD_CHANGE_REQUIRED→ACTIVE</x:v>
+        <x:v>16／26_ステータス定義 STATUS-USERの主状態を導出。passwordMustChangeとは独立。</x:v>
       </x:c>
     </x:row>
     <x:row r="145" ht="15" hidden="0" customHeight="1">
@@ -11501,7 +10862,7 @@
         <x:v>最大30</x:v>
       </x:c>
       <x:c r="H168" s="67" t="str">
-        <x:v>ACTIVE/DISABLED/LOCKED/PASSWORD_CHANGE_REQUIRED</x:v>
+        <x:v>ACTIVE/DISABLED/LOCKED</x:v>
       </x:c>
       <x:c r="I168" s="67" t="str">
         <x:v>不可</x:v>
@@ -11510,7 +10871,7 @@
         <x:v>状態</x:v>
       </x:c>
       <x:c r="K168" s="67" t="str">
-        <x:v>DERIVED: users.enabled / locked_until / password_must_change; priority=DISABLED→LOCKED→PASSWORD_CHANGE_REQUIRED→ACTIVE</x:v>
+        <x:v>16／26_ステータス定義 STATUS-USERの主状態を導出。passwordMustChangeとは独立。</x:v>
       </x:c>
     </x:row>
     <x:row r="169" ht="15" hidden="0" customHeight="1">
@@ -11539,10 +10900,10 @@
         <x:v>ISO-8601 / Asia-Tokyo</x:v>
       </x:c>
       <x:c r="I169" s="67" t="str">
-        <x:v>不可</x:v>
+        <x:v>可</x:v>
       </x:c>
       <x:c r="J169" s="67" t="str">
-        <x:v>Lock期限</x:v>
+        <x:v>Lock期限。未設定・Lock解除済はNull。15／07 users.locked_until、16／28 BR-AUTH-002の成功時Clearに従う。</x:v>
       </x:c>
       <x:c r="K169" s="67" t="str">
         <x:v>users.locked_until</x:v>
@@ -11688,7 +11049,7 @@
         <x:v>users.enabled</x:v>
       </x:c>
     </x:row>
-    <x:row r="174" ht="15" hidden="0" customHeight="1">
+    <x:row r="174" ht="40" hidden="0" customHeight="1">
       <x:c r="A174" s="67" t="str">
         <x:v>API-USR-003</x:v>
       </x:c>
@@ -11717,11 +11078,12 @@
         <x:v>不可</x:v>
       </x:c>
       <x:c r="J174" s="67" t="str">
-        <x:v>Role ID一覧</x:v>
+        <x:v>有効内蔵Roleを1つ以上含む、重複なし。02／09の保護条件。</x:v>
       </x:c>
       <x:c r="K174" s="67" t="str">
         <x:v>COLLECTION INPUT: roleIds[] → user_roles.role_id (replace assignment set)</x:v>
       </x:c>
+      <x:c r="L174" s="241"/>
     </x:row>
     <x:row r="175" ht="15" hidden="0" customHeight="1">
       <x:c r="A175" s="67" t="str">
@@ -12318,7 +11680,7 @@
         <x:v>Log traceId</x:v>
       </x:c>
     </x:row>
-    <x:row r="192" ht="15" hidden="0" customHeight="1">
+    <x:row r="192" ht="40" hidden="0" customHeight="1">
       <x:c r="A192" s="67" t="str">
         <x:v>API-USR-004</x:v>
       </x:c>
@@ -12344,14 +11706,15 @@
         <x:v>-</x:v>
       </x:c>
       <x:c r="I192" s="67" t="str">
-        <x:v>不可</x:v>
+        <x:v>可</x:v>
       </x:c>
       <x:c r="J192" s="67" t="str">
-        <x:v>temporaryPassword</x:v>
+        <x:v>初回成功のみ一時Password。冪等再送はNull（処理済）。BR-API-002。</x:v>
       </x:c>
       <x:c r="K192" s="67" t="str">
         <x:v>Service生成（一時Password）</x:v>
       </x:c>
+      <x:c r="L192" s="241"/>
     </x:row>
     <x:row r="193" ht="15" hidden="0" customHeight="1">
       <x:c r="A193" s="67" t="str">
@@ -13458,7 +12821,7 @@
         <x:v>必須</x:v>
       </x:c>
       <x:c r="G224" s="67" t="str">
-        <x:v>最大2000</x:v>
+        <x:v>最大500</x:v>
       </x:c>
       <x:c r="H224" s="67" t="str">
         <x:v>-</x:v>
@@ -14151,7 +13514,7 @@
       <x:c r="J244" s="67"/>
       <x:c r="K244" s="67"/>
     </x:row>
-    <x:row r="245" ht="24" hidden="0" customHeight="1">
+    <x:row r="245" ht="40" hidden="0" customHeight="1">
       <x:c r="A245" s="67" t="str">
         <x:v>API-ROLE-004</x:v>
       </x:c>
@@ -14180,11 +13543,12 @@
         <x:v>不可</x:v>
       </x:c>
       <x:c r="J245" s="67" t="str">
-        <x:v>Permission ID一覧</x:v>
+        <x:v>組込Roleは現値と同一のみ。カスタムRoleは既存Permissionで置換。</x:v>
       </x:c>
       <x:c r="K245" s="67" t="str">
         <x:v>COLLECTION INPUT: permissionIds[] → role_permissions.permission_id (replace assignment set)</x:v>
       </x:c>
+      <x:c r="L245" s="241"/>
     </x:row>
     <x:row r="246" ht="15" hidden="0" customHeight="1">
       <x:c r="A246" s="67" t="str">
@@ -15119,7 +14483,7 @@
         <x:v>最大20</x:v>
       </x:c>
       <x:c r="H272" s="67" t="str">
-        <x:v>-</x:v>
+        <x:v>SUCCESS/FAILURE</x:v>
       </x:c>
       <x:c r="I272" s="67" t="str">
         <x:v>可</x:v>
@@ -16707,39 +16071,17 @@
       </x:c>
     </x:row>
     <x:row r="318" ht="15" hidden="0" customHeight="1">
-      <x:c r="A318" s="67" t="str">
-        <x:v>API-TASK-009</x:v>
-      </x:c>
-      <x:c r="B318" s="67" t="str">
-        <x:v>Request</x:v>
-      </x:c>
-      <x:c r="C318" s="67" t="str">
-        <x:v>path</x:v>
-      </x:c>
-      <x:c r="D318" s="67" t="str">
-        <x:v>request.path.id</x:v>
-      </x:c>
-      <x:c r="E318" s="67" t="str">
-        <x:v>Long</x:v>
-      </x:c>
-      <x:c r="F318" s="67" t="str">
-        <x:v>必須</x:v>
-      </x:c>
-      <x:c r="G318" s="67" t="str">
-        <x:v>-</x:v>
-      </x:c>
-      <x:c r="H318" s="67" t="str">
-        <x:v>int64</x:v>
-      </x:c>
-      <x:c r="I318" s="67" t="str">
-        <x:v>不可</x:v>
-      </x:c>
-      <x:c r="J318" s="67" t="str">
-        <x:v>Task ID</x:v>
-      </x:c>
-      <x:c r="K318" s="67" t="str">
-        <x:v>tasks.id</x:v>
-      </x:c>
+      <x:c r="A318" s="67"/>
+      <x:c r="B318" s="67"/>
+      <x:c r="C318" s="67"/>
+      <x:c r="D318" s="67"/>
+      <x:c r="E318" s="67"/>
+      <x:c r="F318" s="67"/>
+      <x:c r="G318" s="67"/>
+      <x:c r="H318" s="67"/>
+      <x:c r="I318" s="67"/>
+      <x:c r="J318" s="67"/>
+      <x:c r="K318" s="67"/>
     </x:row>
     <x:row r="319" ht="15" hidden="0" customHeight="1">
       <x:c r="A319" s="67" t="str">
@@ -16761,7 +16103,7 @@
         <x:v>任意</x:v>
       </x:c>
       <x:c r="G319" s="67" t="str">
-        <x:v>最大45</x:v>
+        <x:v>最大64</x:v>
       </x:c>
       <x:c r="H319" s="67" t="str">
         <x:v>IPv4/IPv6</x:v>
@@ -16807,25 +16149,200 @@
       <x:c r="J322" s="186"/>
       <x:c r="K322" s="186"/>
     </x:row>
+    <x:row r="323" ht="110" customHeight="1">
+      <x:c r="A323" s="241" t="str">
+        <x:v>API-AUTH-001</x:v>
+      </x:c>
+      <x:c r="B323" s="241" t="str">
+        <x:v>Response</x:v>
+      </x:c>
+      <x:c r="C323" s="241" t="str">
+        <x:v>body</x:v>
+      </x:c>
+      <x:c r="D323" s="241" t="str">
+        <x:v>response.body.data.user.passwordMustChange</x:v>
+      </x:c>
+      <x:c r="E323" s="241" t="str">
+        <x:v>Boolean</x:v>
+      </x:c>
+      <x:c r="F323" s="241" t="str">
+        <x:v>必須</x:v>
+      </x:c>
+      <x:c r="G323" s="241" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="H323" s="241" t="str">
+        <x:v>true/false</x:v>
+      </x:c>
+      <x:c r="I323" s="241" t="str">
+        <x:v>不可</x:v>
+      </x:c>
+      <x:c r="J323" s="241" t="str">
+        <x:v>初回/Reset後のPassword変更必須判定</x:v>
+      </x:c>
+      <x:c r="K323" s="241" t="str">
+        <x:v>users.password_must_change</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="324" ht="110" customHeight="1">
+      <x:c r="A324" s="241" t="str">
+        <x:v>API-AUTH-004</x:v>
+      </x:c>
+      <x:c r="B324" s="241" t="str">
+        <x:v>Response</x:v>
+      </x:c>
+      <x:c r="C324" s="241" t="str">
+        <x:v>body</x:v>
+      </x:c>
+      <x:c r="D324" s="241" t="str">
+        <x:v>response.body.data.user.passwordMustChange</x:v>
+      </x:c>
+      <x:c r="E324" s="241" t="str">
+        <x:v>Boolean</x:v>
+      </x:c>
+      <x:c r="F324" s="241" t="str">
+        <x:v>必須</x:v>
+      </x:c>
+      <x:c r="G324" s="241" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="H324" s="241" t="str">
+        <x:v>true/false</x:v>
+      </x:c>
+      <x:c r="I324" s="241" t="str">
+        <x:v>不可</x:v>
+      </x:c>
+      <x:c r="J324" s="241" t="str">
+        <x:v>初回/Reset後のPassword変更必須判定</x:v>
+      </x:c>
+      <x:c r="K324" s="241" t="str">
+        <x:v>users.password_must_change</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="325" ht="110" customHeight="1">
+      <x:c r="A325" s="241" t="str">
+        <x:v>API-LOG-002</x:v>
+      </x:c>
+      <x:c r="B325" s="241" t="str">
+        <x:v>Response</x:v>
+      </x:c>
+      <x:c r="C325" s="241" t="str">
+        <x:v>body</x:v>
+      </x:c>
+      <x:c r="D325" s="241" t="str">
+        <x:v>response.body.data.beforeValues</x:v>
+      </x:c>
+      <x:c r="E325" s="241" t="str">
+        <x:v>Object</x:v>
+      </x:c>
+      <x:c r="F325" s="241" t="str">
+        <x:v>必須</x:v>
+      </x:c>
+      <x:c r="G325" s="241" t="str">
+        <x:v>変更対象項目のみ</x:v>
+      </x:c>
+      <x:c r="H325" s="241" t="str">
+        <x:v>JSON。キー=対象Tableの業務項目名、値=String/Number/Boolean/Array/Null</x:v>
+      </x:c>
+      <x:c r="I325" s="241" t="str">
+        <x:v>可</x:v>
+      </x:c>
+      <x:c r="J325" s="241" t="str">
+        <x:v>マスク済監査値。値なしはNull。機密項目はキーごと除外</x:v>
+      </x:c>
+      <x:c r="K325" s="241" t="str">
+        <x:v>operation_logs.before_values</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="326" ht="110" customHeight="1">
+      <x:c r="A326" s="241" t="str">
+        <x:v>API-LOG-002</x:v>
+      </x:c>
+      <x:c r="B326" s="241" t="str">
+        <x:v>Response</x:v>
+      </x:c>
+      <x:c r="C326" s="241" t="str">
+        <x:v>body</x:v>
+      </x:c>
+      <x:c r="D326" s="241" t="str">
+        <x:v>response.body.data.afterValues</x:v>
+      </x:c>
+      <x:c r="E326" s="241" t="str">
+        <x:v>Object</x:v>
+      </x:c>
+      <x:c r="F326" s="241" t="str">
+        <x:v>必須</x:v>
+      </x:c>
+      <x:c r="G326" s="241" t="str">
+        <x:v>変更対象項目のみ</x:v>
+      </x:c>
+      <x:c r="H326" s="241" t="str">
+        <x:v>JSON。キー=対象Tableの業務項目名、値=String/Number/Boolean/Array/Null</x:v>
+      </x:c>
+      <x:c r="I326" s="241" t="str">
+        <x:v>可</x:v>
+      </x:c>
+      <x:c r="J326" s="241" t="str">
+        <x:v>マスク済監査値。値なしはNull。機密項目はキーごと除外</x:v>
+      </x:c>
+      <x:c r="K326" s="241" t="str">
+        <x:v>operation_logs.after_values</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="327" ht="54" customHeight="1">
+      <x:c r="A327" s="241" t="str">
+        <x:v>API-MST-002</x:v>
+      </x:c>
+      <x:c r="B327" s="241" t="str">
+        <x:v>Request</x:v>
+      </x:c>
+      <x:c r="C327" s="241" t="str">
+        <x:v>query</x:v>
+      </x:c>
+      <x:c r="D327" s="241" t="str">
+        <x:v>request.query.purpose</x:v>
+      </x:c>
+      <x:c r="E327" s="241" t="str">
+        <x:v>String</x:v>
+      </x:c>
+      <x:c r="F327" s="241" t="str">
+        <x:v>任意</x:v>
+      </x:c>
+      <x:c r="G327" s="241" t="str">
+        <x:v>最大30</x:v>
+      </x:c>
+      <x:c r="H327" s="241" t="str">
+        <x:v>DEFAULT/PROJECT_PM/PROJECT_MEMBER/TASK_ASSIGNEE</x:v>
+      </x:c>
+      <x:c r="I327" s="241" t="str">
+        <x:v>可</x:v>
+      </x:c>
+      <x:c r="J327" s="241" t="str">
+        <x:v>省略DEFAULT。PJ管理候補の判定目的。</x:v>
+      </x:c>
+      <x:c r="K327" s="241" t="str">
+        <x:v>業務条件</x:v>
+      </x:c>
+      <x:c r="L327" s="241"/>
+    </x:row>
   </x:sheetData>
   <x:mergeCells>
     <x:mergeCell ref="A1:K2"/>
     <x:mergeCell ref="A6:K6"/>
-    <x:mergeCell ref="A309:K310"/>
     <x:mergeCell ref="A321:K322"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
 </file>
 
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="18" hidden="0" customWidth="1"/>
     <x:col min="2" max="2" width="28" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="72" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="82" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="100" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="100" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="12" hidden="0" customWidth="1"/>
     <x:col min="6" max="6" width="28" hidden="0" customWidth="1"/>
     <x:col min="7" max="7" width="38" hidden="0" customWidth="1"/>
@@ -16859,8 +16376,8 @@
         <x:v>Company WorkHub</x:v>
       </x:c>
       <x:c r="C3" s="139"/>
-      <x:c r="D3" s="174" t="str">
-        <x:v>文書番号</x:v>
+      <x:c r="D3" s="246" t="str">
+        <x:v>章ID</x:v>
       </x:c>
       <x:c r="E3" s="139" t="str">
         <x:v>CW-BD-10-SAMPLE</x:v>
@@ -16872,18 +16389,29 @@
       <x:c r="A4" s="174" t="str">
         <x:v>版数</x:v>
       </x:c>
-      <x:c r="B4" s="139" t="str">
-        <x:v>Ver.1.8</x:v>
+      <x:c r="B4" s="63" t="str">
+        <x:v>Ver.2.5</x:v>
       </x:c>
       <x:c r="C4" s="139"/>
       <x:c r="D4" s="174" t="str">
         <x:v>改訂日</x:v>
       </x:c>
-      <x:c r="E4" s="139" t="str">
-        <x:v>2026-08-12</x:v>
+      <x:c r="E4" s="63" t="str">
+        <x:v>2026-09-24</x:v>
       </x:c>
       <x:c r="F4" s="139"/>
       <x:c r="G4" s="139"/>
+    </x:row>
+    <x:row r="5" ht="42" customHeight="1">
+      <x:c r="A5" s="203" t="str">
+        <x:v>参考資料。Contract正本は23_API項目定義。Request例は送信区分別の表示用Object（そのまま送るJSONではない）。認証等の共通Headerは10／19参照。Binary PartはFile名で表記。各行は独立した例。</x:v>
+      </x:c>
+      <x:c r="B5" s="203"/>
+      <x:c r="C5" s="203"/>
+      <x:c r="D5" s="203"/>
+      <x:c r="E5" s="203"/>
+      <x:c r="F5" s="203"/>
+      <x:c r="G5" s="203"/>
     </x:row>
     <x:row r="6">
       <x:c r="A6" s="175" t="str">
@@ -16919,7 +16447,7 @@
         <x:v>備考</x:v>
       </x:c>
     </x:row>
-    <x:row r="8" ht="120" customHeight="1">
+    <x:row r="8" ht="100" customHeight="1">
       <x:c r="A8" s="67" t="str">
         <x:v>API-AUTH-001</x:v>
       </x:c>
@@ -16927,35 +16455,10 @@
         <x:v>ログイン</x:v>
       </x:c>
       <x:c r="C8" s="67" t="str">
-        <x:v>{
-  "body": {
-    "username": "サンプル",
-    "password": "********"
-  }
-}</x:v>
+        <x:v>{"body": {"username": "training.user", "password": "Train9!Sample"}}</x:v>
       </x:c>
       <x:c r="D8" s="67" t="str">
-        <x:v>{
-  "code": "COMMON-0000",
-  "message": "処理成功",
-  "timestamp": "2026-08-10T10:00:00+09:00",
-  "traceId": "7f3a9c01e2b44d8a",
-  "data": {
-    "accessToken": "sample",
-    "expiresIn": 1800,
-    "user": {
-      "id": 1001,
-      "username": "サンプル",
-      "name": "サンプル",
-      "roles": [
-        "SAMPLE"
-      ],
-      "permissions": [
-        "SAMPLE"
-      ]
-    }
-  }
-}</x:v>
+        <x:v>{"code": "COMMON-0000", "message": "処理成功", "timestamp": "2026-08-10T10:00:00+09:00", "traceId": "7f3a9c01e2b44d8a", "data": {"accessToken": "sample", "expiresIn": 1800, "user": {"id": 1001, "username": "training.user", "name": "サンプル", "roles": ["ROLE-EMP"], "permissions": ["PERM-TASK-READ", "PERM-TASK-PROGRESS"], "passwordMustChange": false}}}</x:v>
       </x:c>
       <x:c r="E8" s="67" t="str">
         <x:v>200</x:v>
@@ -16967,7 +16470,7 @@
         <x:v>値は例。項目定義を正とする</x:v>
       </x:c>
     </x:row>
-    <x:row r="9" ht="120" customHeight="1">
+    <x:row r="9" ht="100" customHeight="1">
       <x:c r="A9" s="67" t="str">
         <x:v>API-AUTH-002</x:v>
       </x:c>
@@ -16975,14 +16478,7 @@
         <x:v>ログアウト</x:v>
       </x:c>
       <x:c r="C9" s="67" t="str">
-        <x:v>{
-  "header": {
-    "Authorization": "sample"
-  },
-  "cookie": {
-    "refreshToken": "sample"
-  }
-}</x:v>
+        <x:v>{"header": {"Authorization": "Bearer sample-access-token"}, "cookie": {"refreshToken": "sample"}}</x:v>
       </x:c>
       <x:c r="D9" s="67" t="str">
         <x:v>-（Response Bodyなし）</x:v>
@@ -16997,7 +16493,7 @@
         <x:v>値は例。項目定義を正とする</x:v>
       </x:c>
     </x:row>
-    <x:row r="10" ht="120" customHeight="1">
+    <x:row r="10" ht="100" customHeight="1">
       <x:c r="A10" s="67" t="str">
         <x:v>API-AUTH-003</x:v>
       </x:c>
@@ -17005,23 +16501,10 @@
         <x:v>Token更新</x:v>
       </x:c>
       <x:c r="C10" s="67" t="str">
-        <x:v>{
-  "cookie": {
-    "refreshToken": "sample"
-  }
-}</x:v>
+        <x:v>{"cookie": {"refreshToken": "sample"}}</x:v>
       </x:c>
       <x:c r="D10" s="67" t="str">
-        <x:v>{
-  "code": "COMMON-0000",
-  "message": "処理成功",
-  "timestamp": "2026-08-10T10:00:00+09:00",
-  "traceId": "7f3a9c01e2b44d8a",
-  "data": {
-    "accessToken": "sample",
-    "expiresIn": 1800
-  }
-}</x:v>
+        <x:v>{"code": "COMMON-0000", "message": "処理成功", "timestamp": "2026-08-10T10:00:00+09:00", "traceId": "7f3a9c01e2b44d8a", "data": {"accessToken": "sample", "expiresIn": 1800}}</x:v>
       </x:c>
       <x:c r="E10" s="67" t="str">
         <x:v>200</x:v>
@@ -17033,7 +16516,7 @@
         <x:v>値は例。項目定義を正とする</x:v>
       </x:c>
     </x:row>
-    <x:row r="11" ht="120" customHeight="1">
+    <x:row r="11" ht="100" customHeight="1">
       <x:c r="A11" s="67" t="str">
         <x:v>API-AUTH-004</x:v>
       </x:c>
@@ -17044,28 +16527,7 @@
         <x:v>{}</x:v>
       </x:c>
       <x:c r="D11" s="67" t="str">
-        <x:v>{
-  "code": "COMMON-0000",
-  "message": "処理成功",
-  "timestamp": "2026-08-10T10:00:00+09:00",
-  "traceId": "7f3a9c01e2b44d8a",
-  "data": {
-    "user": {
-      "id": 1001,
-      "employeeId": 1001,
-      "name": "サンプル",
-      "roles": [
-        "SAMPLE"
-      ],
-      "permissions": [
-        "SAMPLE"
-      ],
-      "menus": [
-        "SAMPLE"
-      ]
-    }
-  }
-}</x:v>
+        <x:v>{"code": "COMMON-0000", "message": "処理成功", "timestamp": "2026-08-10T10:00:00+09:00", "traceId": "7f3a9c01e2b44d8a", "data": {"user": {"id": 1001, "employeeId": 1001, "name": "サンプル", "roles": ["ROLE-EMP"], "permissions": ["PERM-TASK-READ", "PERM-TASK-PROGRESS"], "menus": ["マイタスク"], "passwordMustChange": false}}}</x:v>
       </x:c>
       <x:c r="E11" s="67" t="str">
         <x:v>200</x:v>
@@ -17077,7 +16539,7 @@
         <x:v>値は例。項目定義を正とする</x:v>
       </x:c>
     </x:row>
-    <x:row r="12" ht="120" customHeight="1">
+    <x:row r="12" ht="100" customHeight="1">
       <x:c r="A12" s="67" t="str">
         <x:v>API-AUTH-005</x:v>
       </x:c>
@@ -17085,13 +16547,7 @@
         <x:v>パスワード変更</x:v>
       </x:c>
       <x:c r="C12" s="67" t="str">
-        <x:v>{
-  "body": {
-    "currentPassword": "********",
-    "newPassword": "********",
-    "confirmPassword": "********"
-  }
-}</x:v>
+        <x:v>{"body": {"currentPassword": "Train9!Sample", "newPassword": "Train8!Changed", "confirmPassword": "Train8!Changed"}}</x:v>
       </x:c>
       <x:c r="D12" s="67" t="str">
         <x:v>-（Response Bodyなし）</x:v>
@@ -17106,7 +16562,7 @@
         <x:v>値は例。項目定義を正とする</x:v>
       </x:c>
     </x:row>
-    <x:row r="13" ht="120" customHeight="1">
+    <x:row r="13" ht="100" customHeight="1">
       <x:c r="A13" s="67" t="str">
         <x:v>API-DASH-001</x:v>
       </x:c>
@@ -17114,41 +16570,10 @@
         <x:v>ホーム集計取得</x:v>
       </x:c>
       <x:c r="C13" s="67" t="str">
-        <x:v>{
-  "query": {
-    "periodFrom": "2026-08-10",
-    "periodTo": "2026-08-10"
-  }
-}</x:v>
+        <x:v>{"query": {"periodFrom": "2026-08-10", "periodTo": "2026-08-10"}}</x:v>
       </x:c>
       <x:c r="D13" s="67" t="str">
-        <x:v>{
-  "code": "COMMON-0000",
-  "message": "処理成功",
-  "timestamp": "2026-08-10T10:00:00+09:00",
-  "traceId": "7f3a9c01e2b44d8a",
-  "data": {
-    "projectCount": 1,
-    "taskStatusCounts": {
-      "todo": 10,
-      "inProgress": 8,
-      "review": 3,
-      "completed": 20,
-      "cancelled": 1
-    },
-    "dueSoonCount": 1,
-    "reportSubmittedCount": 1,
-    "recentNotifications": [
-      {
-        "id": 1001,
-        "notificationType": "TASK_DUE",
-        "title": "sample",
-        "content": "sample",
-        "relatedType": "TASK"
-      }
-    ]
-  }
-}</x:v>
+        <x:v>{"code": "COMMON-0000", "message": "処理成功", "timestamp": "2026-08-17T10:00:00+09:00", "traceId": "7f3a9c01e2b44d8a", "data": {"projectCount": 1, "taskStatusCounts": {"todo": 10, "inProgress": 8, "review": 3, "completed": 20, "cancelled": 1}, "dueSoonCount": 1, "reportSubmittedCount": 1, "recentNotifications": [{"id": 1001, "notificationType": "TASK_DUE", "title": "sample", "createdAt": "2026-08-17T09:00:00+09:00", "isRead": false}]}}</x:v>
       </x:c>
       <x:c r="E13" s="67" t="str">
         <x:v>200</x:v>
@@ -17160,7 +16585,7 @@
         <x:v>値は例。項目定義を正とする</x:v>
       </x:c>
     </x:row>
-    <x:row r="14" ht="120" customHeight="1">
+    <x:row r="14" ht="100" customHeight="1">
       <x:c r="A14" s="67" t="str">
         <x:v>API-MST-001</x:v>
       </x:c>
@@ -17168,29 +16593,10 @@
         <x:v>部門選択肢</x:v>
       </x:c>
       <x:c r="C14" s="67" t="str">
-        <x:v>{
-  "query": {
-    "activeOnly": true
-  }
-}</x:v>
+        <x:v>{"query": {"activeOnly": true}}</x:v>
       </x:c>
       <x:c r="D14" s="67" t="str">
-        <x:v>{
-  "code": "COMMON-0000",
-  "message": "処理成功",
-  "timestamp": "2026-08-10T10:00:00+09:00",
-  "traceId": "7f3a9c01e2b44d8a",
-  "data": {
-    "departments": [
-      {
-        "id": 1001,
-        "departmentCode": "sample",
-        "name": "サンプル",
-        "parentId": 1001
-      }
-    ]
-  }
-}</x:v>
+        <x:v>{"code": "COMMON-0000", "message": "処理成功", "timestamp": "2026-08-10T10:00:00+09:00", "traceId": "7f3a9c01e2b44d8a", "data": {"departments": [{"id": 1001, "departmentCode": "sample", "name": "サンプル", "parentId": 1000}]}}</x:v>
       </x:c>
       <x:c r="E14" s="67" t="str">
         <x:v>200</x:v>
@@ -17202,7 +16608,7 @@
         <x:v>値は例。項目定義を正とする</x:v>
       </x:c>
     </x:row>
-    <x:row r="15" ht="120" customHeight="1">
+    <x:row r="15" ht="100" customHeight="1">
       <x:c r="A15" s="67" t="str">
         <x:v>API-MST-002</x:v>
       </x:c>
@@ -17210,34 +16616,10 @@
         <x:v>社員選択肢</x:v>
       </x:c>
       <x:c r="C15" s="67" t="str">
-        <x:v>{
-  "query": {
-    "projectId": 1001,
-    "keyword": "sample",
-    "activeOnly": true
-  }
-}</x:v>
+        <x:v>{"query": {"projectId": 1001, "keyword": "sample", "activeOnly": true}}</x:v>
       </x:c>
       <x:c r="D15" s="67" t="str">
-        <x:v>{
-  "code": "COMMON-0000",
-  "message": "処理成功",
-  "timestamp": "2026-08-10T10:00:00+09:00",
-  "traceId": "7f3a9c01e2b44d8a",
-  "data": {
-    "employees": [
-      {
-        "id": 1001,
-        "employeeCode": "sample",
-        "name": "サンプル",
-        "nameKana": "サンプル",
-        "email": "user@example.co.jp",
-        "departmentId": 1001,
-        "departmentName": "サンプル"
-      }
-    ]
-  }
-}</x:v>
+        <x:v>{"code": "COMMON-0000", "message": "処理成功", "timestamp": "2026-08-10T10:00:00+09:00", "traceId": "7f3a9c01e2b44d8a", "data": {"employees": [{"id": 1001, "employeeCode": "sample", "name": "サンプル", "nameKana": "サンプル", "email": "user@example.co.jp", "departmentId": 1001, "departmentName": "サンプル"}]}}</x:v>
       </x:c>
       <x:c r="E15" s="67" t="str">
         <x:v>200</x:v>
@@ -17249,7 +16631,7 @@
         <x:v>値は例。項目定義を正とする</x:v>
       </x:c>
     </x:row>
-    <x:row r="16" ht="120" customHeight="1">
+    <x:row r="16" ht="100" customHeight="1">
       <x:c r="A16" s="67" t="str">
         <x:v>API-MST-003</x:v>
       </x:c>
@@ -17257,30 +16639,10 @@
         <x:v>PJ選択肢</x:v>
       </x:c>
       <x:c r="C16" s="67" t="str">
-        <x:v>{
-  "query": {
-    "activeOnly": true
-  }
-}</x:v>
+        <x:v>{"query": {"activeOnly": true}}</x:v>
       </x:c>
       <x:c r="D16" s="67" t="str">
-        <x:v>{
-  "code": "COMMON-0000",
-  "message": "処理成功",
-  "timestamp": "2026-08-10T10:00:00+09:00",
-  "traceId": "7f3a9c01e2b44d8a",
-  "data": {
-    "projects": [
-      {
-        "id": 1001,
-        "projectCode": "sample",
-        "name": "サンプル",
-        "managerId": 1001,
-        "managerName": "サンプル"
-      }
-    ]
-  }
-}</x:v>
+        <x:v>{"code": "COMMON-0000", "message": "処理成功", "timestamp": "2026-08-10T10:00:00+09:00", "traceId": "7f3a9c01e2b44d8a", "data": {"projects": [{"id": 1001, "projectCode": "sample", "name": "サンプル", "managerId": 1001, "managerName": "サンプル"}]}}</x:v>
       </x:c>
       <x:c r="E16" s="67" t="str">
         <x:v>200</x:v>
@@ -17292,7 +16654,7 @@
         <x:v>値は例。項目定義を正とする</x:v>
       </x:c>
     </x:row>
-    <x:row r="17" ht="120" customHeight="1">
+    <x:row r="17" ht="100" customHeight="1">
       <x:c r="A17" s="67" t="str">
         <x:v>API-MST-004</x:v>
       </x:c>
@@ -17303,30 +16665,7 @@
         <x:v>{}</x:v>
       </x:c>
       <x:c r="D17" s="67" t="str">
-        <x:v>{
-  "code": "COMMON-0000",
-  "message": "処理成功",
-  "timestamp": "2026-08-10T10:00:00+09:00",
-  "traceId": "7f3a9c01e2b44d8a",
-  "data": {
-    "roles": [
-      {
-        "id": 1001,
-        "roleCode": "sample",
-        "roleName": "サンプル",
-        "description": "sample",
-        "status": "ACTIVE"
-      }
-    ],
-    "permissions": [
-      {
-        "id": 1001,
-        "permissionCode": "sample",
-        "permissionName": "サンプル"
-      }
-    ]
-  }
-}</x:v>
+        <x:v>{"code": "COMMON-0000", "message": "処理成功", "timestamp": "2026-08-10T10:00:00+09:00", "traceId": "7f3a9c01e2b44d8a", "data": {"roles": [{"id": 1001, "roleCode": "ROLE-EMP", "roleName": "サンプル", "description": "sample", "status": "ACTIVE"}], "permissions": [{"id": 1001, "permissionCode": "PERM-TASK-READ", "permissionName": "サンプル"}]}}</x:v>
       </x:c>
       <x:c r="E17" s="67" t="str">
         <x:v>200</x:v>
@@ -17338,7 +16677,7 @@
         <x:v>値は例。項目定義を正とする</x:v>
       </x:c>
     </x:row>
-    <x:row r="18" ht="120" customHeight="1">
+    <x:row r="18" ht="100" customHeight="1">
       <x:c r="A18" s="67" t="str">
         <x:v>API-USR-001</x:v>
       </x:c>
@@ -17346,47 +16685,10 @@
         <x:v>ユーザー検索</x:v>
       </x:c>
       <x:c r="C18" s="67" t="str">
-        <x:v>{
-  "query": {
-    "username": "サンプル",
-    "name": "サンプル",
-    "status": "ACTIVE",
-    "locked": true,
-    "page": 0,
-    "size": 20,
-    "sort": "sample"
-  }
-}</x:v>
+        <x:v>{"query": {"username": "サンプル", "name": "サンプル", "status": "ACTIVE", "locked": false, "page": 0, "size": 20}}</x:v>
       </x:c>
       <x:c r="D18" s="67" t="str">
-        <x:v>{
-  "code": "COMMON-0000",
-  "message": "処理成功",
-  "timestamp": "2026-08-10T10:00:00+09:00",
-  "traceId": "7f3a9c01e2b44d8a",
-  "data": {
-    "content": [
-      {
-        "id": 1001,
-        "username": "サンプル",
-        "employeeId": 1001,
-        "employeeCode": "sample",
-        "name": "サンプル",
-        "status": "ACTIVE",
-        "roles": [
-          "SAMPLE"
-        ],
-        "version": 1
-      }
-    ],
-    "page": 1,
-    "size": 1,
-    "totalElements": 1001,
-    "totalPages": 1,
-    "first": true,
-    "last": true
-  }
-}</x:v>
+        <x:v>{"code": "COMMON-0000", "message": "処理成功", "timestamp": "2026-08-10T10:00:00+09:00", "traceId": "7f3a9c01e2b44d8a", "data": {"content": [{"id": 1001, "username": "サンプル", "employeeId": 1001, "employeeCode": "sample", "name": "サンプル", "status": "ACTIVE", "roles": ["ROLE-EMP"], "version": 1}], "page": 0, "size": 20, "totalElements": 1, "totalPages": 1, "first": true, "last": true}}</x:v>
       </x:c>
       <x:c r="E18" s="67" t="str">
         <x:v>200</x:v>
@@ -17398,7 +16700,7 @@
         <x:v>値は例。項目定義を正とする</x:v>
       </x:c>
     </x:row>
-    <x:row r="19" ht="120" customHeight="1">
+    <x:row r="19" ht="100" customHeight="1">
       <x:c r="A19" s="67" t="str">
         <x:v>API-USR-002</x:v>
       </x:c>
@@ -17406,37 +16708,10 @@
         <x:v>ユーザー詳細</x:v>
       </x:c>
       <x:c r="C19" s="67" t="str">
-        <x:v>{
-  "path": {
-    "id": 1001
-  }
-}</x:v>
+        <x:v>{"path": {"id": 1001}}</x:v>
       </x:c>
       <x:c r="D19" s="67" t="str">
-        <x:v>{
-  "code": "COMMON-0000",
-  "message": "処理成功",
-  "timestamp": "2026-08-10T10:00:00+09:00",
-  "traceId": "7f3a9c01e2b44d8a",
-  "data": {
-    "id": 1001,
-    "username": "サンプル",
-    "employee": {
-      "id": 1001,
-      "employeeCode": "EMP0001",
-      "name": "山田 太郎",
-      "departmentId": 10,
-      "departmentName": "開発部",
-      "employmentStatus": "EMPLOYED"
-    },
-    "status": "ACTIVE",
-    "lockedUntil": "2026-08-10T10:00:00+09:00",
-    "roles": [
-      "SAMPLE"
-    ],
-    "version": 1
-  }
-}</x:v>
+        <x:v>{"code": "COMMON-0000", "message": "処理成功", "timestamp": "2026-08-10T10:00:00+09:00", "traceId": "7f3a9c01e2b44d8a", "data": {"id": 1001, "username": "サンプル", "employee": {"id": 1001, "employeeCode": "EMP0001", "name": "山田 太郎", "departmentId": 10, "departmentName": "開発部", "employmentStatus": "EMPLOYED"}, "status": "LOCKED", "lockedUntil": "2026-08-10T10:30:00+09:00", "roles": ["ROLE-EMP"], "version": 1}}</x:v>
       </x:c>
       <x:c r="E19" s="67" t="str">
         <x:v>200</x:v>
@@ -17445,10 +16720,10 @@
         <x:v>application/json</x:v>
       </x:c>
       <x:c r="G19" s="67" t="str">
-        <x:v>値は例。項目定義を正とする</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="20" ht="120" customHeight="1">
+        <x:v>値は例。項目定義を正とする。Lock中Userの例。未設定・Lock解除済はlockedUntil=null。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" ht="100" customHeight="1">
       <x:c r="A20" s="67" t="str">
         <x:v>API-USR-003</x:v>
       </x:c>
@@ -17456,35 +16731,10 @@
         <x:v>ユーザー状態・Role更新</x:v>
       </x:c>
       <x:c r="C20" s="67" t="str">
-        <x:v>{
-  "path": {
-    "id": 1001
-  },
-  "body": {
-    "enabled": true,
-    "roleIds": [
-      1001,
-      1002
-    ],
-    "version": 1
-  }
-}</x:v>
+        <x:v>{"path": {"id": 1001}, "body": {"enabled": true, "roleIds": [1001, 1002], "version": 1}}</x:v>
       </x:c>
       <x:c r="D20" s="67" t="str">
-        <x:v>{
-  "code": "COMMON-0000",
-  "message": "処理成功",
-  "timestamp": "2026-08-10T10:00:00+09:00",
-  "traceId": "7f3a9c01e2b44d8a",
-  "data": {
-    "id": 1001,
-    "enabled": true,
-    "roles": [
-      "SAMPLE"
-    ],
-    "version": 1
-  }
-}</x:v>
+        <x:v>{"code": "COMMON-0000", "message": "処理成功", "timestamp": "2026-08-10T10:00:00+09:00", "traceId": "7f3a9c01e2b44d8a", "data": {"id": 1001, "enabled": true, "roles": ["ROLE-EMP"], "version": 2}}</x:v>
       </x:c>
       <x:c r="E20" s="67" t="str">
         <x:v>200</x:v>
@@ -17496,7 +16746,7 @@
         <x:v>値は例。項目定義を正とする</x:v>
       </x:c>
     </x:row>
-    <x:row r="21" ht="120" customHeight="1">
+    <x:row r="21" ht="100" customHeight="1">
       <x:c r="A21" s="67" t="str">
         <x:v>API-USR-004</x:v>
       </x:c>
@@ -17504,28 +16754,13 @@
         <x:v>パスワードリセット</x:v>
       </x:c>
       <x:c r="C21" s="67" t="str">
-        <x:v>{
-  "path": {
-    "id": 1001
-  },
-  "header": {
-    "X-Idempotency-Key": "550e8400-e29b-41d4-a716-446655440000"
-  }
-}</x:v>
+        <x:v>{"path": {"id": 1001}, "header": {"X-Idempotency-Key": "550e8400-e29b-41d4-a716-446655440000"}}</x:v>
       </x:c>
       <x:c r="D21" s="67" t="str">
-        <x:v>{
-  "code": "COMMON-0000",
-  "message": "処理成功",
-  "timestamp": "2026-08-10T10:00:00+09:00",
-  "traceId": "7f3a9c01e2b44d8a",
-  "data": {
-    "temporaryPassword": "********"
-  }
-}</x:v>
-      </x:c>
-      <x:c r="E21" s="67" t="str">
-        <x:v>201</x:v>
+        <x:v>{"code": "COMMON-0000", "message": "処理成功", "timestamp": "2026-08-10T10:00:00+09:00", "traceId": "7f3a9c01e2b44d8a", "data": {"temporaryPassword": "Train9!Sample"}}</x:v>
+      </x:c>
+      <x:c r="E21" s="67" t="n">
+        <x:v>200</x:v>
       </x:c>
       <x:c r="F21" s="67" t="str">
         <x:v>application/json</x:v>
@@ -17534,7 +16769,7 @@
         <x:v>値は例。項目定義を正とする</x:v>
       </x:c>
     </x:row>
-    <x:row r="22" ht="120" customHeight="1">
+    <x:row r="22" ht="100" customHeight="1">
       <x:c r="A22" s="67" t="str">
         <x:v>API-ROLE-001</x:v>
       </x:c>
@@ -17542,40 +16777,10 @@
         <x:v>Role一覧</x:v>
       </x:c>
       <x:c r="C22" s="67" t="str">
-        <x:v>{
-  "query": {
-    "status": "ACTIVE",
-    "page": 0,
-    "size": 20
-  }
-}</x:v>
+        <x:v>{"query": {"status": "ACTIVE", "page": 0, "size": 20}}</x:v>
       </x:c>
       <x:c r="D22" s="67" t="str">
-        <x:v>{
-  "code": "COMMON-0000",
-  "message": "処理成功",
-  "timestamp": "2026-08-10T10:00:00+09:00",
-  "traceId": "7f3a9c01e2b44d8a",
-  "data": {
-    "content": [
-      {
-        "id": 1001,
-        "roleCode": "sample",
-        "roleName": "サンプル",
-        "description": "sample",
-        "status": "ACTIVE",
-        "permissionCount": 1,
-        "version": 1
-      }
-    ],
-    "page": 1,
-    "size": 1,
-    "totalElements": 1001,
-    "totalPages": 1,
-    "first": true,
-    "last": true
-  }
-}</x:v>
+        <x:v>{"code": "COMMON-0000", "message": "処理成功", "timestamp": "2026-08-10T10:00:00+09:00", "traceId": "7f3a9c01e2b44d8a", "data": {"content": [{"id": 1001, "roleCode": "ROLE-EMP", "roleName": "サンプル", "description": "sample", "status": "ACTIVE", "permissionCount": 1, "version": 1}], "page": 0, "size": 20, "totalElements": 1, "totalPages": 1, "first": true, "last": true}}</x:v>
       </x:c>
       <x:c r="E22" s="67" t="str">
         <x:v>200</x:v>
@@ -17587,7 +16792,7 @@
         <x:v>値は例。項目定義を正とする</x:v>
       </x:c>
     </x:row>
-    <x:row r="23" ht="120" customHeight="1">
+    <x:row r="23" ht="100" customHeight="1">
       <x:c r="A23" s="67" t="str">
         <x:v>API-ROLE-002</x:v>
       </x:c>
@@ -17595,31 +16800,10 @@
         <x:v>Role詳細</x:v>
       </x:c>
       <x:c r="C23" s="67" t="str">
-        <x:v>{
-  "path": {
-    "id": 1001
-  }
-}</x:v>
+        <x:v>{"path": {"id": 1001}}</x:v>
       </x:c>
       <x:c r="D23" s="67" t="str">
-        <x:v>{
-  "code": "COMMON-0000",
-  "message": "処理成功",
-  "timestamp": "2026-08-10T10:00:00+09:00",
-  "traceId": "7f3a9c01e2b44d8a",
-  "data": {
-    "id": 1001,
-    "roleCode": "sample",
-    "roleName": "サンプル",
-    "description": "sample",
-    "status": "ACTIVE",
-    "permissionIds": [
-      1001,
-      1002
-    ],
-    "version": 1
-  }
-}</x:v>
+        <x:v>{"code": "COMMON-0000", "message": "処理成功", "timestamp": "2026-08-10T10:00:00+09:00", "traceId": "7f3a9c01e2b44d8a", "data": {"id": 1001, "roleCode": "ROLE-EMP", "roleName": "サンプル", "description": "sample", "status": "ACTIVE", "permissionIds": [1001, 1002], "version": 1}}</x:v>
       </x:c>
       <x:c r="E23" s="67" t="str">
         <x:v>200</x:v>
@@ -17631,7 +16815,7 @@
         <x:v>値は例。項目定義を正とする</x:v>
       </x:c>
     </x:row>
-    <x:row r="24" ht="120" customHeight="1">
+    <x:row r="24" ht="100" customHeight="1">
       <x:c r="A24" s="67" t="str">
         <x:v>API-ROLE-003</x:v>
       </x:c>
@@ -17639,33 +16823,10 @@
         <x:v>Role登録</x:v>
       </x:c>
       <x:c r="C24" s="67" t="str">
-        <x:v>{
-  "body": {
-    "roleCode": "sample",
-    "roleName": "サンプル",
-    "description": "sample",
-    "permissionIds": [
-      1001,
-      1002
-    ]
-  },
-  "header": {
-    "X-Idempotency-Key": "550e8400-e29b-41d4-a716-446655440000"
-  }
-}</x:v>
+        <x:v>{"body": {"roleCode": "ROLE-SUPPORT", "roleName": "サンプル", "description": "sample", "permissionIds": [1001, 1002]}, "header": {"X-Idempotency-Key": "550e8400-e29b-41d4-a716-446655440000"}}</x:v>
       </x:c>
       <x:c r="D24" s="67" t="str">
-        <x:v>{
-  "code": "COMMON-0000",
-  "message": "処理成功",
-  "timestamp": "2026-08-10T10:00:00+09:00",
-  "traceId": "7f3a9c01e2b44d8a",
-  "data": {
-    "id": 1001,
-    "roleCode": "sample",
-    "version": 1
-  }
-}</x:v>
+        <x:v>{"code": "COMMON-0000", "message": "処理成功", "timestamp": "2026-08-10T10:00:00+09:00", "traceId": "7f3a9c01e2b44d8a", "data": {"id": 1001, "roleCode": "ROLE-SUPPORT", "version": 1}}</x:v>
       </x:c>
       <x:c r="E24" s="67" t="str">
         <x:v>201</x:v>
@@ -17677,7 +16838,7 @@
         <x:v>値は例。項目定義を正とする</x:v>
       </x:c>
     </x:row>
-    <x:row r="25" ht="120" customHeight="1">
+    <x:row r="25" ht="100" customHeight="1">
       <x:c r="A25" s="67" t="str">
         <x:v>API-ROLE-004</x:v>
       </x:c>
@@ -17685,37 +16846,10 @@
         <x:v>Role更新</x:v>
       </x:c>
       <x:c r="C25" s="67" t="str">
-        <x:v>{
-  "path": {
-    "id": 1001
-  },
-  "body": {
-    "roleName": "サンプル",
-    "description": "sample",
-    "permissionIds": [
-      1001,
-      1002
-    ],
-    "version": 1
-  }
-}</x:v>
+        <x:v>{"path": {"id": 1001}, "body": {"roleName": "サンプル", "description": "sample", "permissionIds": [1001, 1002], "version": 1}}</x:v>
       </x:c>
       <x:c r="D25" s="67" t="str">
-        <x:v>{
-  "code": "COMMON-0000",
-  "message": "処理成功",
-  "timestamp": "2026-08-10T10:00:00+09:00",
-  "traceId": "7f3a9c01e2b44d8a",
-  "data": {
-    "id": 1001,
-    "status": "ACTIVE",
-    "permissionIds": [
-      1001,
-      1002
-    ],
-    "version": 1
-  }
-}</x:v>
+        <x:v>{"code": "COMMON-0000", "message": "処理成功", "timestamp": "2026-08-10T10:00:00+09:00", "traceId": "7f3a9c01e2b44d8a", "data": {"id": 1001, "status": "ACTIVE", "permissionIds": [1001, 1002], "version": 2}}</x:v>
       </x:c>
       <x:c r="E25" s="67" t="str">
         <x:v>200</x:v>
@@ -17727,7 +16861,7 @@
         <x:v>値は例。項目定義を正とする</x:v>
       </x:c>
     </x:row>
-    <x:row r="26" ht="120" customHeight="1">
+    <x:row r="26" ht="100" customHeight="1">
       <x:c r="A26" s="67" t="str">
         <x:v>API-ROLE-005</x:v>
       </x:c>
@@ -17735,28 +16869,10 @@
         <x:v>Role状態変更</x:v>
       </x:c>
       <x:c r="C26" s="67" t="str">
-        <x:v>{
-  "path": {
-    "id": 1001
-  },
-  "body": {
-    "status": "ACTIVE",
-    "version": 1
-  }
-}</x:v>
+        <x:v>{"path": {"id": 1001}, "body": {"status": "ACTIVE", "version": 1}}</x:v>
       </x:c>
       <x:c r="D26" s="67" t="str">
-        <x:v>{
-  "code": "COMMON-0000",
-  "message": "処理成功",
-  "timestamp": "2026-08-10T10:00:00+09:00",
-  "traceId": "7f3a9c01e2b44d8a",
-  "data": {
-    "id": 1001,
-    "status": "ACTIVE",
-    "version": 1
-  }
-}</x:v>
+        <x:v>{"code": "COMMON-0000", "message": "処理成功", "timestamp": "2026-08-10T10:00:00+09:00", "traceId": "7f3a9c01e2b44d8a", "data": {"id": 1001, "status": "ACTIVE", "version": 2}}</x:v>
       </x:c>
       <x:c r="E26" s="67" t="str">
         <x:v>200</x:v>
@@ -17768,7 +16884,7 @@
         <x:v>値は例。項目定義を正とする</x:v>
       </x:c>
     </x:row>
-    <x:row r="27" ht="120" customHeight="1">
+    <x:row r="27" ht="115" customHeight="1">
       <x:c r="A27" s="67" t="str">
         <x:v>API-LOG-001</x:v>
       </x:c>
@@ -17776,50 +16892,10 @@
         <x:v>操作Log検索</x:v>
       </x:c>
       <x:c r="C27" s="67" t="str">
-        <x:v>{
-  "query": {
-    "from": "sample",
-    "to": "sample",
-    "userId": 1001,
-    "module": "sample",
-    "action": "sample",
-    "result": "sample",
-    "traceId": 1001,
-    "page": 0,
-    "size": 20,
-    "sort": "sample"
-  }
-}</x:v>
+        <x:v>{"query": {"from": "2026-08-10T00:00:00+09:00", "to": "2026-08-10T23:59:59+09:00", "userId": 1001, "module": "sample", "action": "sample", "result": "SUCCESS", "traceId": "7f3a9c01e2b44d8a", "page": 0, "size": 20}}</x:v>
       </x:c>
       <x:c r="D27" s="67" t="str">
-        <x:v>{
-  "code": "COMMON-0000",
-  "message": "処理成功",
-  "timestamp": "2026-08-10T10:00:00+09:00",
-  "traceId": "7f3a9c01e2b44d8a",
-  "data": {
-    "content": [
-      {
-        "id": 1001,
-        "occurredAt": "2026-08-10T10:00:00+09:00",
-        "userId": 1001,
-        "username": "サンプル",
-        "module": "sample",
-        "action": "sample",
-        "result": "SUCCESS",
-        "targetType": "sample",
-        "targetId": 1001,
-        "traceId": "7f3a9c01e2b44d8a"
-      }
-    ],
-    "page": 1,
-    "size": 1,
-    "totalElements": 1001,
-    "totalPages": 1,
-    "first": true,
-    "last": true
-  }
-}</x:v>
+        <x:v>{"code": "COMMON-0000", "message": "処理成功", "timestamp": "2026-08-10T10:00:00+09:00", "traceId": "7f3a9c01e2b44d8a", "data": {"content": [{"id": 1001, "occurredAt": "2026-08-10T10:00:00+09:00", "userId": 1001, "username": "サンプル", "module": "sample", "action": "sample", "result": "SUCCESS", "targetType": "sample", "targetId": 1001, "traceId": "7f3a9c01e2b44d8a"}], "page": 0, "size": 20, "totalElements": 1, "totalPages": 1, "first": true, "last": true}}</x:v>
       </x:c>
       <x:c r="E27" s="67" t="str">
         <x:v>200</x:v>
@@ -17831,7 +16907,7 @@
         <x:v>値は例。項目定義を正とする</x:v>
       </x:c>
     </x:row>
-    <x:row r="28" ht="120" customHeight="1">
+    <x:row r="28" ht="115" customHeight="1">
       <x:c r="A28" s="67" t="str">
         <x:v>API-LOG-002</x:v>
       </x:c>
@@ -17839,35 +16915,10 @@
         <x:v>操作Log詳細</x:v>
       </x:c>
       <x:c r="C28" s="67" t="str">
-        <x:v>{
-  "path": {
-    "id": 1001
-  }
-}</x:v>
+        <x:v>{"path": {"id": 1001}}</x:v>
       </x:c>
       <x:c r="D28" s="67" t="str">
-        <x:v>{
-  "code": "COMMON-0000",
-  "message": "処理成功",
-  "timestamp": "2026-08-10T10:00:00+09:00",
-  "traceId": "7f3a9c01e2b44d8a",
-  "data": {
-    "id": 1001,
-    "occurredAt": "2026-08-10T10:00:00+09:00",
-    "userId": 1001,
-    "username": "サンプル",
-    "module": "sample",
-    "action": "sample",
-    "result": "SUCCESS",
-    "targetType": "sample",
-    "targetId": 1001,
-    "traceId": "7f3a9c01e2b44d8a",
-    "requestSummary": "sample",
-    "responseSummary": "sample",
-    "errorCode": "sample",
-    "ipAddress": "sample"
-  }
-}</x:v>
+        <x:v>{"code": "COMMON-0000", "message": "処理成功", "timestamp": "2026-08-10T10:00:00+09:00", "traceId": "7f3a9c01e2b44d8a", "data": {"id": 1001, "occurredAt": "2026-08-10T10:00:00+09:00", "userId": 1001, "username": "サンプル", "module": "sample", "action": "sample", "result": "SUCCESS", "targetType": "sample", "targetId": 1001, "traceId": "7f3a9c01e2b44d8a", "requestSummary": "sample", "responseSummary": "sample", "errorCode": null, "ipAddress": "192.0.2.10", "beforeValues": {"status": "TODO"}, "afterValues": {"status": "IN_PROGRESS"}}}</x:v>
       </x:c>
       <x:c r="E28" s="67" t="str">
         <x:v>200</x:v>

--- a/基本設計/10_API共通と認証_基本設計書.xlsx
+++ b/基本設計/10_API共通と認証_基本設計書.xlsx
@@ -2,14 +2,14 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00_表紙" sheetId="1" r:id="R84cc4ccf8b664f89"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_改訂履歴" sheetId="2" r:id="R14e99cd0657a4b1b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="18_API一覧" sheetId="19" r:id="R4387273638c94cc7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="19_API共通I-O" sheetId="20" r:id="R9124917b8c9c440d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="21_エラーコード" sheetId="22" r:id="R85e6074e324243fe"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="22_API処理・権限" sheetId="23" r:id="R1a362846ed4e40d2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="23_API項目定義" sheetId="24" r:id="R78c4b59547e34f12"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="24_APIサンプル" sheetId="25" r:id="R1b425e0f3f6e4f01"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00_表紙" sheetId="1" r:id="Rff23c7d0a3d34b70"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_改訂履歴" sheetId="2" r:id="R8585da9df2f9408c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="18_API一覧" sheetId="19" r:id="R2eca0f4f710f4063"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="19_API共通I-O" sheetId="20" r:id="R68e1531cb0584a34"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="21_エラーコード" sheetId="22" r:id="R46d09f5c4f1b4158"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="22_API処理・権限" sheetId="23" r:id="R9fb5a999c6554dd8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="23_API項目定義" sheetId="24" r:id="Ra848c900dfba438d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="24_APIサンプル" sheetId="25" r:id="Re37b4c435a794dea"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1320,7 +1320,7 @@
     <x:row r="11">
       <x:c r="B11"/>
       <x:c r="C11" s="203" t="str">
-        <x:v>Ver.2.5</x:v>
+        <x:v>Ver.2.6</x:v>
       </x:c>
       <x:c r="D11"/>
       <x:c r="E11"/>
@@ -1343,20 +1343,28 @@
         <x:v>版数</x:v>
       </x:c>
       <x:c r="D13" s="243" t="str">
-        <x:v>Ver.2.5</x:v>
-      </x:c>
-      <x:c r="E13" s="196"/>
-      <x:c r="F13" s="196"/>
+        <x:v>Ver.2.6</x:v>
+      </x:c>
+      <x:c r="E13" s="196" t="str">
+        <x:v>Ver.2.6</x:v>
+      </x:c>
+      <x:c r="F13" s="196" t="str">
+        <x:v>Ver.2.6</x:v>
+      </x:c>
     </x:row>
     <x:row r="14">
       <x:c r="C14" s="235" t="str">
         <x:v>改訂日</x:v>
       </x:c>
       <x:c r="D14" s="243" t="str">
-        <x:v>2026-09-24</x:v>
-      </x:c>
-      <x:c r="E14" s="196"/>
-      <x:c r="F14" s="196"/>
+        <x:v>2026-09-28</x:v>
+      </x:c>
+      <x:c r="E14" s="196" t="str">
+        <x:v>2026-09-28</x:v>
+      </x:c>
+      <x:c r="F14" s="196" t="str">
+        <x:v>2026-09-28</x:v>
+      </x:c>
     </x:row>
     <x:row r="15">
       <x:c r="C15" s="235" t="str">
@@ -1375,10 +1383,14 @@
         <x:v>状態</x:v>
       </x:c>
       <x:c r="D16" s="243" t="str">
-        <x:v>Review中</x:v>
-      </x:c>
-      <x:c r="E16" s="196"/>
-      <x:c r="F16" s="196"/>
+        <x:v>修正済</x:v>
+      </x:c>
+      <x:c r="E16" s="196" t="str">
+        <x:v>修正済</x:v>
+      </x:c>
+      <x:c r="F16" s="196" t="str">
+        <x:v>修正済</x:v>
+      </x:c>
     </x:row>
     <x:row r="17" ht="26" customHeight="1">
       <x:c r="A17" s="245"/>
@@ -1402,31 +1414,73 @@
     </x:row>
     <x:row r="19">
       <x:c r="A19"/>
-      <x:c r="B19"/>
-      <x:c r="C19"/>
-      <x:c r="D19"/>
-      <x:c r="E19"/>
-      <x:c r="F19"/>
-      <x:c r="G19"/>
-      <x:c r="H19"/>
+      <x:c r="B19" t="str">
+        <x:v>基準Baseline：BL-2026-09-24。変更管理：CHG-AUTH-20260928-01。本改訂はログイン限流・Lock境界の明確化。変更承認後に次Baselineへ組み入れる。</x:v>
+      </x:c>
+      <x:c r="C19" t="str">
+        <x:v>基準Baseline：BL-2026-09-24。変更管理：CHG-AUTH-20260928-01。本改訂はログイン限流・Lock境界の明確化。変更承認後に次Baselineへ組み入れる。</x:v>
+      </x:c>
+      <x:c r="D19" t="str">
+        <x:v>基準Baseline：BL-2026-09-24。変更管理：CHG-AUTH-20260928-01。本改訂はログイン限流・Lock境界の明確化。変更承認後に次Baselineへ組み入れる。</x:v>
+      </x:c>
+      <x:c r="E19" t="str">
+        <x:v>基準Baseline：BL-2026-09-24。変更管理：CHG-AUTH-20260928-01。本改訂はログイン限流・Lock境界の明確化。変更承認後に次Baselineへ組み入れる。</x:v>
+      </x:c>
+      <x:c r="F19" t="str">
+        <x:v>基準Baseline：BL-2026-09-24。変更管理：CHG-AUTH-20260928-01。本改訂はログイン限流・Lock境界の明確化。変更承認後に次Baselineへ組み入れる。</x:v>
+      </x:c>
+      <x:c r="G19" t="str">
+        <x:v>基準Baseline：BL-2026-09-24。変更管理：CHG-AUTH-20260928-01。本改訂はログイン限流・Lock境界の明確化。変更承認後に次Baselineへ組み入れる。</x:v>
+      </x:c>
+      <x:c r="H19" t="str">
+        <x:v>基準Baseline：BL-2026-09-24。変更管理：CHG-AUTH-20260928-01。本改訂はログイン限流・Lock境界の明確化。変更承認後に次Baselineへ組み入れる。</x:v>
+      </x:c>
     </x:row>
     <x:row r="20">
-      <x:c r="B20"/>
-      <x:c r="C20"/>
-      <x:c r="D20"/>
-      <x:c r="E20"/>
-      <x:c r="F20"/>
-      <x:c r="G20"/>
-      <x:c r="H20"/>
+      <x:c r="B20" t="str">
+        <x:v>基準Baseline：BL-2026-09-24。変更管理：CHG-AUTH-20260928-01。本改訂はログイン限流・Lock境界の明確化。変更承認後に次Baselineへ組み入れる。</x:v>
+      </x:c>
+      <x:c r="C20" t="str">
+        <x:v>基準Baseline：BL-2026-09-24。変更管理：CHG-AUTH-20260928-01。本改訂はログイン限流・Lock境界の明確化。変更承認後に次Baselineへ組み入れる。</x:v>
+      </x:c>
+      <x:c r="D20" t="str">
+        <x:v>基準Baseline：BL-2026-09-24。変更管理：CHG-AUTH-20260928-01。本改訂はログイン限流・Lock境界の明確化。変更承認後に次Baselineへ組み入れる。</x:v>
+      </x:c>
+      <x:c r="E20" t="str">
+        <x:v>基準Baseline：BL-2026-09-24。変更管理：CHG-AUTH-20260928-01。本改訂はログイン限流・Lock境界の明確化。変更承認後に次Baselineへ組み入れる。</x:v>
+      </x:c>
+      <x:c r="F20" t="str">
+        <x:v>基準Baseline：BL-2026-09-24。変更管理：CHG-AUTH-20260928-01。本改訂はログイン限流・Lock境界の明確化。変更承認後に次Baselineへ組み入れる。</x:v>
+      </x:c>
+      <x:c r="G20" t="str">
+        <x:v>基準Baseline：BL-2026-09-24。変更管理：CHG-AUTH-20260928-01。本改訂はログイン限流・Lock境界の明確化。変更承認後に次Baselineへ組み入れる。</x:v>
+      </x:c>
+      <x:c r="H20" t="str">
+        <x:v>基準Baseline：BL-2026-09-24。変更管理：CHG-AUTH-20260928-01。本改訂はログイン限流・Lock境界の明確化。変更承認後に次Baselineへ組み入れる。</x:v>
+      </x:c>
     </x:row>
     <x:row r="21">
-      <x:c r="B21" s="240"/>
-      <x:c r="C21" s="240"/>
-      <x:c r="D21" s="240"/>
-      <x:c r="E21" s="240"/>
-      <x:c r="F21" s="240"/>
-      <x:c r="G21" s="240"/>
-      <x:c r="H21" s="240"/>
+      <x:c r="B21" s="240" t="str">
+        <x:v>基準Baseline：BL-2026-09-24。変更管理：CHG-AUTH-20260928-01。本改訂はログイン限流・Lock境界の明確化。変更承認後に次Baselineへ組み入れる。</x:v>
+      </x:c>
+      <x:c r="C21" s="240" t="str">
+        <x:v>基準Baseline：BL-2026-09-24。変更管理：CHG-AUTH-20260928-01。本改訂はログイン限流・Lock境界の明確化。変更承認後に次Baselineへ組み入れる。</x:v>
+      </x:c>
+      <x:c r="D21" s="240" t="str">
+        <x:v>基準Baseline：BL-2026-09-24。変更管理：CHG-AUTH-20260928-01。本改訂はログイン限流・Lock境界の明確化。変更承認後に次Baselineへ組み入れる。</x:v>
+      </x:c>
+      <x:c r="E21" s="240" t="str">
+        <x:v>基準Baseline：BL-2026-09-24。変更管理：CHG-AUTH-20260928-01。本改訂はログイン限流・Lock境界の明確化。変更承認後に次Baselineへ組み入れる。</x:v>
+      </x:c>
+      <x:c r="F21" s="240" t="str">
+        <x:v>基準Baseline：BL-2026-09-24。変更管理：CHG-AUTH-20260928-01。本改訂はログイン限流・Lock境界の明確化。変更承認後に次Baselineへ組み入れる。</x:v>
+      </x:c>
+      <x:c r="G21" s="240" t="str">
+        <x:v>基準Baseline：BL-2026-09-24。変更管理：CHG-AUTH-20260928-01。本改訂はログイン限流・Lock境界の明確化。変更承認後に次Baselineへ組み入れる。</x:v>
+      </x:c>
+      <x:c r="H21" s="240" t="str">
+        <x:v>基準Baseline：BL-2026-09-24。変更管理：CHG-AUTH-20260928-01。本改訂はログイン限流・Lock境界の明確化。変更承認後に次Baselineへ組み入れる。</x:v>
+      </x:c>
     </x:row>
     <x:row r="22">
       <x:c r="B22"/>
@@ -1518,15 +1572,29 @@
     </x:row>
     <x:row r="4" ht="24" customHeight="1">
       <x:c r="A4" s="246" t="str">
-        <x:v>版数：Ver.2.5    改訂日：2026-09-24    Baseline：BL-2026-09-24</x:v>
-      </x:c>
-      <x:c r="B4" s="63"/>
-      <x:c r="C4" s="63"/>
-      <x:c r="D4" s="246"/>
-      <x:c r="E4" s="63"/>
-      <x:c r="F4" s="63"/>
-      <x:c r="G4" s="63"/>
-      <x:c r="H4" s="63"/>
+        <x:v>版数：Ver.2.6    改訂日：2026-09-28    基準Baseline：BL-2026-09-24</x:v>
+      </x:c>
+      <x:c r="B4" s="63" t="str">
+        <x:v>版数：Ver.2.6    改訂日：2026-09-28    基準Baseline：BL-2026-09-24</x:v>
+      </x:c>
+      <x:c r="C4" s="63" t="str">
+        <x:v>版数：Ver.2.6    改訂日：2026-09-28    基準Baseline：BL-2026-09-24</x:v>
+      </x:c>
+      <x:c r="D4" s="246" t="str">
+        <x:v>版数：Ver.2.6    改訂日：2026-09-28    基準Baseline：BL-2026-09-24</x:v>
+      </x:c>
+      <x:c r="E4" s="63" t="str">
+        <x:v>版数：Ver.2.6    改訂日：2026-09-28    基準Baseline：BL-2026-09-24</x:v>
+      </x:c>
+      <x:c r="F4" s="63" t="str">
+        <x:v>版数：Ver.2.6    改訂日：2026-09-28    基準Baseline：BL-2026-09-24</x:v>
+      </x:c>
+      <x:c r="G4" s="63" t="str">
+        <x:v>版数：Ver.2.6    改訂日：2026-09-28    基準Baseline：BL-2026-09-24</x:v>
+      </x:c>
+      <x:c r="H4" s="63" t="str">
+        <x:v>版数：Ver.2.6    改訂日：2026-09-28    基準Baseline：BL-2026-09-24</x:v>
+      </x:c>
     </x:row>
     <x:row r="5">
       <x:c r="A5"/>
@@ -1916,6 +1984,32 @@
       </x:c>
       <x:c r="H20" s="245" t="str">
         <x:v>BL-2026-09-24。責任者・Review者・承認者はProject Leaderが記入。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" ht="115" customHeight="1">
+      <x:c r="A21" s="241" t="str">
+        <x:v>Ver.2.6</x:v>
+      </x:c>
+      <x:c r="B21" s="241" t="str">
+        <x:v>2026-09-28</x:v>
+      </x:c>
+      <x:c r="C21" s="241" t="str">
+        <x:v>ログイン試行制限の独立固定窓、5回目Lock成立・満了後再開を明確化。CHG-AUTH-20260928-01</x:v>
+      </x:c>
+      <x:c r="D21" s="241" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="E21" s="241" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="F21" s="241" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="G21" s="241" t="str">
+        <x:v>修正済</x:v>
+      </x:c>
+      <x:c r="H21" s="241" t="str">
+        <x:v>変更指示に基づく改訂。新Baseline承認は別途記録。</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -1985,15 +2079,19 @@
     </x:row>
     <x:row r="4">
       <x:c r="A4" s="246" t="str">
-        <x:v>版数：Ver.2.5</x:v>
-      </x:c>
-      <x:c r="B4" s="63"/>
+        <x:v>版数：Ver.2.6</x:v>
+      </x:c>
+      <x:c r="B4" s="63" t="str">
+        <x:v>版数：Ver.2.6</x:v>
+      </x:c>
       <x:c r="C4" s="63"/>
       <x:c r="D4" s="63"/>
       <x:c r="E4" s="246" t="str">
-        <x:v>改訂日：2026-09-24</x:v>
-      </x:c>
-      <x:c r="F4" s="63"/>
+        <x:v>改訂日：2026-09-28</x:v>
+      </x:c>
+      <x:c r="F4" s="63" t="str">
+        <x:v>改訂日：2026-09-28</x:v>
+      </x:c>
       <x:c r="G4" s="63"/>
       <x:c r="H4" s="63"/>
       <x:c r="I4" s="63"/>
@@ -3008,13 +3106,17 @@
     </x:row>
     <x:row r="4">
       <x:c r="A4" s="247" t="str">
-        <x:v>版数：Ver.2.5</x:v>
-      </x:c>
-      <x:c r="B4" s="23"/>
+        <x:v>版数：Ver.2.6</x:v>
+      </x:c>
+      <x:c r="B4" s="23" t="str">
+        <x:v>版数：Ver.2.6</x:v>
+      </x:c>
       <x:c r="C4" s="248" t="str">
-        <x:v>Ver.2.5</x:v>
-      </x:c>
-      <x:c r="D4" s="21"/>
+        <x:v>Ver.2.6</x:v>
+      </x:c>
+      <x:c r="D4" s="21" t="str">
+        <x:v>Ver.2.6</x:v>
+      </x:c>
       <x:c r="E4" s="23" t="str">
         <x:v>作成日</x:v>
       </x:c>
@@ -3946,7 +4048,7 @@
       </x:c>
       <x:c r="H12" s="256" t="str"/>
     </x:row>
-    <x:row r="13" ht="42" customHeight="1">
+    <x:row r="13" ht="105" customHeight="1">
       <x:c r="A13" s="255" t="str">
         <x:v>AUTH-4001</x:v>
       </x:c>
@@ -3968,7 +4070,9 @@
       <x:c r="G13" s="255" t="str">
         <x:v>不可</x:v>
       </x:c>
-      <x:c r="H13" s="255" t="str"/>
+      <x:c r="H13" s="255" t="str">
+        <x:v>API-AUTH-001：不存在User、またはBR-AUTH-002の第1～4回Password不一致（Lock満了後の最初の失敗を含む）。</x:v>
+      </x:c>
     </x:row>
     <x:row r="14" ht="42" customHeight="1">
       <x:c r="A14" s="256" t="str">
@@ -4018,7 +4122,7 @@
       </x:c>
       <x:c r="H15" s="255" t="str"/>
     </x:row>
-    <x:row r="16" ht="42" customHeight="1">
+    <x:row r="16" ht="105" customHeight="1">
       <x:c r="A16" s="256" t="str">
         <x:v>AUTH-4004</x:v>
       </x:c>
@@ -4038,9 +4142,11 @@
         <x:v>WARN</x:v>
       </x:c>
       <x:c r="G16" s="256" t="str">
-        <x:v>不可</x:v>
-      </x:c>
-      <x:c r="H16" s="256" t="str"/>
+        <x:v>Lock満了後可</x:v>
+      </x:c>
+      <x:c r="H16" s="256" t="str">
+        <x:v>API-AUTH-001：第5回Password失敗でLock成立した当該Request、およびnow&lt;locked_untilのRequest。状態更新・満了解除は16／28 BR-AUTH-002を正本とする。</x:v>
+      </x:c>
     </x:row>
     <x:row r="17" ht="42" customHeight="1">
       <x:c r="A17" s="255" t="str">
@@ -4090,7 +4196,7 @@
       </x:c>
       <x:c r="H18" s="256" t="str"/>
     </x:row>
-    <x:row r="19" ht="57" customHeight="1">
+    <x:row r="19" ht="105" customHeight="1">
       <x:c r="A19" s="255" t="str">
         <x:v>AUTH-4290</x:v>
       </x:c>
@@ -4113,7 +4219,7 @@
         <x:v>可（60秒後）</x:v>
       </x:c>
       <x:c r="H19" s="255" t="str">
-        <x:v>IP/username単位10回/分。Retry-After: 60を返却</x:v>
+        <x:v>19／35・36のIP／username独立固定Window制限を適用。どちらか超過で429。Retry-After:60を返却。</x:v>
       </x:c>
     </x:row>
     <x:row r="20">
@@ -4363,14 +4469,14 @@
         <x:v>版数</x:v>
       </x:c>
       <x:c r="B4" s="63" t="str">
-        <x:v>Ver.2.5</x:v>
+        <x:v>Ver.2.6</x:v>
       </x:c>
       <x:c r="C4" s="63"/>
       <x:c r="D4" s="62" t="str">
         <x:v>改訂日</x:v>
       </x:c>
       <x:c r="E4" s="63" t="str">
-        <x:v>2026-09-24</x:v>
+        <x:v>2026-09-28</x:v>
       </x:c>
       <x:c r="F4" s="63"/>
       <x:c r="G4" s="63"/>
@@ -4424,7 +4530,7 @@
         <x:v>利用元・補足</x:v>
       </x:c>
     </x:row>
-    <x:row r="8" ht="182" customHeight="1">
+    <x:row r="8" ht="140" customHeight="1">
       <x:c r="A8" s="67" t="str">
         <x:v>API-AUTH-001</x:v>
       </x:c>
@@ -4432,7 +4538,7 @@
         <x:v>ログイン</x:v>
       </x:c>
       <x:c r="C8" s="67" t="str">
-        <x:v>1) 02の対応Permission/Data Scopeを判定。2) 23_API項目定義に従い入力を検証。3) users,roles,permissions,login_histories / Redisを参照/更新。4) TX-011の境界でCommit/Rollback。5) 23_API項目定義の正常Responseを返す。</x:v>
+        <x:v>1) 公開APIとして入力検証。2) 19／35・36の試行制限。3) users取得、状態判定・Lock満了解除・Password照合を16／28 BR-AUTH-001/002に従い実施。4) 正常は権限参照・Token発行、認証結果履歴を記録。5) TX-011でCommit/Rollback後、23のResponse／21のErrorを返却。</x:v>
       </x:c>
       <x:c r="D8" s="67" t="str">
         <x:v>02／13_API権限対応 API-AUTH-001
@@ -4448,10 +4554,10 @@
       <x:c r="G8" s="67" t="str">
         <x:v>traceId付きLog。Password/Token/個人情報はMask</x:v>
       </x:c>
-      <x:c r="H8" s="203" t="str">
-        <x:v>users,roles,permissions,login_histories / Redis</x:v>
-      </x:c>
-      <x:c r="I8" s="203" t="str">
+      <x:c r="H8" s="241" t="str">
+        <x:v>users,employees,roles,user_roles,permissions,role_permissions,refresh_tokens,login_histories / Redis</x:v>
+      </x:c>
+      <x:c r="I8" s="241" t="str">
         <x:v>SCR-001</x:v>
       </x:c>
     </x:row>
@@ -5171,7 +5277,7 @@
         <x:v>版数</x:v>
       </x:c>
       <x:c r="B4" s="63" t="str">
-        <x:v>Ver.2.5</x:v>
+        <x:v>Ver.2.6</x:v>
       </x:c>
       <x:c r="C4" s="139"/>
       <x:c r="D4" s="139"/>
@@ -5180,7 +5286,7 @@
         <x:v>改訂日</x:v>
       </x:c>
       <x:c r="G4" s="63" t="str">
-        <x:v>2026-09-24</x:v>
+        <x:v>2026-09-28</x:v>
       </x:c>
       <x:c r="H4" s="139"/>
       <x:c r="I4" s="139"/>
@@ -16390,14 +16496,14 @@
         <x:v>版数</x:v>
       </x:c>
       <x:c r="B4" s="63" t="str">
-        <x:v>Ver.2.5</x:v>
+        <x:v>Ver.2.6</x:v>
       </x:c>
       <x:c r="C4" s="139"/>
       <x:c r="D4" s="174" t="str">
         <x:v>改訂日</x:v>
       </x:c>
       <x:c r="E4" s="63" t="str">
-        <x:v>2026-09-24</x:v>
+        <x:v>2026-09-28</x:v>
       </x:c>
       <x:c r="F4" s="139"/>
       <x:c r="G4" s="139"/>

--- a/基本設計/10_API共通と認証_基本設計書.xlsx
+++ b/基本設計/10_API共通と認証_基本設計書.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00_表紙" sheetId="1" r:id="Rff23c7d0a3d34b70"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_改訂履歴" sheetId="2" r:id="R8585da9df2f9408c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="18_API一覧" sheetId="19" r:id="R2eca0f4f710f4063"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="19_API共通I-O" sheetId="20" r:id="R68e1531cb0584a34"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="21_エラーコード" sheetId="22" r:id="R46d09f5c4f1b4158"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="22_API処理・権限" sheetId="23" r:id="R9fb5a999c6554dd8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="23_API項目定義" sheetId="24" r:id="Ra848c900dfba438d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="24_APIサンプル" sheetId="25" r:id="Re37b4c435a794dea"/>
-  </x:sheets>
-</x:workbook>
+<ns0:workbook xmlns:ns0="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <ns0:sheets>
+    <ns0:sheet name="00_表紙" sheetId="1" ns1:id="R26acc7e2e7ca4377"/>
+    <ns0:sheet name="01_改訂履歴" sheetId="2" ns1:id="Re12fe77be41a478f"/>
+    <ns0:sheet name="18_API一覧" sheetId="19" ns1:id="R977d33cb9cff4dbe"/>
+    <ns0:sheet name="19_API共通I-O" sheetId="20" ns1:id="Rf1b51900966f4e51"/>
+    <ns0:sheet name="21_エラーコード" sheetId="22" ns1:id="R94f16b2069c64e54"/>
+    <ns0:sheet name="22_API処理・権限" sheetId="23" ns1:id="Ra68a01ad3197493f"/>
+    <ns0:sheet name="23_API項目定義" sheetId="24" ns1:id="R01db1a4d85f94e94"/>
+    <ns0:sheet name="24_APIサンプル" sheetId="25" ns1:id="R398209dcf4de41bb"/>
+  </ns0:sheets>
+</ns0:workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1320,7 +1320,7 @@
     <x:row r="11">
       <x:c r="B11"/>
       <x:c r="C11" s="203" t="str">
-        <x:v>Ver.2.6</x:v>
+        <x:v>Ver.2.7</x:v>
       </x:c>
       <x:c r="D11"/>
       <x:c r="E11"/>
@@ -1343,7 +1343,7 @@
         <x:v>版数</x:v>
       </x:c>
       <x:c r="D13" s="243" t="str">
-        <x:v>Ver.2.6</x:v>
+        <x:v>Ver.2.7</x:v>
       </x:c>
       <x:c r="E13" s="196" t="str">
         <x:v>Ver.2.6</x:v>
@@ -1357,7 +1357,7 @@
         <x:v>改訂日</x:v>
       </x:c>
       <x:c r="D14" s="243" t="str">
-        <x:v>2026-09-28</x:v>
+        <x:v>2026-09-29</x:v>
       </x:c>
       <x:c r="E14" s="196" t="str">
         <x:v>2026-09-28</x:v>
@@ -1572,7 +1572,7 @@
     </x:row>
     <x:row r="4" ht="24" customHeight="1">
       <x:c r="A4" s="246" t="str">
-        <x:v>版数：Ver.2.6    改訂日：2026-09-28    基準Baseline：BL-2026-09-24</x:v>
+        <x:v>版数：Ver.2.7    改訂日：2026-09-29    基準Baseline：BL-2026-09-24</x:v>
       </x:c>
       <x:c r="B4" s="63" t="str">
         <x:v>版数：Ver.2.6    改訂日：2026-09-28    基準Baseline：BL-2026-09-24</x:v>
@@ -2010,6 +2010,32 @@
       </x:c>
       <x:c r="H21" s="241" t="str">
         <x:v>変更指示に基づく改訂。新Baseline承認は別途記録。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" ht="95" customHeight="1">
+      <x:c r="A22" t="str">
+        <x:v>Ver.2.7</x:v>
+      </x:c>
+      <x:c r="B22" t="str">
+        <x:v>2026-09-29</x:v>
+      </x:c>
+      <x:c r="C22" t="str">
+        <x:v>CHG-MENU-20260929-01：U-01対応。固定Menu Code・menus契約・下流Bindingを整合。既存権限・Route・DBは変更なし。</x:v>
+      </x:c>
+      <x:c r="D22" t="str">
+        <x:v>－</x:v>
+      </x:c>
+      <x:c r="E22" t="str">
+        <x:v>－</x:v>
+      </x:c>
+      <x:c r="F22" t="str">
+        <x:v>－</x:v>
+      </x:c>
+      <x:c r="G22" t="str">
+        <x:v>修正済</x:v>
+      </x:c>
+      <x:c r="H22" t="str">
+        <x:v>方式合意に基づく補完。成果物の正式承認は別途。</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -2079,7 +2105,7 @@
     </x:row>
     <x:row r="4">
       <x:c r="A4" s="246" t="str">
-        <x:v>版数：Ver.2.6</x:v>
+        <x:v>版数：Ver.2.7</x:v>
       </x:c>
       <x:c r="B4" s="63" t="str">
         <x:v>版数：Ver.2.6</x:v>
@@ -2087,7 +2113,7 @@
       <x:c r="C4" s="63"/>
       <x:c r="D4" s="63"/>
       <x:c r="E4" s="246" t="str">
-        <x:v>改訂日：2026-09-28</x:v>
+        <x:v>改訂日：2026-09-29</x:v>
       </x:c>
       <x:c r="F4" s="63" t="str">
         <x:v>改訂日：2026-09-28</x:v>
@@ -3106,13 +3132,13 @@
     </x:row>
     <x:row r="4">
       <x:c r="A4" s="247" t="str">
-        <x:v>版数：Ver.2.6</x:v>
+        <x:v>版数：Ver.2.7</x:v>
       </x:c>
       <x:c r="B4" s="23" t="str">
         <x:v>版数：Ver.2.6</x:v>
       </x:c>
       <x:c r="C4" s="248" t="str">
-        <x:v>Ver.2.6</x:v>
+        <x:v>Ver.2.7</x:v>
       </x:c>
       <x:c r="D4" s="21" t="str">
         <x:v>Ver.2.6</x:v>
@@ -4469,14 +4495,14 @@
         <x:v>版数</x:v>
       </x:c>
       <x:c r="B4" s="63" t="str">
-        <x:v>Ver.2.6</x:v>
+        <x:v>Ver.2.7</x:v>
       </x:c>
       <x:c r="C4" s="63"/>
       <x:c r="D4" s="62" t="str">
         <x:v>改訂日</x:v>
       </x:c>
       <x:c r="E4" s="63" t="str">
-        <x:v>2026-09-28</x:v>
+        <x:v>2026-09-29</x:v>
       </x:c>
       <x:c r="F4" s="63"/>
       <x:c r="G4" s="63"/>
@@ -4623,7 +4649,7 @@
         <x:v>共通Interceptor</x:v>
       </x:c>
     </x:row>
-    <x:row r="11" ht="30" customHeight="1">
+    <x:row r="11" ht="125" customHeight="1">
       <x:c r="A11" s="67" t="str">
         <x:v>API-AUTH-004</x:v>
       </x:c>
@@ -4631,7 +4657,7 @@
         <x:v>現在ユーザー取得</x:v>
       </x:c>
       <x:c r="C11" s="67" t="str">
-        <x:v>1) 02の対応Permission/Data Scopeを判定。2) 23_API項目定義に従い入力を検証。3) users,employees,roles,permissionsを参照。4) 業務Dataの更新なし。5) 23_API項目定義の正常Responseを返す。</x:v>
+        <x:v>1) 02の対応Permission/Data Scopeを判定。2) 23_API項目定義に従い入力を検証。3) users,employees,roles,permissionsを参照。4) 業務Dataの更新なし。5) menusを02／10_メニュー権限の固定Code・Role/Permission条件・表示順で生成する。6) 23_API項目定義の正常Responseを返す。</x:v>
       </x:c>
       <x:c r="D11" s="67" t="str">
         <x:v>02／13_API権限対応 API-AUTH-004
@@ -5277,7 +5303,7 @@
         <x:v>版数</x:v>
       </x:c>
       <x:c r="B4" s="63" t="str">
-        <x:v>Ver.2.6</x:v>
+        <x:v>Ver.2.7</x:v>
       </x:c>
       <x:c r="C4" s="139"/>
       <x:c r="D4" s="139"/>
@@ -5286,7 +5312,7 @@
         <x:v>改訂日</x:v>
       </x:c>
       <x:c r="G4" s="63" t="str">
-        <x:v>2026-09-28</x:v>
+        <x:v>2026-09-29</x:v>
       </x:c>
       <x:c r="H4" s="139"/>
       <x:c r="I4" s="139"/>
@@ -6638,7 +6664,7 @@
         <x:v>permissions + role_permissions + user_roles</x:v>
       </x:c>
     </x:row>
-    <x:row r="45" ht="15" hidden="0" customHeight="1">
+    <x:row r="45" ht="115" hidden="0" customHeight="1">
       <x:c r="A45" s="67" t="str">
         <x:v>API-AUTH-004</x:v>
       </x:c>
@@ -6661,16 +6687,16 @@
         <x:v>-</x:v>
       </x:c>
       <x:c r="H45" s="67" t="str">
-        <x:v>-</x:v>
+        <x:v>02_権限基本設計書／10_メニュー権限／2節 Menu Code（大文字小文字区別）</x:v>
       </x:c>
       <x:c r="I45" s="67" t="str">
         <x:v>不可</x:v>
       </x:c>
       <x:c r="J45" s="67" t="str">
-        <x:v>menus</x:v>
+        <x:v>固定Menu Code配列。空配列可、配列・要素ともNull不可、各要素String。重複なし、02の表示順昇順。表示名・Routeは返却しない。</x:v>
       </x:c>
       <x:c r="K45" s="67" t="str">
-        <x:v>permissionsからMenu生成</x:v>
+        <x:v>02／10_メニュー権限の生成規則に従い、roles・permissionsから生成（DB列追加なし）。</x:v>
       </x:c>
     </x:row>
     <x:row r="46" ht="15" hidden="0" customHeight="1">
@@ -16430,6 +16456,41 @@
         <x:v>業務条件</x:v>
       </x:c>
       <x:c r="L327" s="241"/>
+    </x:row>
+    <x:row r="328" ht="160" customHeight="1">
+      <x:c r="A328" t="str">
+        <x:v>API-AUTH-004</x:v>
+      </x:c>
+      <x:c r="B328" t="str">
+        <x:v>Response</x:v>
+      </x:c>
+      <x:c r="C328" t="str">
+        <x:v>body</x:v>
+      </x:c>
+      <x:c r="D328" t="str">
+        <x:v>response.body.data.user.menus[]</x:v>
+      </x:c>
+      <x:c r="E328" t="str">
+        <x:v>String</x:v>
+      </x:c>
+      <x:c r="F328" t="str">
+        <x:v>要素存在時必須</x:v>
+      </x:c>
+      <x:c r="G328" t="str">
+        <x:v>02の固定Code値域</x:v>
+      </x:c>
+      <x:c r="H328" t="str">
+        <x:v>02／10_メニュー権限 2節のMenu Code</x:v>
+      </x:c>
+      <x:c r="I328" t="str">
+        <x:v>不可</x:v>
+      </x:c>
+      <x:c r="J328" t="str">
+        <x:v>固定Code。Clientは未知Stringを無視・重複を表示時集約する。欠落・Null・非String要素は共通Schema Error。未知StringのみはSchema ErrorにせずMenu候補から除外。</x:v>
+      </x:c>
+      <x:c r="K328" t="str">
+        <x:v>02／10_メニュー権限</x:v>
+      </x:c>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -16496,14 +16557,14 @@
         <x:v>版数</x:v>
       </x:c>
       <x:c r="B4" s="63" t="str">
-        <x:v>Ver.2.6</x:v>
+        <x:v>Ver.2.7</x:v>
       </x:c>
       <x:c r="C4" s="139"/>
       <x:c r="D4" s="174" t="str">
         <x:v>改訂日</x:v>
       </x:c>
       <x:c r="E4" s="63" t="str">
-        <x:v>2026-09-28</x:v>
+        <x:v>2026-09-29</x:v>
       </x:c>
       <x:c r="F4" s="139"/>
       <x:c r="G4" s="139"/>
@@ -16622,7 +16683,7 @@
         <x:v>値は例。項目定義を正とする</x:v>
       </x:c>
     </x:row>
-    <x:row r="11" ht="100" customHeight="1">
+    <x:row r="11" ht="270" customHeight="1">
       <x:c r="A11" s="67" t="str">
         <x:v>API-AUTH-004</x:v>
       </x:c>
@@ -16633,7 +16694,7 @@
         <x:v>{}</x:v>
       </x:c>
       <x:c r="D11" s="67" t="str">
-        <x:v>{"code": "COMMON-0000", "message": "処理成功", "timestamp": "2026-08-10T10:00:00+09:00", "traceId": "7f3a9c01e2b44d8a", "data": {"user": {"id": 1001, "employeeId": 1001, "name": "サンプル", "roles": ["ROLE-EMP"], "permissions": ["PERM-TASK-READ", "PERM-TASK-PROGRESS"], "menus": ["マイタスク"], "passwordMustChange": false}}}</x:v>
+        <x:v>{"code":"COMMON-0000","message":"処理成功","timestamp":"2026-08-10T10:00:00+09:00","traceId":"7f3a9c01e2b44d8a","data":{"user":{"id":1001,"employeeId":1001,"name":"サンプル","roles":["ROLE-EMP"],"permissions":["PERM-DASH-READ","PERM-PRJ-READ","PERM-TASK-READ","PERM-TASK-PROGRESS","PERM-RPT-SELF","PERM-FILE-WRITE"],"menus":["MENU-HOME","MENU-PROJECTS","MENU-MY-PROJECTS","MENU-MY-TASKS","MENU-TASK-BOARD","MENU-MY-REPORTS","MENU-NOTIFICATIONS"],"passwordMustChange":false}}}</x:v>
       </x:c>
       <x:c r="E11" s="67" t="str">
         <x:v>200</x:v>

--- a/基本設計/10_API共通と認証_基本設計書.xlsx
+++ b/基本設計/10_API共通と認証_基本設計書.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<ns0:workbook xmlns:ns0="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <ns0:sheets>
-    <ns0:sheet name="00_表紙" sheetId="1" ns1:id="R26acc7e2e7ca4377"/>
-    <ns0:sheet name="01_改訂履歴" sheetId="2" ns1:id="Re12fe77be41a478f"/>
-    <ns0:sheet name="18_API一覧" sheetId="19" ns1:id="R977d33cb9cff4dbe"/>
-    <ns0:sheet name="19_API共通I-O" sheetId="20" ns1:id="Rf1b51900966f4e51"/>
-    <ns0:sheet name="21_エラーコード" sheetId="22" ns1:id="R94f16b2069c64e54"/>
-    <ns0:sheet name="22_API処理・権限" sheetId="23" ns1:id="Ra68a01ad3197493f"/>
-    <ns0:sheet name="23_API項目定義" sheetId="24" ns1:id="R01db1a4d85f94e94"/>
-    <ns0:sheet name="24_APIサンプル" sheetId="25" ns1:id="R398209dcf4de41bb"/>
-  </ns0:sheets>
-</ns0:workbook>
+<x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheets>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00_表紙" sheetId="1" r:id="R6ced9d6bdc0c4b48"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_改訂履歴" sheetId="2" r:id="Rf4bd3a41175c468e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="18_API一覧" sheetId="19" r:id="R2a359c2f480f4233"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="19_API共通I-O" sheetId="20" r:id="Reece9ad6746e41ad"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="21_エラーコード" sheetId="22" r:id="R87b9f86e6a554b50"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="22_API処理・権限" sheetId="23" r:id="R46bf1d61c2fc4bb7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="23_API項目定義" sheetId="24" r:id="Ree148ef3594a4089"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="24_APIサンプル" sheetId="25" r:id="R8f4a9e7acb344ee7"/>
+  </x:sheets>
+</x:workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2020,7 +2020,7 @@
         <x:v>2026-09-29</x:v>
       </x:c>
       <x:c r="C22" t="str">
-        <x:v>CHG-MENU-20260929-01：U-01対応。固定Menu Code・menus契約・下流Bindingを整合。既存権限・Route・DBは変更なし。</x:v>
+        <x:v>CHG-MENU-20260929-01：U-01対応。固定Menu Code・menus契約・下流Bindingを整合。既存権限・Route・DBは変更なし。 Serverの許容値とClientの未知Code防御を明確に区別。</x:v>
       </x:c>
       <x:c r="D22" t="str">
         <x:v>－</x:v>
@@ -16458,37 +16458,37 @@
       <x:c r="L327" s="241"/>
     </x:row>
     <x:row r="328" ht="160" customHeight="1">
-      <x:c r="A328" t="str">
+      <x:c r="A328" s="241" t="str">
         <x:v>API-AUTH-004</x:v>
       </x:c>
-      <x:c r="B328" t="str">
-        <x:v>Response</x:v>
-      </x:c>
-      <x:c r="C328" t="str">
-        <x:v>body</x:v>
-      </x:c>
-      <x:c r="D328" t="str">
+      <x:c r="B328" s="241" t="str">
+        <x:v>Response</x:v>
+      </x:c>
+      <x:c r="C328" s="241" t="str">
+        <x:v>body</x:v>
+      </x:c>
+      <x:c r="D328" s="241" t="str">
         <x:v>response.body.data.user.menus[]</x:v>
       </x:c>
-      <x:c r="E328" t="str">
+      <x:c r="E328" s="241" t="str">
         <x:v>String</x:v>
       </x:c>
-      <x:c r="F328" t="str">
+      <x:c r="F328" s="241" t="str">
         <x:v>要素存在時必須</x:v>
       </x:c>
-      <x:c r="G328" t="str">
+      <x:c r="G328" s="241" t="str">
         <x:v>02の固定Code値域</x:v>
       </x:c>
-      <x:c r="H328" t="str">
+      <x:c r="H328" s="241" t="str">
         <x:v>02／10_メニュー権限 2節のMenu Code</x:v>
       </x:c>
-      <x:c r="I328" t="str">
-        <x:v>不可</x:v>
-      </x:c>
-      <x:c r="J328" t="str">
-        <x:v>固定Code。Clientは未知Stringを無視・重複を表示時集約する。欠落・Null・非String要素は共通Schema Error。未知StringのみはSchema ErrorにせずMenu候補から除外。</x:v>
-      </x:c>
-      <x:c r="K328" t="str">
+      <x:c r="I328" s="241" t="str">
+        <x:v>不可</x:v>
+      </x:c>
+      <x:c r="J328" s="241" t="str">
+        <x:v>Server返却値は02／10_メニュー権限 2節の14 Codeのみ。独自Code・未知Codeは契約上不可。Clientは防御として未知Stringを無視・重複を表示時集約する。欠落・Null・非String要素は共通Schema Error。未知Stringの除外は契約上の許可を意味しない。</x:v>
+      </x:c>
+      <x:c r="K328" s="241" t="str">
         <x:v>02／10_メニュー権限</x:v>
       </x:c>
     </x:row>

--- a/基本設計/10_API共通と認証_基本設計書.xlsx
+++ b/基本設計/10_API共通と認証_基本設計書.xlsx
@@ -2,14 +2,14 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00_表紙" sheetId="1" r:id="Rff23c7d0a3d34b70"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_改訂履歴" sheetId="2" r:id="R8585da9df2f9408c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="18_API一覧" sheetId="19" r:id="R2eca0f4f710f4063"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="19_API共通I-O" sheetId="20" r:id="R68e1531cb0584a34"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="21_エラーコード" sheetId="22" r:id="R46d09f5c4f1b4158"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="22_API処理・権限" sheetId="23" r:id="R9fb5a999c6554dd8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="23_API項目定義" sheetId="24" r:id="Ra848c900dfba438d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="24_APIサンプル" sheetId="25" r:id="Re37b4c435a794dea"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00_表紙" sheetId="1" r:id="R6ced9d6bdc0c4b48"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_改訂履歴" sheetId="2" r:id="Rf4bd3a41175c468e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="18_API一覧" sheetId="19" r:id="R2a359c2f480f4233"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="19_API共通I-O" sheetId="20" r:id="Reece9ad6746e41ad"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="21_エラーコード" sheetId="22" r:id="R87b9f86e6a554b50"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="22_API処理・権限" sheetId="23" r:id="R46bf1d61c2fc4bb7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="23_API項目定義" sheetId="24" r:id="Ree148ef3594a4089"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="24_APIサンプル" sheetId="25" r:id="R8f4a9e7acb344ee7"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1320,7 +1320,7 @@
     <x:row r="11">
       <x:c r="B11"/>
       <x:c r="C11" s="203" t="str">
-        <x:v>Ver.2.6</x:v>
+        <x:v>Ver.2.7</x:v>
       </x:c>
       <x:c r="D11"/>
       <x:c r="E11"/>
@@ -1343,7 +1343,7 @@
         <x:v>版数</x:v>
       </x:c>
       <x:c r="D13" s="243" t="str">
-        <x:v>Ver.2.6</x:v>
+        <x:v>Ver.2.7</x:v>
       </x:c>
       <x:c r="E13" s="196" t="str">
         <x:v>Ver.2.6</x:v>
@@ -1357,7 +1357,7 @@
         <x:v>改訂日</x:v>
       </x:c>
       <x:c r="D14" s="243" t="str">
-        <x:v>2026-09-28</x:v>
+        <x:v>2026-09-29</x:v>
       </x:c>
       <x:c r="E14" s="196" t="str">
         <x:v>2026-09-28</x:v>
@@ -1572,7 +1572,7 @@
     </x:row>
     <x:row r="4" ht="24" customHeight="1">
       <x:c r="A4" s="246" t="str">
-        <x:v>版数：Ver.2.6    改訂日：2026-09-28    基準Baseline：BL-2026-09-24</x:v>
+        <x:v>版数：Ver.2.7    改訂日：2026-09-29    基準Baseline：BL-2026-09-24</x:v>
       </x:c>
       <x:c r="B4" s="63" t="str">
         <x:v>版数：Ver.2.6    改訂日：2026-09-28    基準Baseline：BL-2026-09-24</x:v>
@@ -2010,6 +2010,32 @@
       </x:c>
       <x:c r="H21" s="241" t="str">
         <x:v>変更指示に基づく改訂。新Baseline承認は別途記録。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" ht="95" customHeight="1">
+      <x:c r="A22" t="str">
+        <x:v>Ver.2.7</x:v>
+      </x:c>
+      <x:c r="B22" t="str">
+        <x:v>2026-09-29</x:v>
+      </x:c>
+      <x:c r="C22" t="str">
+        <x:v>CHG-MENU-20260929-01：U-01対応。固定Menu Code・menus契約・下流Bindingを整合。既存権限・Route・DBは変更なし。 Serverの許容値とClientの未知Code防御を明確に区別。</x:v>
+      </x:c>
+      <x:c r="D22" t="str">
+        <x:v>－</x:v>
+      </x:c>
+      <x:c r="E22" t="str">
+        <x:v>－</x:v>
+      </x:c>
+      <x:c r="F22" t="str">
+        <x:v>－</x:v>
+      </x:c>
+      <x:c r="G22" t="str">
+        <x:v>修正済</x:v>
+      </x:c>
+      <x:c r="H22" t="str">
+        <x:v>方式合意に基づく補完。成果物の正式承認は別途。</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -2079,7 +2105,7 @@
     </x:row>
     <x:row r="4">
       <x:c r="A4" s="246" t="str">
-        <x:v>版数：Ver.2.6</x:v>
+        <x:v>版数：Ver.2.7</x:v>
       </x:c>
       <x:c r="B4" s="63" t="str">
         <x:v>版数：Ver.2.6</x:v>
@@ -2087,7 +2113,7 @@
       <x:c r="C4" s="63"/>
       <x:c r="D4" s="63"/>
       <x:c r="E4" s="246" t="str">
-        <x:v>改訂日：2026-09-28</x:v>
+        <x:v>改訂日：2026-09-29</x:v>
       </x:c>
       <x:c r="F4" s="63" t="str">
         <x:v>改訂日：2026-09-28</x:v>
@@ -3106,13 +3132,13 @@
     </x:row>
     <x:row r="4">
       <x:c r="A4" s="247" t="str">
-        <x:v>版数：Ver.2.6</x:v>
+        <x:v>版数：Ver.2.7</x:v>
       </x:c>
       <x:c r="B4" s="23" t="str">
         <x:v>版数：Ver.2.6</x:v>
       </x:c>
       <x:c r="C4" s="248" t="str">
-        <x:v>Ver.2.6</x:v>
+        <x:v>Ver.2.7</x:v>
       </x:c>
       <x:c r="D4" s="21" t="str">
         <x:v>Ver.2.6</x:v>
@@ -4469,14 +4495,14 @@
         <x:v>版数</x:v>
       </x:c>
       <x:c r="B4" s="63" t="str">
-        <x:v>Ver.2.6</x:v>
+        <x:v>Ver.2.7</x:v>
       </x:c>
       <x:c r="C4" s="63"/>
       <x:c r="D4" s="62" t="str">
         <x:v>改訂日</x:v>
       </x:c>
       <x:c r="E4" s="63" t="str">
-        <x:v>2026-09-28</x:v>
+        <x:v>2026-09-29</x:v>
       </x:c>
       <x:c r="F4" s="63"/>
       <x:c r="G4" s="63"/>
@@ -4623,7 +4649,7 @@
         <x:v>共通Interceptor</x:v>
       </x:c>
     </x:row>
-    <x:row r="11" ht="30" customHeight="1">
+    <x:row r="11" ht="125" customHeight="1">
       <x:c r="A11" s="67" t="str">
         <x:v>API-AUTH-004</x:v>
       </x:c>
@@ -4631,7 +4657,7 @@
         <x:v>現在ユーザー取得</x:v>
       </x:c>
       <x:c r="C11" s="67" t="str">
-        <x:v>1) 02の対応Permission/Data Scopeを判定。2) 23_API項目定義に従い入力を検証。3) users,employees,roles,permissionsを参照。4) 業務Dataの更新なし。5) 23_API項目定義の正常Responseを返す。</x:v>
+        <x:v>1) 02の対応Permission/Data Scopeを判定。2) 23_API項目定義に従い入力を検証。3) users,employees,roles,permissionsを参照。4) 業務Dataの更新なし。5) menusを02／10_メニュー権限の固定Code・Role/Permission条件・表示順で生成する。6) 23_API項目定義の正常Responseを返す。</x:v>
       </x:c>
       <x:c r="D11" s="67" t="str">
         <x:v>02／13_API権限対応 API-AUTH-004
@@ -5277,7 +5303,7 @@
         <x:v>版数</x:v>
       </x:c>
       <x:c r="B4" s="63" t="str">
-        <x:v>Ver.2.6</x:v>
+        <x:v>Ver.2.7</x:v>
       </x:c>
       <x:c r="C4" s="139"/>
       <x:c r="D4" s="139"/>
@@ -5286,7 +5312,7 @@
         <x:v>改訂日</x:v>
       </x:c>
       <x:c r="G4" s="63" t="str">
-        <x:v>2026-09-28</x:v>
+        <x:v>2026-09-29</x:v>
       </x:c>
       <x:c r="H4" s="139"/>
       <x:c r="I4" s="139"/>
@@ -6638,7 +6664,7 @@
         <x:v>permissions + role_permissions + user_roles</x:v>
       </x:c>
     </x:row>
-    <x:row r="45" ht="15" hidden="0" customHeight="1">
+    <x:row r="45" ht="115" hidden="0" customHeight="1">
       <x:c r="A45" s="67" t="str">
         <x:v>API-AUTH-004</x:v>
       </x:c>
@@ -6661,16 +6687,16 @@
         <x:v>-</x:v>
       </x:c>
       <x:c r="H45" s="67" t="str">
-        <x:v>-</x:v>
+        <x:v>02_権限基本設計書／10_メニュー権限／2節 Menu Code（大文字小文字区別）</x:v>
       </x:c>
       <x:c r="I45" s="67" t="str">
         <x:v>不可</x:v>
       </x:c>
       <x:c r="J45" s="67" t="str">
-        <x:v>menus</x:v>
+        <x:v>固定Menu Code配列。空配列可、配列・要素ともNull不可、各要素String。重複なし、02の表示順昇順。表示名・Routeは返却しない。</x:v>
       </x:c>
       <x:c r="K45" s="67" t="str">
-        <x:v>permissionsからMenu生成</x:v>
+        <x:v>02／10_メニュー権限の生成規則に従い、roles・permissionsから生成（DB列追加なし）。</x:v>
       </x:c>
     </x:row>
     <x:row r="46" ht="15" hidden="0" customHeight="1">
@@ -16430,6 +16456,41 @@
         <x:v>業務条件</x:v>
       </x:c>
       <x:c r="L327" s="241"/>
+    </x:row>
+    <x:row r="328" ht="160" customHeight="1">
+      <x:c r="A328" s="241" t="str">
+        <x:v>API-AUTH-004</x:v>
+      </x:c>
+      <x:c r="B328" s="241" t="str">
+        <x:v>Response</x:v>
+      </x:c>
+      <x:c r="C328" s="241" t="str">
+        <x:v>body</x:v>
+      </x:c>
+      <x:c r="D328" s="241" t="str">
+        <x:v>response.body.data.user.menus[]</x:v>
+      </x:c>
+      <x:c r="E328" s="241" t="str">
+        <x:v>String</x:v>
+      </x:c>
+      <x:c r="F328" s="241" t="str">
+        <x:v>要素存在時必須</x:v>
+      </x:c>
+      <x:c r="G328" s="241" t="str">
+        <x:v>02の固定Code値域</x:v>
+      </x:c>
+      <x:c r="H328" s="241" t="str">
+        <x:v>02／10_メニュー権限 2節のMenu Code</x:v>
+      </x:c>
+      <x:c r="I328" s="241" t="str">
+        <x:v>不可</x:v>
+      </x:c>
+      <x:c r="J328" s="241" t="str">
+        <x:v>Server返却値は02／10_メニュー権限 2節の14 Codeのみ。独自Code・未知Codeは契約上不可。Clientは防御として未知Stringを無視・重複を表示時集約する。欠落・Null・非String要素は共通Schema Error。未知Stringの除外は契約上の許可を意味しない。</x:v>
+      </x:c>
+      <x:c r="K328" s="241" t="str">
+        <x:v>02／10_メニュー権限</x:v>
+      </x:c>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -16496,14 +16557,14 @@
         <x:v>版数</x:v>
       </x:c>
       <x:c r="B4" s="63" t="str">
-        <x:v>Ver.2.6</x:v>
+        <x:v>Ver.2.7</x:v>
       </x:c>
       <x:c r="C4" s="139"/>
       <x:c r="D4" s="174" t="str">
         <x:v>改訂日</x:v>
       </x:c>
       <x:c r="E4" s="63" t="str">
-        <x:v>2026-09-28</x:v>
+        <x:v>2026-09-29</x:v>
       </x:c>
       <x:c r="F4" s="139"/>
       <x:c r="G4" s="139"/>
@@ -16622,7 +16683,7 @@
         <x:v>値は例。項目定義を正とする</x:v>
       </x:c>
     </x:row>
-    <x:row r="11" ht="100" customHeight="1">
+    <x:row r="11" ht="270" customHeight="1">
       <x:c r="A11" s="67" t="str">
         <x:v>API-AUTH-004</x:v>
       </x:c>
@@ -16633,7 +16694,7 @@
         <x:v>{}</x:v>
       </x:c>
       <x:c r="D11" s="67" t="str">
-        <x:v>{"code": "COMMON-0000", "message": "処理成功", "timestamp": "2026-08-10T10:00:00+09:00", "traceId": "7f3a9c01e2b44d8a", "data": {"user": {"id": 1001, "employeeId": 1001, "name": "サンプル", "roles": ["ROLE-EMP"], "permissions": ["PERM-TASK-READ", "PERM-TASK-PROGRESS"], "menus": ["マイタスク"], "passwordMustChange": false}}}</x:v>
+        <x:v>{"code":"COMMON-0000","message":"処理成功","timestamp":"2026-08-10T10:00:00+09:00","traceId":"7f3a9c01e2b44d8a","data":{"user":{"id":1001,"employeeId":1001,"name":"サンプル","roles":["ROLE-EMP"],"permissions":["PERM-DASH-READ","PERM-PRJ-READ","PERM-TASK-READ","PERM-TASK-PROGRESS","PERM-RPT-SELF","PERM-FILE-WRITE"],"menus":["MENU-HOME","MENU-PROJECTS","MENU-MY-PROJECTS","MENU-MY-TASKS","MENU-TASK-BOARD","MENU-MY-REPORTS","MENU-NOTIFICATIONS"],"passwordMustChange":false}}}</x:v>
       </x:c>
       <x:c r="E11" s="67" t="str">
         <x:v>200</x:v>
